--- a/Data/NDA_active_passive_voice1.xlsx
+++ b/Data/NDA_active_passive_voice1.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -472,2895 +472,2785 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>1</v>
+        <v>33</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>They do not accept credit cards everywhere.</t>
+          <t>The government has launched a massive tribal</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Credit cards are not being accepted</t>
+          <t>A massive tribal welfare programme is</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Credit cards were not accepted everywhere.</t>
+          <t>A massive tribal welfare program has been launched by the government.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Credit cards do not accept them everywhere.</t>
+          <t>Jharkhand government has launched a</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Credit cards are not accepted everywhere.</t>
+          <t>The government in Jharkhand has launched</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Credit cards are not accepted everywhere.</t>
+          <t>A massive tribal welfare program has been launched by the government.</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>"They" is the subject, and "credit cards" is the object. In passive voice, the object becomes the subject, and the verb changes to "are not accepted."</t>
+          <t>The object "a massive tribal welfare program" becomes the subject, and "has launched" changes to "has been launched</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>2</v>
+        <v>112</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>The police caught the thief at last.</t>
+          <t>The purity of justice is maintained by the reports</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>At last the thief was caught by the police</t>
+          <t>The law courts maintain purity of justice in</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>The thief at last caught the police.</t>
+          <t>The reports of the proceedings of the law</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>The thief was at last caught by the police.</t>
+          <t>Pure justice is maintained in the proceedings</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>At last the thief by the police was caught.</t>
+          <t>The maintenance of justice is pure in the</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>At last the thief was caught by the police</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>"The police" is the subject, and "the thief" is the object. The verb "caught" changes to "was caught" in the passive form.</t>
-        </is>
-      </c>
+          <t>The reports of the proceedings of the law</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>The question paper for the eleventh standard was set by the history teacher</t>
+          <t>It is being read by us.</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>The history teacher set the question paper.</t>
+          <t>We are reading it.</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>The history teacher set the eleventh question</t>
+          <t>It will be read by us.</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>The history teacher set the question paper</t>
+          <t>We can read it.</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>The history teacher had the question paper</t>
+          <t>We have to read it.</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>The history teacher set the question paper</t>
+          <t>We are reading it.</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>The subject "the history teacher" performs the action, and "was set" changes to "set."</t>
+          <t>The subject "we" performs the action, and "is being read" changes to "are reading."</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>4</v>
+        <v>107</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Somebody has stolen his book.</t>
+          <t>Everyone admires our principal.</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>His book was stolen.</t>
+          <t>Our principal has been admired by everyone.</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>His book was stolen by somebody.</t>
+          <t>Our principal was admired by everyone.</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>His book has been stolen.</t>
+          <t>Our principal is being admired by everyone.</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>His book had been stolen by somebody.</t>
+          <t>Our principal is admired by everyone.</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>His book has been stolen.</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>The object "his book" becomes the subject, and the verb changes to "has been stolen."</t>
-        </is>
-      </c>
+          <t>Our principal is admired by everyone.</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>5</v>
+        <v>36</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>We will telecast the programme next Sunday at 4</t>
+          <t>They will demolish the entire block.</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>The programme will be telecast by us next sunday at 4pm</t>
+          <t>The entire block is being demolished</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>The programme would be telecast by us next</t>
+          <t>The block may be demolished entirely.</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>The programme will be telecasted by us next</t>
+          <t>The entire block will have to be demolished</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>The programme would be telecasted by us</t>
+          <t>The entire block will be demolished by them.</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>The programme will be telecast by us next sunday at 4pm</t>
+          <t>The entire block will be demolished by them.</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>The object "the programme" becomes the subject, and the verb changes to "will be telecast."</t>
+          <t>The object "the entire block" becomes the subject, and "will demolish" changes to "will be demolished.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>6</v>
+        <v>123</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Open the door.</t>
+          <t>Shut all the doors and windows in the night.</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Let the door should open.</t>
+          <t>Let all the doors and windows be shut in the</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Let the door is opened.</t>
+          <t>All the doors and windows may be shut in</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Let open the door.</t>
+          <t>Let all the doors and windows remain shut</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Let the door be opened.</t>
+          <t>All the doors and windows be shutted in</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Let the door be opened.</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>In imperative sentences, "let" is used to form the passive voice.</t>
-        </is>
-      </c>
+          <t>Let all the doors and windows be shut in the</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>7</v>
+        <v>86</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>‘The Titanic’ was hit by an iceberg.</t>
+          <t>Gagan Narang and Vijay won bronze medals in</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>An iceberg hit “The Titanic’.</t>
+          <t>Bronze medals won by Gagan Narang and</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>An iceberg was hit by ‘The Titanic.’`</t>
+          <t>Bronze medals had been won by Gagan</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>An iceberg was being hit by ‘The Titanic’.</t>
+          <t>Bronze medals were won by Gagan Narang</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>An iceberg was hitting ‘The Titanic.’</t>
+          <t>Bronze medals have been won by Gagan</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>An iceberg hit “The Titanic’.</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>he subject "The Titanic" becomes the object, and "was hit" changes to "hit."</t>
-        </is>
-      </c>
+          <t>Bronze medals were won by Gagan Narang</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>8</v>
+        <v>37</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>The comic scenes in the play were overdone by the actor</t>
+          <t>The burglar destroyed several items in the room.</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>The actors overdid the comic scenes in the</t>
+          <t>Several items destroyed in the room by the</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>The actors overacted the comic scenes in the play</t>
+          <t>Several items in the room were destroyed by the burglar</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>The play was full of comic scenes.</t>
+          <t>Including the carpet, several items in the</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>The actors comically performed the play.</t>
+          <t>The burglar, being destroyed several items</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>The actors overacted the comic scenes in the play</t>
+          <t>Several items in the room were destroyed by the burglar</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>The subject "the actors" becomes active, and "were overdone" changes to "overdid."</t>
+          <t>The object "several items in the room" becomes the subject, and "destroyed" changes to "were destroyed."</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>9</v>
+        <v>103</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>My watch has been stolen.</t>
+          <t>Jane Austen devoted her whole life to her</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Someone has stolen my watch.</t>
+          <t>Jane Austen’s whole life is devoted to her</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>They have stolen my watch.</t>
+          <t>Jane Austen’s whole life had been devoted</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>The watch has been stolen by him.</t>
+          <t>Jane Austen’s whole life was devoted to her</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Somebody have stolen my watch.</t>
+          <t>Jane Austen’s whole life has devoted to her</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Someone has stolen my watch.</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>The subject "someone" becomes explicit, and "has been stolen" changes to "has stolen."</t>
-        </is>
-      </c>
+          <t>Jane Austen’s whole life was devoted to her</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>10</v>
+        <v>70</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>The doctor advised her to take rest.</t>
+          <t>She learns music.</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>She has been advised rest by the doctor.</t>
+          <t>Music was learnt by her.</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>She was advised to be taken ret by the doctor.</t>
+          <t>Music was being learnt by her.</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>She was advised to take rest by the doctor.</t>
+          <t>Music is being learnt by her.</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>She has been advised to take rest by the</t>
+          <t>Music is leant by her.</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>She was advised to take rest by the doctor.</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>The object "her" becomes the subject, and "advised" changes to "was advised."</t>
-        </is>
-      </c>
+          <t>Music is leant by her.</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>11</v>
+        <v>65</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>People call him a fool.</t>
+          <t>The house has been painted yellow by Nikil.</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>He has been called a fool</t>
+          <t>Nikil had painted the house yellow.</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>He is called a fool by the people.</t>
+          <t>Nikil has painted the house yellow.</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>The people have been calling him a fool.</t>
+          <t>Nikil was painting yellow the house.</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>We all people have called him a fool</t>
+          <t>Nikil has been painting yellow the house.</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>He is called a fool by the people.</t>
+          <t>Nikil has painted the house yellow.</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>The object "him" becomes the subject, and "call" changes to "is called."</t>
+          <t>The subject "Nikhil" becomes active, and "has been painted" changes to "has painted."</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>12</v>
+        <v>66</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>It is being read by us.</t>
+          <t>The news surprised me.</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>We are reading it.</t>
+          <t>I am surprised by the news.</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>It will be read by us.</t>
+          <t>I was surprised by the news.</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>We can read it.</t>
+          <t>The news was surprised by me.</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>We have to read it.</t>
+          <t>The news was a big surprise.</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>We are reading it.</t>
+          <t>I was surprised by the news.</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>The subject "we" performs the action, and "is being read" changes to "are reading."</t>
+          <t>The object "me" becomes the subject, and "surprised" changes to "was surprised."</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>13</v>
+        <v>62</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>He had committed a mistake.</t>
+          <t>We waste much time on social websites.</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>A mistake had committed by him.</t>
+          <t>Much time was wasted on social websites.</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>A mistake was committed by him.</t>
+          <t>Much time will be wasted on social websites.</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>A mistake had been committed by him.</t>
+          <t>Much time is wasted by us on social websites</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>A mistake has been committed by him</t>
+          <t>Much time is being wasted y us on social websites</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>A mistake had been committed by him.</t>
+          <t>Much time is wasted by us on social websites</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>The object "a mistake" becomes the subject, and "had committed" changes to "had been committed."</t>
+          <t>The object "much time" becomes the subject, and "waste" changes to "is wasted."</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>The most useful training of my career was given to me by my boss</t>
+          <t>The students were laughing at the old man.</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>My boss has been giving me the most useful</t>
+          <t>The old man was being laughed at by the</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>My boss gives me the most useful training.</t>
+          <t>The old man was laughed at by the students.</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>My boss is giving me the most usefully</t>
+          <t>The old man was being laughed by the</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>My boss gave me the most useful training of my career</t>
+          <t>The old man is laughing at the students.</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>My boss gave me the most useful training of my career</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>The subject "the mentor" becomes active, and "was given" changes to "gave."</t>
-        </is>
-      </c>
+          <t>The old man was being laughed at by the</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>15</v>
+        <v>126</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>We have decided to open a new branch</t>
+          <t>She always cooks delicious food.</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>To open a new branch was decided by us.</t>
+          <t>Delicious food is always cooked by her.</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>To be opened a new branch has been decided.</t>
+          <t>Delicious food is always being cooked by</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>It has been decided to open a new branch.</t>
+          <t>Delicious food has been cooked by her.</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>It may be decided to open a new branch by</t>
+          <t>Delicious food was being cooked by her.</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>It has been decided to open a new branch.</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>The object "a new branch" becomes the subject, and "have decided" changes to "has been decided to be open."</t>
-        </is>
-      </c>
+          <t>Delicious food is always cooked by her.</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>16</v>
+        <v>108</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>The loan will be sanctioned by the bank.</t>
+          <t>The Manager granted me two days leave.</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>The bank sanctioned the loan.</t>
+          <t>I had been granted two days’ leave by the</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>The bank is going to sanction the loan.</t>
+          <t>I have been granted two days’ leave by the</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>The bank would sanction the loan.</t>
+          <t>I granted two days’ leave by the Manager.</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>The bank will sanction the loan.</t>
+          <t>I was granted two days’ leave by the</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>The bank will sanction the loan.</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>The subject "the bank" performs the action, and "will be sanctioned" changes to "will sanction."</t>
-        </is>
-      </c>
+          <t>I was granted two days’ leave by the</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>17</v>
+        <v>75</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Paint the windows.</t>
+          <t>Don’t subject the animals to cruelty.</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Windows should be painted.</t>
+          <t>The animals are not to be subjected to</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Let the windows be painted.</t>
+          <t>The animals shall not be subjected to cruelty.</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Let be the windows painted.</t>
+          <t>The animals will not be subjected to cruelty.</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Windows are let to be painted.</t>
+          <t>The animals should not be subjected to</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Let the windows be painted.</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>In imperative sentences, "let" is used for passive voice.</t>
-        </is>
-      </c>
+          <t>The animals should not be subjected to</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>18</v>
+        <v>61</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>The traitors should be shot dead.</t>
+          <t>My parents are advising me about my further studies</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>They should have shot the traitors dead.</t>
+          <t>I am being advised about my further studies by my parents.</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>They shall shoot the traitors dead.</t>
+          <t>I am advised by my parents about my further studies</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>They should shoot the traitors dead.</t>
+          <t>I was advised about my further studies by my parent</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>They shot the traitors dead.</t>
+          <t>I had been advised about my further studies</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>They should shoot the traitors dead.</t>
+          <t>I am being advised about my further studies by my parents.</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>The subject "someone" performs the action, and "should be shot" changes to "should shoot."</t>
+          <t>The object "me" becomes the subject, and "are advising" changes to "am being advised."</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>19</v>
+        <v>42</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Rahul is teaching the children in the slum areas.</t>
+          <t>One must keep one’s promises.</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>The children in the slum areas are taught by</t>
+          <t>One’s promises are kept</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>The children are taught by Rahul in the slum</t>
+          <t>One’s promises must kept</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>In the slum areas the children are learning</t>
+          <t>One’s promises were kept</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>The children in the slum areas are being taught by Rahul</t>
+          <t>One’s promises must be kept</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>The children in the slum areas are being taught by Rahul</t>
+          <t>One’s promises must be kept</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>The object "the children in the slum areas" becomes the subject, and "is teaching" changes to "are being taught."</t>
+          <t>The object "promises" becomes the subject, and "must keep" changes to "must be kept."</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>20</v>
+        <v>96</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>One cannot expect children to understand these problems</t>
+          <t>One should not question his integrity.</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Children cannot be expected to understand</t>
+          <t>His integrity should not be questioned by</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Children to understand these problems</t>
+          <t>His integrity should not be questioned.</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Children cannot be expected to understand these problems</t>
+          <t>How can his integrity be questioned ?</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>To understand these problems cannot be</t>
+          <t>Who can doubt his integrity ?</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Children cannot be expected to understand these problems</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>The object "children" becomes the subject, and "cannot expect" changes to "cannot be expected."</t>
-        </is>
-      </c>
+          <t>His integrity should not be questioned.</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>21</v>
+        <v>105</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Why did she break the garden wall?</t>
+          <t>They are looking after the child jointly.</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Why the garden wall was broken by her?</t>
+          <t>The child is being looked after by them</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Why had the garden wall been broken by</t>
+          <t>The child is looked after by them jointly</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Why was the garden wall broken by her?</t>
+          <t>The child was being looked after by them</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Why will the garden wall be broken by her?</t>
+          <t>The child had been looked after by them</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Why was the garden wall broken by her?</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>The object "the garden wall" becomes the subject, and "did break" changes to "was broken."</t>
-        </is>
-      </c>
+          <t>The child is being looked after by them</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>22</v>
+        <v>120</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>The students were laughing at the old man.</t>
+          <t>Who painted it?</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>The old man was being laughed at by the</t>
+          <t>It was painted?</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>The old man was laughed at by the students.</t>
+          <t>Was it painted?</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>The old man was being laughed by the</t>
+          <t>Had it been painted by?</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>The old man is laughing at the students.</t>
+          <t>By whom was it painted?</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>The old man was being laughed at by the</t>
+          <t>By whom was it painted?</t>
         </is>
       </c>
       <c r="H23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>23</v>
+        <v>71</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>He admonished her for the error.</t>
+          <t>They are going to build a new airport near the old</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>She was admonished by him for the error.</t>
+          <t>A new airport going to be built near the old</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>She has been admonished by him for the</t>
+          <t>A new airport is being built near the old one.</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>She would be admonished by him for the</t>
+          <t>A new airport will be built near the old one.</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>She is admonished by him for the error.</t>
+          <t>A new airport is going to be built near the</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>She was admonished by him for the error.</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>The object "her" becomes the subject, and "admonished" changes to "was admonished."</t>
-        </is>
-      </c>
+          <t>A new airport is going to be built near the</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>24</v>
+        <v>94</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Can we send this big parcel by air?</t>
+          <t>One should keep one’s promises.</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Can this big parcel be sent by air?</t>
+          <t>Promises should be kept.</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Can this big parcel sent by air?</t>
+          <t>One’s promises should be kept.</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Could this big parcel be sent by air?</t>
+          <t>Keep the promises made by you.</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Could this big parcel sent by us by air?</t>
+          <t>Promises be kept.</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Can this big parcel be sent by air?</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>The object "this big parcel" becomes the subject, and "send" changes to "be sent."</t>
-        </is>
-      </c>
+          <t>One’s promises should be kept.</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>The boys saved many elders from drowning.</t>
+          <t>The police caught the thief at last.</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Many elders are saved from drowning by the</t>
+          <t>At last the thief was caught by the police</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Many elders are being saved from drowning</t>
+          <t>The thief at last caught the police.</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Many elders were saved from drowning by the boys</t>
+          <t>The thief was at last caught by the police.</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Many elders have been saved from drowning</t>
+          <t>At last the thief by the police was caught.</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Many elders were saved from drowning by the boys</t>
+          <t>At last the thief was caught by the police</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>The object "many elders" becomes the subject, and "saved" changes to "were saved</t>
+          <t>"The police" is the subject, and "the thief" is the object. The verb "caught" changes to "was caught" in the passive form.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>We found him a good wife.</t>
+          <t>The comic scenes in the play were overdone by the actor</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>He was found a good wife by us.</t>
+          <t>The actors overdid the comic scenes in the</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>A good wife was found out by them.</t>
+          <t>The actors overacted the comic scenes in the play</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>A good wife found him.</t>
+          <t>The play was full of comic scenes.</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>A good wife was being found by us.</t>
+          <t>The actors comically performed the play.</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>He was found a good wife by us.</t>
+          <t>The actors overacted the comic scenes in the play</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>The object "him" becomes the subject, and "found" changes to "was found."</t>
+          <t>The subject "the actors" becomes active, and "were overdone" changes to "overdid."</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>27</v>
+        <v>99</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>You will be taken care of by me.</t>
+          <t>A big variety store was inaugurated by Sachin.</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>I will be taking care of you.</t>
+          <t>Sachin inaugurated a big variety store.</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>I would take care of you.</t>
+          <t>Sachin had inaugurated a big variety store.</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>I will take care of you.</t>
+          <t>Sachin has inaugurated a big variety store.</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>I will being take care of you.</t>
+          <t>Sachin inaugurate a big variety store.</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>I will take care of you.</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>The subject "you" becomes the object, and "will be taken care of" changes to "will take care of."</t>
-        </is>
-      </c>
+          <t>Sachin inaugurated a big variety store.</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>28</v>
+        <v>122</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Promises should be kept.</t>
+          <t>The judge delivered the sentence at the courtroom</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>You must keep the premises.</t>
+          <t>The sentence been delivered yesterday by the</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>We must keep the promises</t>
+          <t>The sentence was delivered by the judge at</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Keep the promises</t>
+          <t>The sentence was being delivered at the</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>One should keep the promises</t>
+          <t>Yesterday, the sentence had been delivered</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>One should keep the promises</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>The subject "promises" becomes the object, and "should be kept" changes to "should keep."</t>
-        </is>
-      </c>
+          <t>The sentence was delivered by the judge at</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>29</v>
+        <v>55</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Circumstances forced him to resign his post.</t>
+          <t>Your little boy broke my kitchen window this</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Circumstances make him to resign his post.</t>
+          <t>My kitchen window was broken by your little boy this morning.</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>He was forced to resign his post by circumstances</t>
+          <t>My kitchen window had been broken by your</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>He is forced to resign his post.</t>
+          <t>My kitchen window is broken by you little</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>He is forced and resigned his post.</t>
+          <t>My kitchen window was being broken by</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>He was forced to resign his post by circumstances</t>
+          <t>My kitchen window was broken by your little boy this morning.</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>The object "him" becomes the subject, and "forced" changes to "was forced."</t>
+          <t>The object "my kitchen window" becomes the subject, and "broke" changes to "was broken."</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>30</v>
+        <v>87</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>He would have written this essay in time.</t>
+          <t>The modern means of communication have made</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>The essay was written on time.</t>
+          <t>Life had been made so much easier by the</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>This essay would have been written by him in time</t>
+          <t>Life is being so much easier by the modern</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>The essay was written by him in time.</t>
+          <t>Life has been made so much easier by the</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>He wrote the essay on time.</t>
+          <t>Life was made so much easier by the modern</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>This essay would have been written by him in time</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>The object "this essay" becomes the subject, and "would have written" changes to "would have been written."</t>
-        </is>
-      </c>
+          <t>Life has been made so much easier by the</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>31</v>
+        <v>67</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Our task had been completed before sunset.</t>
+          <t>I will have completed the task by tomorrow.</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>We completed our task before sunset.</t>
+          <t>The task will be completed by me by</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>We have completed our task before sunset.</t>
+          <t>By tomorrow the task will have been completed</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>We complete our task before sunset.</t>
+          <t>The task would be completed by me by tomorrow</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>We had completed our task before sunset.</t>
+          <t>By tomorrow the task would have been  completed</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>We had completed our task before sunset.</t>
+          <t>By tomorrow the task will have been completed</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>The subject "our task" becomes the object, and "had been completed" changes to "had completed</t>
+          <t>The object "the task" becomes the subject, and "will have completed" changes to "will have been completed</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>32</v>
+        <v>102</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>The boy laughed at the beggar.</t>
+          <t>Who helps you in your daily chores?</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>The beggar was laughed by the boy.</t>
+          <t>By who are you helped in your daily chores?</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>The beggar was being laughed by the boy.</t>
+          <t>By whom are you helped in your daily</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>The beggar was being laughed at by the boy.</t>
+          <t>By who you are helped in your daily chores?</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>The beggar was laughed at by the boy.</t>
+          <t>By whom you were helped in your daily</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>The beggar was laughed at by the boy.</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>The object "the beggar" becomes the subject, and "laughed at" changes to "was laughed at.</t>
-        </is>
-      </c>
+          <t>By whom are you helped in your daily</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>The government has launched a massive tribal</t>
+          <t>He teaches us grammar.</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>A massive tribal welfare programme is</t>
+          <t>Grammar is taught to us by him</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>A massive tribal welfare program has been launched by the government.</t>
+          <t>We are taught grammar by him.</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Jharkhand government has launched a</t>
+          <t>Grammar will be taught of us by him.</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>The government in Jharkhand has launched</t>
+          <t>We were teached grammar by him.</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>A massive tribal welfare program has been launched by the government.</t>
+          <t>Grammar is taught to us by him</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>The object "a massive tribal welfare program" becomes the subject, and "has launched" changes to "has been launched</t>
+          <t>The object "grammar" becomes the subject, and "teaches" changes to "is taught."</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>34</v>
+        <v>79</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>The boys were playing cricket.</t>
+          <t>Today I accomplished my task successfully.</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Cricket had been played by the boys.</t>
+          <t>Today my task is accomplished successfully</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Cricket has been played by the boys.</t>
+          <t>Today my task accomplished successfully.</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Cricket was played by the boys.</t>
+          <t>Today my task was accomplished</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Cricket was being played by the boys.</t>
+          <t>Today my task was accomplished
+successfully</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Cricket was being played by the boys.</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>The object "cricket" becomes the subject, and "were playing" changes to "was being played.</t>
-        </is>
-      </c>
+          <t>Today my task was accomplished
+successfully</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>They drew a circle in the morning.</t>
+          <t>Why did she break the garden wall?</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>A circle was being drawn by them in the</t>
+          <t>Why the garden wall was broken by her?</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>A circle was drawn by them in the morning.</t>
+          <t>Why had the garden wall been broken by</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>In the morning a circle have been drawn by</t>
+          <t>Why was the garden wall broken by her?</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>A circle has been drawing since morning.</t>
+          <t>Why will the garden wall be broken by her?</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>A circle was drawn by them in the morning.</t>
+          <t>Why was the garden wall broken by her?</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>The object "a circle" becomes the subject, and "drew" changes to "was drawn."</t>
+          <t>The object "the garden wall" becomes the subject, and "did break" changes to "was broken."</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>36</v>
+        <v>54</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>They will demolish the entire block.</t>
+          <t>People speak English all over the world.</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>The entire block is being demolished</t>
+          <t>English was spoken all over the world.</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>The block may be demolished entirely.</t>
+          <t>English have been spoken all over the world.</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>The entire block will have to be demolished</t>
+          <t>English has been spoken all over the world.</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>The entire block will be demolished by them.</t>
+          <t>English is spoken all over the world by people</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>The entire block will be demolished by them.</t>
+          <t>English is spoken all over the world by people</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>The object "the entire block" becomes the subject, and "will demolish" changes to "will be demolished.</t>
+          <t>The object "English" becomes the subject, and "speak" changes to "is spoken."</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>The burglar destroyed several items in the room.</t>
+          <t>He would have written this essay in time.</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Several items destroyed in the room by the</t>
+          <t>The essay was written on time.</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Several items in the room were destroyed by the burglar</t>
+          <t>This essay would have been written by him in time</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Including the carpet, several items in the</t>
+          <t>The essay was written by him in time.</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>The burglar, being destroyed several items</t>
+          <t>He wrote the essay on time.</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Several items in the room were destroyed by the burglar</t>
+          <t>This essay would have been written by him in time</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>The object "several items in the room" becomes the subject, and "destroyed" changes to "were destroyed."</t>
+          <t>The object "this essay" becomes the subject, and "would have written" changes to "would have been written."</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>38</v>
+        <v>25</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>We must respect the elders.</t>
+          <t>The boys saved many elders from drowning.</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>The elders deserve respect from us.</t>
+          <t>Many elders are saved from drowning by the</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>The elders must be respected.</t>
+          <t>Many elders are being saved from drowning</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>The elders must be respected by us.</t>
+          <t>Many elders were saved from drowning by the boys</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Respect the elders we must.</t>
+          <t>Many elders have been saved from drowning</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>The elders must be respected by us.</t>
+          <t>Many elders were saved from drowning by the boys</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>The object "the elders" becomes the subject, and "must respect" changes to "must be respected."</t>
+          <t>The object "many elders" becomes the subject, and "saved" changes to "were saved</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>39</v>
+        <v>3</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>We have warned you.</t>
+          <t>The question paper for the eleventh standard was set by the history teacher</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>You have been warned by us</t>
+          <t>The history teacher set the question paper.</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>We have you warned.</t>
+          <t>The history teacher set the eleventh question</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Warned you have been.</t>
+          <t>The history teacher set the question paper</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Have you been warned.</t>
+          <t>The history teacher had the question paper</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>You have been warned by us</t>
+          <t>The history teacher set the question paper</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>The object "you" becomes the subject, and "have warned" changes to "have been warned.</t>
+          <t>The subject "the history teacher" performs the action, and "was set" changes to "set."</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>40</v>
+        <v>63</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Has anybody answered your question?</t>
+          <t>A great deal of harm is caused to the environment</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Your question has been answered?</t>
+          <t>We have caused a great deal of harm to the environment</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Anybody has answered your question?</t>
+          <t>The environment causes a great deal of harm</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Has your question been answered by anybody?</t>
+          <t>We cause a great deal of harm to the environment</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Have your answered you question ?</t>
+          <t>The environment is being caused a great deal harm</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Has your question been answered by anybody?</t>
+          <t>We cause a great deal of harm to the environment</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>The object "your question" becomes the subject, and "has answered" changes to "has been answered."</t>
+          <t>The subject "human activities" becomes active, and "is caused" changes to "cause."</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>41</v>
+        <v>127</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>The shopkeeper lowered the prices.</t>
+          <t>Mother gave him a little puppy.</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>The prices lowered the shopkeeper</t>
+          <t>He was given a little puppy by mother.</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>The prices were lowered by the shopkeeper</t>
+          <t>A little puppy was being given to him by</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Down went the prices</t>
+          <t>He had been given a little puppy by mother.</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>The shopkeeper got down the prices</t>
+          <t>A little puppy is given to him by his mother.</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>The prices were lowered by the shopkeeper</t>
-        </is>
-      </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>The object "the prices" becomes the subject, and "lowered" changes to "were lowered."</t>
-        </is>
-      </c>
+          <t>He was given a little puppy by mother.</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>42</v>
+        <v>97</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>One must keep one’s promises.</t>
+          <t>I have been sent here by the editor of Tribune.</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>One’s promises are kept</t>
+          <t>The editor of Tribune has send me here.</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>One’s promises must kept</t>
+          <t>The editor of Tribune sent me here.</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>One’s promises were kept</t>
+          <t>The editor of Tribune has sent me here.</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>One’s promises must be kept</t>
+          <t>The editor of Tribune send me here.</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>One’s promises must be kept</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>The object "promises" becomes the subject, and "must keep" changes to "must be kept."</t>
-        </is>
-      </c>
+          <t>The editor of Tribune has sent me here.</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>43</v>
+        <v>23</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>The government has not approved the new drug</t>
+          <t>He admonished her for the error.</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>The government approval for the sale of the</t>
+          <t>She was admonished by him for the error.</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>The new drug has not been approved by the government</t>
+          <t>She has been admonished by him for the</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>For the sale of the new drug we have not</t>
+          <t>She would be admonished by him for the</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>The new drug was not approved by the</t>
+          <t>She is admonished by him for the error.</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>The new drug has not been approved by the government</t>
+          <t>She was admonished by him for the error.</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>The object "the new drug" becomes the subject, and "has not approved" changes to "has not been approved."</t>
+          <t>The object "her" becomes the subject, and "admonished" changes to "was admonished."</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>44</v>
+        <v>82</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>They have published all the details of the report</t>
+          <t>When did he return my books ?</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>All the details of the report have been published by them</t>
+          <t>When were my books returned by him ?</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>The publication of the details of invention</t>
+          <t>When will my books be returned by him ?</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>All the details have been invented by the</t>
+          <t>When has he returned my books ?</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>All the inventions have been detailed by</t>
+          <t>When are my books returned by him ?</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>All the details of the report have been published by them</t>
-        </is>
-      </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>The object "all the details of the report" becomes the subject, and "have published" changes to "have been published."</t>
-        </is>
-      </c>
+          <t>When were my books returned by him ?</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>He teaches us grammar.</t>
+          <t>My books have been stolen.</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Grammar is taught to us by him</t>
+          <t>Someone has stolen my books.</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>We are taught grammar by him.</t>
+          <t>Someone stole my books.</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Grammar will be taught of us by him.</t>
+          <t>Someone have stolen my books.</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>We were teached grammar by him.</t>
+          <t>They stole my books.</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Grammar is taught to us by him</t>
+          <t>Someone has stolen my books.</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>The object "grammar" becomes the subject, and "teaches" changes to "is taught."</t>
+          <t>The subject "someone" is added, and "have been stolen" changes to "has stolen."</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>46</v>
+        <v>11</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>The manager could not accept the union leader’s proposal</t>
+          <t>People call him a fool.</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>The union leader’s proposal could not be accepted by the manager</t>
+          <t>He has been called a fool</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>The union leader’s proposals were not</t>
+          <t>He is called a fool by the people.</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>The union leader’s proposals will not be</t>
+          <t>The people have been calling him a fool.</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>The union leader’s proposals would not be</t>
+          <t>We all people have called him a fool</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>The union leader’s proposal could not be accepted by the manager</t>
+          <t>He is called a fool by the people.</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>The object "the union leader’s proposal" becomes the subject, and "could not accept" changes to "could not be accepted."</t>
+          <t>The object "him" becomes the subject, and "call" changes to "is called."</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Prepare yourself for the worst.</t>
+          <t>We have warned you.</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>You be prepared for the worst.</t>
+          <t>You have been warned by us</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>The worst should be prepared by yourself.</t>
+          <t>We have you warned.</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Let yourself be prepared for the worst.</t>
+          <t>Warned you have been.</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>For the worst, preparation should be made</t>
+          <t>Have you been warned.</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Let yourself be prepared for the worst.</t>
+          <t>You have been warned by us</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Imperative sentences use "let" in passive voice</t>
+          <t>The object "you" becomes the subject, and "have warned" changes to "have been warned.</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Please shut the door and go to sleep.</t>
+          <t>The boy laughed at the beggar.</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>The door is to be shut and you are to go to sleep</t>
+          <t>The beggar was laughed by the boy.</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Let the door be shut and you be asleep</t>
+          <t>The beggar was being laughed by the boy.</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>You are requested to shut the door and go to sleep</t>
+          <t>The beggar was being laughed at by the boy.</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>The door is to be shut and you are requested</t>
+          <t>The beggar was laughed at by the boy.</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>You are requested to shut the door and go to sleep</t>
-        </is>
-      </c>
-      <c r="H49" t="inlineStr"/>
+          <t>The beggar was laughed at by the boy.</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>The object "the beggar" becomes the subject, and "laughed at" changes to "was laughed at.</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>49</v>
+        <v>80</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>It is impossible to do this.</t>
+          <t>Look! They have painted the door.</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Doing this is impossible.</t>
+          <t>Look! The door’s being painted.</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>This is impossible to be done</t>
+          <t>Look! The door had been painted.</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>This must not be done</t>
+          <t>Look! The door has been painted.</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>This can’t be done</t>
+          <t>Look ! The door was painted.</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>This is impossible to be done</t>
+          <t>Look! The door has been painted.</t>
         </is>
       </c>
       <c r="H50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>We must take care of all living species on Earth.</t>
+          <t>The storm damaged the roof.</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>All living species on Earth are taken care of</t>
+          <t>The roof is damaged by the storm.</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>All living species on Earth must be taken care of by us</t>
+          <t>The roof was damage by the storm.</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>All living species on Earth had been taken</t>
+          <t>The roof was damaged by the storm.</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>All living species on Earth will be taken care</t>
+          <t>The roof would be damaged by the storm</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>All living species on Earth must be taken care of by us</t>
+          <t>The roof was damaged by the storm.</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>The object "all living species on Earth" becomes the subject, and "must take care of" changes to "must be taken care of</t>
+          <t>The object "the roof" becomes the subject, and "damaged" changes to "was damaged."</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>51</v>
+        <v>90</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>They are considering your proposal,</t>
+          <t>The scheme permits investors to buy the shares</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Your proposal is being considered by them.</t>
+          <t>Under the scheme the investors may be</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>You proposal was being considered by them.</t>
+          <t>Under the scheme the investors have been</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Your proposal was considered by them.</t>
+          <t>Under the scheme the investors are permitted</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Your proposal is considered by them.</t>
+          <t>Under the scheme the investors were</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Your proposal is being considered by them.</t>
-        </is>
-      </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>The object "your proposal" becomes the subject, and "are considering" changes to "is being considered.</t>
-        </is>
-      </c>
+          <t>Under the scheme the investors are permitted</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>52</v>
+        <v>106</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Two hundred people were arrested by the police.</t>
+          <t>How many languages are spoken in India?</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>The police have arrested two hundred people.</t>
+          <t>How many languages Indians are speaking</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>The police arrested two hundred people.</t>
+          <t>How many languages Indians speak?</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>The police had arrested two hundred people.</t>
+          <t>How many languages do Indians speak?</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>The police has arrested two hundred people.</t>
+          <t>How many languages did Indians speak?</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>The police arrested two hundred people.</t>
-        </is>
-      </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>The subject "the police" becomes active, and "were arrested" changes to "arrested."</t>
-        </is>
-      </c>
+          <t>How many languages do Indians speak?</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>53</v>
+        <v>84</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>The storm damaged the roof.</t>
+          <t>Gandhiji started the Quit India Movement in 1942.</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>The roof is damaged by the storm.</t>
+          <t>The Quit India Movement was started by</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>The roof was damage by the storm.</t>
+          <t>The Quit India Movement was been started</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>The roof was damaged by the storm.</t>
+          <t>The Quit India Movement had been started</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>The roof would be damaged by the storm</t>
+          <t>The Quit India Movement started by</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>The roof was damaged by the storm.</t>
-        </is>
-      </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>The object "the roof" becomes the subject, and "damaged" changes to "was damaged."</t>
-        </is>
-      </c>
+          <t>The Quit India Movement was started by</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>54</v>
+        <v>114</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>People speak English all over the world.</t>
+          <t>An awareness is being created among the people</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>English was spoken all over the world.</t>
+          <t>The Government is creating an awareness</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>English have been spoken all over the world.</t>
+          <t>The Government are creating an awareness</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>English has been spoken all over the world.</t>
+          <t>The Government creates an awareness</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>English is spoken all over the world by people</t>
+          <t>The Government created an awareness</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>English is spoken all over the world by people</t>
-        </is>
-      </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>The object "English" becomes the subject, and "speak" changes to "is spoken."</t>
-        </is>
-      </c>
+          <t>The Government is creating an awareness</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>55</v>
+        <v>13</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Your little boy broke my kitchen window this</t>
+          <t>He had committed a mistake.</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>My kitchen window was broken by your little boy this morning.</t>
+          <t>A mistake had committed by him.</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>My kitchen window had been broken by your</t>
+          <t>A mistake was committed by him.</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>My kitchen window is broken by you little</t>
+          <t>A mistake had been committed by him.</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>My kitchen window was being broken by</t>
+          <t>A mistake has been committed by him</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>My kitchen window was broken by your little boy this morning.</t>
+          <t>A mistake had been committed by him.</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>The object "my kitchen window" becomes the subject, and "broke" changes to "was broken."</t>
+          <t>The object "a mistake" becomes the subject, and "had committed" changes to "had been committed."</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>56</v>
+        <v>95</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>The criminal has to obey the court.</t>
+          <t>The thief was caught.</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>The court has to be obeyed by the criminal.</t>
+          <t>The policeman may have caught the thief.</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>The court will have to be obeyed by the</t>
+          <t>The policeman caught the thief.</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>The court must be obeyed.</t>
+          <t>The policeman has caught the thief.</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>The court will be obeyed.</t>
+          <t>The policeman had caught the thief.</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>The court has to be obeyed by the criminal.</t>
-        </is>
-      </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>The object "the court" becomes the subject, and "has to obey" changes to "has to be obeyed."</t>
-        </is>
-      </c>
+          <t>The policeman caught the thief.</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>57</v>
+        <v>20</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>The Metro Rail is being constructed by the corporation</t>
+          <t>One cannot expect children to understand these problems</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>The Corporation has been constructing the metro rail</t>
+          <t>Children cannot be expected to understand</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>The Corporation is constructing the Metro rail</t>
+          <t>Children to understand these problems</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>The Corporation has constructed the Metro rail</t>
+          <t>Children cannot be expected to understand these problems</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>The Corporation was constructing the Metro rail</t>
+          <t>To understand these problems cannot be</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>The Corporation is constructing the Metro rail</t>
+          <t>Children cannot be expected to understand these problems</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>The subject "the corporation" becomes active, and "is being constructed" changes to "is constructing."</t>
+          <t>The object "children" becomes the subject, and "cannot expect" changes to "cannot be expected."</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>58</v>
+        <v>46</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>All the letters were posted by them.</t>
+          <t>The manager could not accept the union leader’s proposal</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>They have posted all the letters.</t>
+          <t>The union leader’s proposal could not be accepted by the manager</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>They had posted all the letters.</t>
+          <t>The union leader’s proposals were not</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>They were posting all the letters.</t>
+          <t>The union leader’s proposals will not be</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>They posted all the letters.</t>
+          <t>The union leader’s proposals would not be</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>They posted all the letters.</t>
+          <t>The union leader’s proposal could not be accepted by the manager</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>The subject "they" performs the action, and "were posted" changes to "posted."</t>
+          <t>The object "the union leader’s proposal" becomes the subject, and "could not accept" changes to "could not be accepted."</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>59</v>
+        <v>28</v>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>The CEO’s son was kidnapped.</t>
+          <t>Promises should be kept.</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Someone kidnapped the CEO’s son.</t>
+          <t>You must keep the premises.</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Someone has kidnapped the CEO’s son.</t>
+          <t>We must keep the promises</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Someone is going to kidnap the CEO’s son.</t>
+          <t>Keep the promises</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Someone is kidnapping the CEO’s son.</t>
+          <t>One should keep the promises</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Someone kidnapped the CEO’s son.</t>
+          <t>One should keep the promises</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>The subject "someone" is added to make the sentence active, and "was kidnapped" changes to "kidnapped."</t>
+          <t>The subject "promises" becomes the object, and "should be kept" changes to "should keep."</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>60</v>
+        <v>41</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>My books have been stolen.</t>
+          <t>The shopkeeper lowered the prices.</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Someone has stolen my books.</t>
+          <t>The prices lowered the shopkeeper</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Someone stole my books.</t>
+          <t>The prices were lowered by the shopkeeper</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Someone have stolen my books.</t>
+          <t>Down went the prices</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>They stole my books.</t>
+          <t>The shopkeeper got down the prices</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Someone has stolen my books.</t>
+          <t>The prices were lowered by the shopkeeper</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>The subject "someone" is added, and "have been stolen" changes to "has stolen."</t>
+          <t>The object "the prices" becomes the subject, and "lowered" changes to "were lowered."</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>61</v>
+        <v>83</v>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>My parents are advising me about my further studies</t>
+          <t>We had to stop all other work to complete our</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>I am being advised about my further studies by my parents.</t>
+          <t>All other work has to be stopped by us to</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>I am advised by my parents about my further studies</t>
+          <t>All other work has stopped by us to complete</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>I was advised about my further studies by my parent</t>
+          <t>All other work had to be stopped by us to</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>I had been advised about my further studies</t>
+          <t>All other work was stopped by us to complete</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>I am being advised about my further studies by my parents.</t>
-        </is>
-      </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>The object "me" becomes the subject, and "are advising" changes to "am being advised."</t>
-        </is>
-      </c>
+          <t>All other work had to be stopped by us to</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>62</v>
+        <v>109</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>We waste much time on social websites.</t>
+          <t>They should shoot the terrorists dead.</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Much time was wasted on social websites.</t>
+          <t>The terrorists been shot dead by them.</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Much time will be wasted on social websites.</t>
+          <t>The terrorists should have been shot dead</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Much time is wasted by us on social websites</t>
+          <t>The terrorists should be shot dead by them.</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Much time is being wasted y us on social websites</t>
+          <t>The terrorists have been shot dead by them.</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Much time is wasted by us on social websites</t>
-        </is>
-      </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>The object "much time" becomes the subject, and "waste" changes to "is wasted."</t>
-        </is>
-      </c>
+          <t>The terrorists should be shot dead by them.</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>63</v>
+        <v>115</v>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>A great deal of harm is caused to the environment</t>
+          <t>Ads on TV increase the sale of any commodity.</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>We have caused a great deal of harm to the environment</t>
+          <t>The sale of any commodity is being increased</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>The environment causes a great deal of harm</t>
+          <t>The sale of any commodity are increased by</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>We cause a great deal of harm to the environment</t>
+          <t>The sale of any commodity are being</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>The environment is being caused a great deal harm</t>
+          <t>The sale of any commodity is increased by</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>We cause a great deal of harm to the environment</t>
-        </is>
-      </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>The subject "human activities" becomes active, and "is caused" changes to "cause."</t>
-        </is>
-      </c>
+          <t>The sale of any commodity is increased by</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>64</v>
+        <v>17</v>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Who wrote this article?</t>
+          <t>Paint the windows.</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Whom was this article written?</t>
+          <t>Windows should be painted.</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>By whom this article was written. ?</t>
+          <t>Let the windows be painted.</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Who was written this article?</t>
+          <t>Let be the windows painted.</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>By whom was this article written?</t>
+          <t>Windows are let to be painted.</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>By whom was this article written?</t>
+          <t>Let the windows be painted.</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>The object "this article" becomes the subject, and "wrote" changes to "was written."</t>
+          <t>In imperative sentences, "let" is used for passive voice.</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>65</v>
+        <v>7</v>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>The house has been painted yellow by Nikil.</t>
+          <t>‘The Titanic’ was hit by an iceberg.</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Nikil had painted the house yellow.</t>
+          <t>An iceberg hit “The Titanic’.</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Nikil has painted the house yellow.</t>
+          <t>An iceberg was hit by ‘The Titanic.’`</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Nikil was painting yellow the house.</t>
+          <t>An iceberg was being hit by ‘The Titanic’.</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Nikil has been painting yellow the house.</t>
+          <t>An iceberg was hitting ‘The Titanic.’</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Nikil has painted the house yellow.</t>
+          <t>An iceberg hit “The Titanic’.</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>The subject "Nikhil" becomes active, and "has been painted" changes to "has painted."</t>
+          <t>he subject "The Titanic" becomes the object, and "was hit" changes to "hit."</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>The news surprised me.</t>
+          <t>The CEO’s son was kidnapped.</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>I am surprised by the news.</t>
+          <t>Someone kidnapped the CEO’s son.</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>I was surprised by the news.</t>
+          <t>Someone has kidnapped the CEO’s son.</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>The news was surprised by me.</t>
+          <t>Someone is going to kidnap the CEO’s son.</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>The news was a big surprise.</t>
+          <t>Someone is kidnapping the CEO’s son.</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>I was surprised by the news.</t>
+          <t>Someone kidnapped the CEO’s son.</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>The object "me" becomes the subject, and "surprised" changes to "was surprised."</t>
+          <t>The subject "someone" is added to make the sentence active, and "was kidnapped" changes to "kidnapped."</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>67</v>
+        <v>116</v>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>I will have completed the task by tomorrow.</t>
+          <t>The Indian Government is encouraging the</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>The task will be completed by me by</t>
+          <t>The Europeans are encouraged by the Indian</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>By tomorrow the task will have been completed</t>
+          <t>The Europeans are encouraging by the Indian</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>The task would be completed by me by tomorrow</t>
+          <t>The Europeans are being encouraged by the</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>By tomorrow the task would have been  completed</t>
+          <t>The Europeans is being encouraged by the</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>By tomorrow the task will have been completed</t>
-        </is>
-      </c>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t>The object "the task" becomes the subject, and "will have completed" changes to "will have been completed</t>
-        </is>
-      </c>
+          <t>The Europeans are being encouraged by the</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>68</v>
+        <v>85</v>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>They are painting the walls.</t>
+          <t>One should avoid honking the horn unnecessarily.</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>The walls are painting them.</t>
+          <t>Unnecessary honking of horn ought to be</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>The walls are painted by them.</t>
+          <t>Unnecessary honking of horn can be avoided.</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>The walls are being painted by them.</t>
+          <t>Unnecessary honking of horn should be</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>The walls in painted by them.</t>
+          <t>Unnecessary honking of horn must be</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>The walls are being painted by them.</t>
-        </is>
-      </c>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>The object "the walls" becomes the subject, and "are painting" changes to "are being painted.</t>
-        </is>
-      </c>
+          <t>Unnecessary honking of horn should be</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>69</v>
+        <v>91</v>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>The box was dropped by the boy.</t>
+          <t>They were pulling down the old building.</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>The boy dropped the box.</t>
+          <t>The old building has been pulled down.</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>The boy drops the box.</t>
+          <t>The old building is being pulled down.</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>The boy has dropped the box.</t>
+          <t>The old building was being pulled down.</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>The boy is dropping the box.</t>
+          <t>The old building was pulled down.</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>The boy dropped the box.</t>
-        </is>
-      </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>The subject "the boy" becomes active, and "was dropped" changes to "dropped."</t>
-        </is>
-      </c>
+          <t>The old building was being pulled down.</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>She learns music.</t>
+          <t>Who wrote this article?</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Music was learnt by her.</t>
+          <t>Whom was this article written?</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Music was being learnt by her.</t>
+          <t>By whom this article was written. ?</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Music is being learnt by her.</t>
+          <t>Who was written this article?</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Music is leant by her.</t>
+          <t>By whom was this article written?</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Music is leant by her.</t>
-        </is>
-      </c>
-      <c r="H71" t="inlineStr"/>
+          <t>By whom was this article written?</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>The object "this article" becomes the subject, and "wrote" changes to "was written."</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>71</v>
+        <v>56</v>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>They are going to build a new airport near the old</t>
+          <t>The criminal has to obey the court.</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>A new airport going to be built near the old</t>
+          <t>The court has to be obeyed by the criminal.</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>A new airport is being built near the old one.</t>
+          <t>The court will have to be obeyed by the</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>A new airport will be built near the old one.</t>
+          <t>The court must be obeyed.</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>A new airport is going to be built near the</t>
+          <t>The court will be obeyed.</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>A new airport is going to be built near the</t>
-        </is>
-      </c>
-      <c r="H72" t="inlineStr"/>
+          <t>The court has to be obeyed by the criminal.</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>The object "the court" becomes the subject, and "has to obey" changes to "has to be obeyed."</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>72</v>
+        <v>31</v>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>My watch can’t be repaired by anyone.</t>
+          <t>Our task had been completed before sunset.</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>No one will repair my watch.</t>
+          <t>We completed our task before sunset.</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>No one can repair my watch.</t>
+          <t>We have completed our task before sunset.</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>No one can’t repair my watch.</t>
+          <t>We complete our task before sunset.</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>No one will be able to repair my watch.</t>
+          <t>We had completed our task before sunset.</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>No one can repair my watch.</t>
-        </is>
-      </c>
-      <c r="H73" t="inlineStr"/>
+          <t>We had completed our task before sunset.</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>The subject "our task" becomes the object, and "had been completed" changes to "had completed</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>73</v>
+        <v>40</v>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Rosemary was moved to tears at the sight of the</t>
+          <t>Has anybody answered your question?</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>The sight of the miserable beggar moved</t>
+          <t>Your question has been answered?</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>The sight of the miserable beggar has moved</t>
+          <t>Anybody has answered your question?</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>The sight of the miserable beggar moves</t>
+          <t>Has your question been answered by anybody?</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>The sight of the miserable beggar had moved</t>
+          <t>Have your answered you question ?</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>The sight of the miserable beggar moved</t>
-        </is>
-      </c>
-      <c r="H74" t="inlineStr"/>
+          <t>Has your question been answered by anybody?</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>The object "your question" becomes the subject, and "has answered" changes to "has been answered."</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -3400,1262 +3290,1332 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>75</v>
+        <v>1</v>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Don’t subject the animals to cruelty.</t>
+          <t>They do not accept credit cards everywhere.</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>The animals are not to be subjected to</t>
+          <t>Credit cards are not being accepted</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>The animals shall not be subjected to cruelty.</t>
+          <t>Credit cards were not accepted everywhere.</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>The animals will not be subjected to cruelty.</t>
+          <t>Credit cards do not accept them everywhere.</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>The animals should not be subjected to</t>
+          <t>Credit cards are not accepted everywhere.</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>The animals should not be subjected to</t>
-        </is>
-      </c>
-      <c r="H76" t="inlineStr"/>
+          <t>Credit cards are not accepted everywhere.</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>"They" is the subject, and "credit cards" is the object. In passive voice, the object becomes the subject, and the verb changes to "are not accepted."</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>76</v>
+        <v>9</v>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Who asked you to draft this letter ?</t>
+          <t>My watch has been stolen.</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>By who you are asked to draft this letter.</t>
+          <t>Someone has stolen my watch.</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>By who have you been asked to draft this</t>
+          <t>They have stolen my watch.</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>By whom were you asked to draft this letter</t>
+          <t>The watch has been stolen by him.</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>By whom you were asked to draft this letter.</t>
+          <t>Somebody have stolen my watch.</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>By whom were you asked to draft this letter</t>
-        </is>
-      </c>
-      <c r="H77" t="inlineStr"/>
+          <t>Someone has stolen my watch.</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>The subject "someone" becomes explicit, and "has been stolen" changes to "has stolen."</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>77</v>
+        <v>52</v>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>They created such a fuss over a trivial matter.</t>
+          <t>Two hundred people were arrested by the police.</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Such a fuss is being created over a trivial</t>
+          <t>The police have arrested two hundred people.</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Such a fuss was created over a trivial matter.</t>
+          <t>The police arrested two hundred people.</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Such a fuss has been created over a trivial</t>
+          <t>The police had arrested two hundred people.</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>By them such a fuss has been created over a</t>
+          <t>The police has arrested two hundred people.</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Such a fuss was created over a trivial matter.</t>
-        </is>
-      </c>
-      <c r="H78" t="inlineStr"/>
+          <t>The police arrested two hundred people.</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>The subject "the police" becomes active, and "were arrested" changes to "arrested."</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>78</v>
+        <v>24</v>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>The lightning caused a serious forest fire and</t>
+          <t>Can we send this big parcel by air?</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>A serious forest fire has been caused by</t>
+          <t>Can this big parcel be sent by air?</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>A serious forest fire has been caused by lightning</t>
+          <t>Can this big parcel sent by air?</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>A serious forest fire had been caused by</t>
+          <t>Could this big parcel be sent by air?</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>A serious forest fire was caused by lightning</t>
+          <t>Could this big parcel sent by us by air?</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>A serious forest fire was caused by lightning</t>
-        </is>
-      </c>
-      <c r="H79" t="inlineStr"/>
+          <t>Can this big parcel be sent by air?</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>The object "this big parcel" becomes the subject, and "send" changes to "be sent."</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>79</v>
+        <v>104</v>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Today I accomplished my task successfully.</t>
+          <t>Hamlet was written by Shakespeare.</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Today my task is accomplished successfully</t>
+          <t>Shakespeare has written Hamlet.</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Today my task accomplished successfully.</t>
+          <t>Shakespeare had written Hamlet.</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Today my task was accomplished</t>
+          <t>Shakespeare wrote Hamlet.</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Today my task was accomplished
-successfully</t>
+          <t>Shakespeare writes Hamlet.</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Today my task was accomplished
-successfully</t>
+          <t>Shakespeare wrote Hamlet.</t>
         </is>
       </c>
       <c r="H80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>80</v>
+        <v>10</v>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Look! They have painted the door.</t>
+          <t>The doctor advised her to take rest.</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Look! The door’s being painted.</t>
+          <t>She has been advised rest by the doctor.</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Look! The door had been painted.</t>
+          <t>She was advised to be taken ret by the doctor.</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Look! The door has been painted.</t>
+          <t>She was advised to take rest by the doctor.</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Look ! The door was painted.</t>
+          <t>She has been advised to take rest by the</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Look! The door has been painted.</t>
-        </is>
-      </c>
-      <c r="H81" t="inlineStr"/>
+          <t>She was advised to take rest by the doctor.</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>The object "her" becomes the subject, and "advised" changes to "was advised."</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>81</v>
+        <v>128</v>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>She was advised 15 days’ rest after her surgery.</t>
+          <t>The company paid her a meagre salary.</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>The doctor was advised her 15 days’ rest after</t>
+          <t>She was paid a meagre salary by the</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>The doctor has advised her 15 days’ rest after</t>
+          <t>A meagre salary has been paid to her by the</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>The doctor advised her 15 days’ rest after</t>
+          <t>She was being paid a meagre salary by the</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>The doctor had advised her 15 days’ rest after</t>
+          <t>A meagre salary was to be paid to her by the</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>The doctor advised her 15 days’ rest after</t>
+          <t>She was paid a meagre salary by the</t>
         </is>
       </c>
       <c r="H82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>82</v>
+        <v>124</v>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>When did he return my books ?</t>
+          <t>People use computers for various purposes.</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>When were my books returned by him ?</t>
+          <t>Computers are being used by people for</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>When will my books be returned by him ?</t>
+          <t>Computers have been used by people for</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>When has he returned my books ?</t>
+          <t>Computers are used by people for various</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>When are my books returned by him ?</t>
+          <t>Computers will be used by people for various</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>When were my books returned by him ?</t>
+          <t>Computers are used by people for various</t>
         </is>
       </c>
       <c r="H83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>We had to stop all other work to complete our</t>
+          <t>She was advised 15 days’ rest after her surgery.</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>All other work has to be stopped by us to</t>
+          <t>The doctor was advised her 15 days’ rest after</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>All other work has stopped by us to complete</t>
+          <t>The doctor has advised her 15 days’ rest after</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>All other work had to be stopped by us to</t>
+          <t>The doctor advised her 15 days’ rest after</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>All other work was stopped by us to complete</t>
+          <t>The doctor had advised her 15 days’ rest after</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>All other work had to be stopped by us to</t>
+          <t>The doctor advised her 15 days’ rest after</t>
         </is>
       </c>
       <c r="H84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>84</v>
+        <v>119</v>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Gandhiji started the Quit India Movement in 1942.</t>
+          <t>Post the letter.</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>The Quit India Movement was started by</t>
+          <t>The letter is posted.</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>The Quit India Movement was been started</t>
+          <t>The letter was posted.</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>The Quit India Movement had been started</t>
+          <t>Let the letter be posted.</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>The Quit India Movement started by</t>
+          <t>The letter will be posted.</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>The Quit India Movement was started by</t>
+          <t>Let the letter be posted.</t>
         </is>
       </c>
       <c r="H85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>85</v>
+        <v>68</v>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>One should avoid honking the horn unnecessarily.</t>
+          <t>They are painting the walls.</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Unnecessary honking of horn ought to be</t>
+          <t>The walls are painting them.</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Unnecessary honking of horn can be avoided.</t>
+          <t>The walls are painted by them.</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Unnecessary honking of horn should be</t>
+          <t>The walls are being painted by them.</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Unnecessary honking of horn must be</t>
+          <t>The walls in painted by them.</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Unnecessary honking of horn should be</t>
-        </is>
-      </c>
-      <c r="H86" t="inlineStr"/>
+          <t>The walls are being painted by them.</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>The object "the walls" becomes the subject, and "are painting" changes to "are being painted.</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>86</v>
+        <v>44</v>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Gagan Narang and Vijay won bronze medals in</t>
+          <t>They have published all the details of the report</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Bronze medals won by Gagan Narang and</t>
+          <t>All the details of the report have been published by them</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Bronze medals had been won by Gagan</t>
+          <t>The publication of the details of invention</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Bronze medals were won by Gagan Narang</t>
+          <t>All the details have been invented by the</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Bronze medals have been won by Gagan</t>
+          <t>All the inventions have been detailed by</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Bronze medals were won by Gagan Narang</t>
-        </is>
-      </c>
-      <c r="H87" t="inlineStr"/>
+          <t>All the details of the report have been published by them</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>The object "all the details of the report" becomes the subject, and "have published" changes to "have been published."</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>87</v>
+        <v>4</v>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>The modern means of communication have made</t>
+          <t>Somebody has stolen his book.</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Life had been made so much easier by the</t>
+          <t>His book was stolen.</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Life is being so much easier by the modern</t>
+          <t>His book was stolen by somebody.</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Life has been made so much easier by the</t>
+          <t>His book has been stolen.</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Life was made so much easier by the modern</t>
+          <t>His book had been stolen by somebody.</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Life has been made so much easier by the</t>
-        </is>
-      </c>
-      <c r="H88" t="inlineStr"/>
+          <t>His book has been stolen.</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>The object "his book" becomes the subject, and the verb changes to "has been stolen."</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>88</v>
+        <v>117</v>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Thick clouds have overcast the sky.</t>
+          <t>He handed her a chair.</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>The sky has been overcast by thick clouds.</t>
+          <t>She was handed a chair by him.</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>The sky overcast by thick clouds.</t>
+          <t>He handed a chair to her.</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>The sky is overcast by thick clouds.</t>
+          <t>He will hand a chair to her.</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>The sky is being overcast by thick clouds.</t>
+          <t>A chair will be handed to her by him</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>The sky has been overcast by thick clouds.</t>
+          <t>She was handed a chair by him.</t>
         </is>
       </c>
       <c r="H89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>89</v>
+        <v>50</v>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>One should not give unsolicited advice.</t>
+          <t>We must take care of all living species on Earth.</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Unsolicited advice is not to be given.</t>
+          <t>All living species on Earth are taken care of</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Unsolicited advice can’t be given.</t>
+          <t>All living species on Earth must be taken care of by us</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Unsolicited advice may not be given.</t>
+          <t>All living species on Earth had been taken</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Unsolicited advice should not be given.</t>
+          <t>All living species on Earth will be taken care</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Unsolicited advice should not be given.</t>
-        </is>
-      </c>
-      <c r="H90" t="inlineStr"/>
+          <t>All living species on Earth must be taken care of by us</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>The object "all living species on Earth" becomes the subject, and "must take care of" changes to "must be taken care of</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>90</v>
+        <v>15</v>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>The scheme permits investors to buy the shares</t>
+          <t>We have decided to open a new branch</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Under the scheme the investors may be</t>
+          <t>To open a new branch was decided by us.</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Under the scheme the investors have been</t>
+          <t>To be opened a new branch has been decided.</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Under the scheme the investors are permitted</t>
+          <t>It has been decided to open a new branch.</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Under the scheme the investors were</t>
+          <t>It may be decided to open a new branch by</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Under the scheme the investors are permitted</t>
-        </is>
-      </c>
-      <c r="H91" t="inlineStr"/>
+          <t>It has been decided to open a new branch.</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>The object "a new branch" becomes the subject, and "have decided" changes to "has been decided to be open."</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>91</v>
+        <v>51</v>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>They were pulling down the old building.</t>
+          <t>They are considering your proposal,</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>The old building has been pulled down.</t>
+          <t>Your proposal is being considered by them.</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>The old building is being pulled down.</t>
+          <t>You proposal was being considered by them.</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>The old building was being pulled down.</t>
+          <t>Your proposal was considered by them.</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>The old building was pulled down.</t>
+          <t>Your proposal is considered by them.</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>The old building was being pulled down.</t>
-        </is>
-      </c>
-      <c r="H92" t="inlineStr"/>
+          <t>Your proposal is being considered by them.</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>The object "your proposal" becomes the subject, and "are considering" changes to "is being considered.</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>92</v>
+        <v>101</v>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Where did you buy this pen ?</t>
+          <t>I was given a watch by my father.</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Where shall you buy this pen ?</t>
+          <t>My father gives me a watch.</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Where is this pen bought by you ?</t>
+          <t>My father has given me a watch.</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Where was this pen bought ?</t>
+          <t>My father had given me a watch.</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Where will you buy this pen ?</t>
+          <t>My father gave me a watch.</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Where was this pen bought ?</t>
+          <t>My father gave me a watch.</t>
         </is>
       </c>
       <c r="H93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>93</v>
+        <v>49</v>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>He abandoned his medical studies.</t>
+          <t>It is impossible to do this.</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>His medical studies had abandoned.</t>
+          <t>Doing this is impossible.</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>His medical studies are abandoned.</t>
+          <t>This is impossible to be done</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>His medical studies have been abandoned.</t>
+          <t>This must not be done</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>His medical studies were abandoned.</t>
+          <t>This can’t be done</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>His medical studies were abandoned.</t>
+          <t>This is impossible to be done</t>
         </is>
       </c>
       <c r="H94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>94</v>
+        <v>130</v>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>One should keep one’s promises.</t>
+          <t>Sameer shut the door with a bang.</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Promises should be kept.</t>
+          <t>The door was shut with a bang by Sameer.</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>One’s promises should be kept.</t>
+          <t>The door with a bang shut by Sameer.</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Keep the promises made by you.</t>
+          <t>The door shut Sameer with a bang.</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Promises be kept.</t>
+          <t>The door had been shut with a bang by</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>One’s promises should be kept.</t>
+          <t>The door was shut with a bang by Sameer.</t>
         </is>
       </c>
       <c r="H95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>The thief was caught.</t>
+          <t>Thick clouds have overcast the sky.</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>The policeman may have caught the thief.</t>
+          <t>The sky has been overcast by thick clouds.</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>The policeman caught the thief.</t>
+          <t>The sky overcast by thick clouds.</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>The policeman has caught the thief.</t>
+          <t>The sky is overcast by thick clouds.</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>The policeman had caught the thief.</t>
+          <t>The sky is being overcast by thick clouds.</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>The policeman caught the thief.</t>
+          <t>The sky has been overcast by thick clouds.</t>
         </is>
       </c>
       <c r="H96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>96</v>
+        <v>5</v>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>One should not question his integrity.</t>
+          <t>We will telecast the programme next Sunday at 4</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>His integrity should not be questioned by</t>
+          <t>The programme will be telecast by us next sunday at 4pm</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>His integrity should not be questioned.</t>
+          <t>The programme would be telecast by us next</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>How can his integrity be questioned ?</t>
+          <t>The programme will be telecasted by us next</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Who can doubt his integrity ?</t>
+          <t>The programme would be telecasted by us</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>His integrity should not be questioned.</t>
-        </is>
-      </c>
-      <c r="H97" t="inlineStr"/>
+          <t>The programme will be telecast by us next sunday at 4pm</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>The object "the programme" becomes the subject, and the verb changes to "will be telecast."</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>97</v>
+        <v>72</v>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>I have been sent here by the editor of Tribune.</t>
+          <t>My watch can’t be repaired by anyone.</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>The editor of Tribune has send me here.</t>
+          <t>No one will repair my watch.</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>The editor of Tribune sent me here.</t>
+          <t>No one can repair my watch.</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>The editor of Tribune has sent me here.</t>
+          <t>No one can’t repair my watch.</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>The editor of Tribune send me here.</t>
+          <t>No one will be able to repair my watch.</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>The editor of Tribune has sent me here.</t>
+          <t>No one can repair my watch.</t>
         </is>
       </c>
       <c r="H98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>98</v>
+        <v>47</v>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Cigarettes cannot be sold here.</t>
+          <t>Prepare yourself for the worst.</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Nobody sold cigarettes here.</t>
+          <t>You be prepared for the worst.</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Nobody could sell cigarettes here.</t>
+          <t>The worst should be prepared by yourself.</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Nobody can sell cigarettes here.</t>
+          <t>Let yourself be prepared for the worst.</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Anybody can’t sell cigarettes here.</t>
+          <t>For the worst, preparation should be made</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Nobody can sell cigarettes here.</t>
-        </is>
-      </c>
-      <c r="H99" t="inlineStr"/>
+          <t>Let yourself be prepared for the worst.</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>Imperative sentences use "let" in passive voice</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>99</v>
+        <v>113</v>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>A big variety store was inaugurated by Sachin.</t>
+          <t>Newton wrote this letter yesterday.</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Sachin inaugurated a big variety store.</t>
+          <t>Yesterday was written letter by Newton.</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Sachin had inaugurated a big variety store.</t>
+          <t>This letter is written by Newton yesterday.</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Sachin has inaugurated a big variety store.</t>
+          <t>This letter was written by Newton yesterday.</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Sachin inaugurate a big variety store.</t>
+          <t>This letter was wrote by Newton yesterday.</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Sachin inaugurated a big variety store.</t>
+          <t>This letter was written by Newton yesterday.</t>
         </is>
       </c>
       <c r="H100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>100</v>
+        <v>129</v>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>When did he finish this work?</t>
+          <t>Do not insult him.</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>When this work was finished by him?</t>
+          <t>Let he not be insulted.</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>When was this work finished by him?</t>
+          <t>Let him not be insulted.</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>When will this work be finished by him?</t>
+          <t>Let not he be insulted.</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>When he finished this work?</t>
+          <t>Let not him be insulted.</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>When was this work finished by him?</t>
+          <t>Let him not be insulted.</t>
         </is>
       </c>
       <c r="H101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>101</v>
+        <v>16</v>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>I was given a watch by my father.</t>
+          <t>The loan will be sanctioned by the bank.</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>My father gives me a watch.</t>
+          <t>The bank sanctioned the loan.</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>My father has given me a watch.</t>
+          <t>The bank is going to sanction the loan.</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>My father had given me a watch.</t>
+          <t>The bank would sanction the loan.</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>My father gave me a watch.</t>
+          <t>The bank will sanction the loan.</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>My father gave me a watch.</t>
-        </is>
-      </c>
-      <c r="H102" t="inlineStr"/>
+          <t>The bank will sanction the loan.</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>The subject "the bank" performs the action, and "will be sanctioned" changes to "will sanction."</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>102</v>
+        <v>18</v>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Who helps you in your daily chores?</t>
+          <t>The traitors should be shot dead.</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>By who are you helped in your daily chores?</t>
+          <t>They should have shot the traitors dead.</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>By whom are you helped in your daily</t>
+          <t>They shall shoot the traitors dead.</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>By who you are helped in your daily chores?</t>
+          <t>They should shoot the traitors dead.</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>By whom you were helped in your daily</t>
+          <t>They shot the traitors dead.</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>By whom are you helped in your daily</t>
-        </is>
-      </c>
-      <c r="H103" t="inlineStr"/>
+          <t>They should shoot the traitors dead.</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>The subject "someone" performs the action, and "should be shot" changes to "should shoot."</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>103</v>
+        <v>58</v>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Jane Austen devoted her whole life to her</t>
+          <t>All the letters were posted by them.</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Jane Austen’s whole life is devoted to her</t>
+          <t>They have posted all the letters.</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Jane Austen’s whole life had been devoted</t>
+          <t>They had posted all the letters.</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Jane Austen’s whole life was devoted to her</t>
+          <t>They were posting all the letters.</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Jane Austen’s whole life has devoted to her</t>
+          <t>They posted all the letters.</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Jane Austen’s whole life was devoted to her</t>
-        </is>
-      </c>
-      <c r="H104" t="inlineStr"/>
+          <t>They posted all the letters.</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>The subject "they" performs the action, and "were posted" changes to "posted."</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>104</v>
+        <v>48</v>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Hamlet was written by Shakespeare.</t>
+          <t>Please shut the door and go to sleep.</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Shakespeare has written Hamlet.</t>
+          <t>The door is to be shut and you are to go to sleep</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Shakespeare had written Hamlet.</t>
+          <t>Let the door be shut and you be asleep</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Shakespeare wrote Hamlet.</t>
+          <t>You are requested to shut the door and go to sleep</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Shakespeare writes Hamlet.</t>
+          <t>The door is to be shut and you are requested</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Shakespeare wrote Hamlet.</t>
+          <t>You are requested to shut the door and go to sleep</t>
         </is>
       </c>
       <c r="H105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>105</v>
+        <v>93</v>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>They are looking after the child jointly.</t>
+          <t>He abandoned his medical studies.</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>The child is being looked after by them</t>
+          <t>His medical studies had abandoned.</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>The child is looked after by them jointly</t>
+          <t>His medical studies are abandoned.</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>The child was being looked after by them</t>
+          <t>His medical studies have been abandoned.</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>The child had been looked after by them</t>
+          <t>His medical studies were abandoned.</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>The child is being looked after by them</t>
+          <t>His medical studies were abandoned.</t>
         </is>
       </c>
       <c r="H106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>106</v>
+        <v>35</v>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>How many languages are spoken in India?</t>
+          <t>They drew a circle in the morning.</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>How many languages Indians are speaking</t>
+          <t>A circle was being drawn by them in the</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>How many languages Indians speak?</t>
+          <t>A circle was drawn by them in the morning.</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>How many languages do Indians speak?</t>
+          <t>In the morning a circle have been drawn by</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>How many languages did Indians speak?</t>
+          <t>A circle has been drawing since morning.</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>How many languages do Indians speak?</t>
-        </is>
-      </c>
-      <c r="H107" t="inlineStr"/>
+          <t>A circle was drawn by them in the morning.</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>The object "a circle" becomes the subject, and "drew" changes to "was drawn."</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>107</v>
+        <v>125</v>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Everyone admires our principal.</t>
+          <t>The problem has been treated by numerous</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Our principal has been admired by everyone.</t>
+          <t>Numerous experts have been treating the</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Our principal was admired by everyone.</t>
+          <t>Numerous experts have treated the problem.</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Our principal is being admired by everyone.</t>
+          <t>Numerous experts had been treating the</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Our principal is admired by everyone.</t>
+          <t>Numerous experts treated the problem.</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Our principal is admired by everyone.</t>
+          <t>Numerous experts have treated the problem.</t>
         </is>
       </c>
       <c r="H108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>108</v>
+        <v>43</v>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>The Manager granted me two days leave.</t>
+          <t>The government has not approved the new drug</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>I had been granted two days’ leave by the</t>
+          <t>The government approval for the sale of the</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>I have been granted two days’ leave by the</t>
+          <t>The new drug has not been approved by the government</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>I granted two days’ leave by the Manager.</t>
+          <t>For the sale of the new drug we have not</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>I was granted two days’ leave by the</t>
+          <t>The new drug was not approved by the</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>I was granted two days’ leave by the</t>
-        </is>
-      </c>
-      <c r="H109" t="inlineStr"/>
+          <t>The new drug has not been approved by the government</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>The object "the new drug" becomes the subject, and "has not approved" changes to "has not been approved."</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>109</v>
+        <v>98</v>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>They should shoot the terrorists dead.</t>
+          <t>Cigarettes cannot be sold here.</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>The terrorists been shot dead by them.</t>
+          <t>Nobody sold cigarettes here.</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>The terrorists should have been shot dead</t>
+          <t>Nobody could sell cigarettes here.</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>The terrorists should be shot dead by them.</t>
+          <t>Nobody can sell cigarettes here.</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>The terrorists have been shot dead by them.</t>
+          <t>Anybody can’t sell cigarettes here.</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>The terrorists should be shot dead by them.</t>
+          <t>Nobody can sell cigarettes here.</t>
         </is>
       </c>
       <c r="H110" t="inlineStr"/>
@@ -4698,723 +4658,763 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>111</v>
+        <v>77</v>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>The whole village was ravaged by the man-eater.</t>
+          <t>They created such a fuss over a trivial matter.</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>The man-eater ravages the whole village.</t>
+          <t>Such a fuss is being created over a trivial</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>The whole village is ravaged by the maneater.</t>
+          <t>Such a fuss was created over a trivial matter.</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>The man-eater ravaged the whole village.</t>
+          <t>Such a fuss has been created over a trivial</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>The whole village is being ravaged by the</t>
+          <t>By them such a fuss has been created over a</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>The man-eater ravaged the whole village.</t>
+          <t>Such a fuss was created over a trivial matter.</t>
         </is>
       </c>
       <c r="H112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>112</v>
+        <v>57</v>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>The purity of justice is maintained by the reports</t>
+          <t>The Metro Rail is being constructed by the corporation</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>The law courts maintain purity of justice in</t>
+          <t>The Corporation has been constructing the metro rail</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>The reports of the proceedings of the law</t>
+          <t>The Corporation is constructing the Metro rail</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Pure justice is maintained in the proceedings</t>
+          <t>The Corporation has constructed the Metro rail</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>The maintenance of justice is pure in the</t>
+          <t>The Corporation was constructing the Metro rail</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>The reports of the proceedings of the law</t>
-        </is>
-      </c>
-      <c r="H113" t="inlineStr"/>
+          <t>The Corporation is constructing the Metro rail</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>The subject "the corporation" becomes active, and "is being constructed" changes to "is constructing."</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>113</v>
+        <v>38</v>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Newton wrote this letter yesterday.</t>
+          <t>We must respect the elders.</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Yesterday was written letter by Newton.</t>
+          <t>The elders deserve respect from us.</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>This letter is written by Newton yesterday.</t>
+          <t>The elders must be respected.</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>This letter was written by Newton yesterday.</t>
+          <t>The elders must be respected by us.</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>This letter was wrote by Newton yesterday.</t>
+          <t>Respect the elders we must.</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>This letter was written by Newton yesterday.</t>
-        </is>
-      </c>
-      <c r="H114" t="inlineStr"/>
+          <t>The elders must be respected by us.</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>The object "the elders" becomes the subject, and "must respect" changes to "must be respected."</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>114</v>
+        <v>73</v>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>An awareness is being created among the people</t>
+          <t>Rosemary was moved to tears at the sight of the</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>The Government is creating an awareness</t>
+          <t>The sight of the miserable beggar moved</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>The Government are creating an awareness</t>
+          <t>The sight of the miserable beggar has moved</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>The Government creates an awareness</t>
+          <t>The sight of the miserable beggar moves</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>The Government created an awareness</t>
+          <t>The sight of the miserable beggar had moved</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>The Government is creating an awareness</t>
+          <t>The sight of the miserable beggar moved</t>
         </is>
       </c>
       <c r="H115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>115</v>
+        <v>29</v>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Ads on TV increase the sale of any commodity.</t>
+          <t>Circumstances forced him to resign his post.</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>The sale of any commodity is being increased</t>
+          <t>Circumstances make him to resign his post.</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>The sale of any commodity are increased by</t>
+          <t>He was forced to resign his post by circumstances</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>The sale of any commodity are being</t>
+          <t>He is forced to resign his post.</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>The sale of any commodity is increased by</t>
+          <t>He is forced and resigned his post.</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>The sale of any commodity is increased by</t>
-        </is>
-      </c>
-      <c r="H116" t="inlineStr"/>
+          <t>He was forced to resign his post by circumstances</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>The object "him" becomes the subject, and "forced" changes to "was forced."</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>116</v>
+        <v>69</v>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>The Indian Government is encouraging the</t>
+          <t>The box was dropped by the boy.</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>The Europeans are encouraged by the Indian</t>
+          <t>The boy dropped the box.</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>The Europeans are encouraging by the Indian</t>
+          <t>The boy drops the box.</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>The Europeans are being encouraged by the</t>
+          <t>The boy has dropped the box.</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>The Europeans is being encouraged by the</t>
+          <t>The boy is dropping the box.</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>The Europeans are being encouraged by the</t>
-        </is>
-      </c>
-      <c r="H117" t="inlineStr"/>
+          <t>The boy dropped the box.</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>The subject "the boy" becomes active, and "was dropped" changes to "dropped."</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>117</v>
+        <v>14</v>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>He handed her a chair.</t>
+          <t>The most useful training of my career was given to me by my boss</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>She was handed a chair by him.</t>
+          <t>My boss has been giving me the most useful</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>He handed a chair to her.</t>
+          <t>My boss gives me the most useful training.</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>He will hand a chair to her.</t>
+          <t>My boss is giving me the most usefully</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>A chair will be handed to her by him</t>
+          <t>My boss gave me the most useful training of my career</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>She was handed a chair by him.</t>
-        </is>
-      </c>
-      <c r="H118" t="inlineStr"/>
+          <t>My boss gave me the most useful training of my career</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>The subject "the mentor" becomes active, and "was given" changes to "gave."</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Call the police at once</t>
+          <t>The whole village was ravaged by the man-eater.</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Let the police be called at once.</t>
+          <t>The man-eater ravages the whole village.</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>The police was to be called at once.</t>
+          <t>The whole village is ravaged by the maneater.</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>The police is to be called at once.</t>
+          <t>The man-eater ravaged the whole village.</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Let the police called at once.</t>
+          <t>The whole village is being ravaged by the</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Let the police be called at once.</t>
+          <t>The man-eater ravaged the whole village.</t>
         </is>
       </c>
       <c r="H119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Post the letter.</t>
+          <t>Nobody has answered my question.</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>The letter is posted.</t>
+          <t>My question has been answered by</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>The letter was posted.</t>
+          <t>My question has not been answered by</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Let the letter be posted.</t>
+          <t>My question was not answered.</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>The letter will be posted.</t>
+          <t>My question remains unanswered.</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Let the letter be posted.</t>
+          <t>My question has not been answered by</t>
         </is>
       </c>
       <c r="H120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Who painted it?</t>
+          <t>When did he finish this work?</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>It was painted?</t>
+          <t>When this work was finished by him?</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Was it painted?</t>
+          <t>When was this work finished by him?</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Had it been painted by?</t>
+          <t>When will this work be finished by him?</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>By whom was it painted?</t>
+          <t>When he finished this work?</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>By whom was it painted?</t>
+          <t>When was this work finished by him?</t>
         </is>
       </c>
       <c r="H121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>121</v>
+        <v>6</v>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Nobody has answered my question.</t>
+          <t>Open the door.</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>My question has been answered by</t>
+          <t>Let the door should open.</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>My question has not been answered by</t>
+          <t>Let the door is opened.</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>My question was not answered.</t>
+          <t>Let open the door.</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>My question remains unanswered.</t>
+          <t>Let the door be opened.</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>My question has not been answered by</t>
-        </is>
-      </c>
-      <c r="H122" t="inlineStr"/>
+          <t>Let the door be opened.</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>In imperative sentences, "let" is used to form the passive voice.</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>122</v>
+        <v>78</v>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>The judge delivered the sentence at the courtroom</t>
+          <t>The lightning caused a serious forest fire and</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>The sentence been delivered yesterday by the</t>
+          <t>A serious forest fire has been caused by</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>The sentence was delivered by the judge at</t>
+          <t>A serious forest fire has been caused by lightning</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>The sentence was being delivered at the</t>
+          <t>A serious forest fire had been caused by</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Yesterday, the sentence had been delivered</t>
+          <t>A serious forest fire was caused by lightning</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>The sentence was delivered by the judge at</t>
+          <t>A serious forest fire was caused by lightning</t>
         </is>
       </c>
       <c r="H123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Shut all the doors and windows in the night.</t>
+          <t>Call the police at once</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Let all the doors and windows be shut in the</t>
+          <t>Let the police be called at once.</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>All the doors and windows may be shut in</t>
+          <t>The police was to be called at once.</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Let all the doors and windows remain shut</t>
+          <t>The police is to be called at once.</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>All the doors and windows be shutted in</t>
+          <t>Let the police called at once.</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Let all the doors and windows be shut in the</t>
+          <t>Let the police be called at once.</t>
         </is>
       </c>
       <c r="H124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>124</v>
+        <v>76</v>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>People use computers for various purposes.</t>
+          <t>Who asked you to draft this letter ?</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Computers are being used by people for</t>
+          <t>By who you are asked to draft this letter.</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>Computers have been used by people for</t>
+          <t>By who have you been asked to draft this</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Computers are used by people for various</t>
+          <t>By whom were you asked to draft this letter</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Computers will be used by people for various</t>
+          <t>By whom you were asked to draft this letter.</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Computers are used by people for various</t>
+          <t>By whom were you asked to draft this letter</t>
         </is>
       </c>
       <c r="H125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>125</v>
+        <v>92</v>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>The problem has been treated by numerous</t>
+          <t>Where did you buy this pen ?</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Numerous experts have been treating the</t>
+          <t>Where shall you buy this pen ?</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>Numerous experts have treated the problem.</t>
+          <t>Where is this pen bought by you ?</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Numerous experts had been treating the</t>
+          <t>Where was this pen bought ?</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Numerous experts treated the problem.</t>
+          <t>Where will you buy this pen ?</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Numerous experts have treated the problem.</t>
+          <t>Where was this pen bought ?</t>
         </is>
       </c>
       <c r="H126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>126</v>
+        <v>26</v>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>She always cooks delicious food.</t>
+          <t>We found him a good wife.</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Delicious food is always cooked by her.</t>
+          <t>He was found a good wife by us.</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>Delicious food is always being cooked by</t>
+          <t>A good wife was found out by them.</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Delicious food has been cooked by her.</t>
+          <t>A good wife found him.</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Delicious food was being cooked by her.</t>
+          <t>A good wife was being found by us.</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Delicious food is always cooked by her.</t>
-        </is>
-      </c>
-      <c r="H127" t="inlineStr"/>
+          <t>He was found a good wife by us.</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>The object "him" becomes the subject, and "found" changes to "was found."</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>127</v>
+        <v>34</v>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Mother gave him a little puppy.</t>
+          <t>The boys were playing cricket.</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>He was given a little puppy by mother.</t>
+          <t>Cricket had been played by the boys.</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>A little puppy was being given to him by</t>
+          <t>Cricket has been played by the boys.</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>He had been given a little puppy by mother.</t>
+          <t>Cricket was played by the boys.</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>A little puppy is given to him by his mother.</t>
+          <t>Cricket was being played by the boys.</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>He was given a little puppy by mother.</t>
-        </is>
-      </c>
-      <c r="H128" t="inlineStr"/>
+          <t>Cricket was being played by the boys.</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>The object "cricket" becomes the subject, and "were playing" changes to "was being played.</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>128</v>
+        <v>89</v>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>The company paid her a meagre salary.</t>
+          <t>One should not give unsolicited advice.</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>She was paid a meagre salary by the</t>
+          <t>Unsolicited advice is not to be given.</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>A meagre salary has been paid to her by the</t>
+          <t>Unsolicited advice can’t be given.</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>She was being paid a meagre salary by the</t>
+          <t>Unsolicited advice may not be given.</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>A meagre salary was to be paid to her by the</t>
+          <t>Unsolicited advice should not be given.</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>She was paid a meagre salary by the</t>
+          <t>Unsolicited advice should not be given.</t>
         </is>
       </c>
       <c r="H129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>129</v>
+        <v>27</v>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Do not insult him.</t>
+          <t>You will be taken care of by me.</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Let he not be insulted.</t>
+          <t>I will be taking care of you.</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>Let him not be insulted.</t>
+          <t>I would take care of you.</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Let not he be insulted.</t>
+          <t>I will take care of you.</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Let not him be insulted.</t>
+          <t>I will being take care of you.</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Let him not be insulted.</t>
-        </is>
-      </c>
-      <c r="H130" t="inlineStr"/>
+          <t>I will take care of you.</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>The subject "you" becomes the object, and "will be taken care of" changes to "will take care of."</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>130</v>
+        <v>19</v>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Sameer shut the door with a bang.</t>
+          <t>Rahul is teaching the children in the slum areas.</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>The door was shut with a bang by Sameer.</t>
+          <t>The children in the slum areas are taught by</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>The door with a bang shut by Sameer.</t>
+          <t>The children are taught by Rahul in the slum</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>The door shut Sameer with a bang.</t>
+          <t>In the slum areas the children are learning</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>The door had been shut with a bang by</t>
+          <t>The children in the slum areas are being taught by Rahul</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>The door was shut with a bang by Sameer.</t>
-        </is>
-      </c>
-      <c r="H131" t="inlineStr"/>
+          <t>The children in the slum areas are being taught by Rahul</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>The object "the children in the slum areas" becomes the subject, and "is teaching" changes to "are being taught."</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Data/NDA_active_passive_voice1.xlsx
+++ b/Data/NDA_active_passive_voice1.xlsx
@@ -472,4946 +472,4946 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>1</v>
+        <v>57</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>They do not accept credit cards everywhere.</t>
+          <t>The Metro Rail is being constructed by the corporation</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Credit cards are not being accepted</t>
+          <t>The Corporation has been constructing the metro rail</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Credit cards were not accepted everywhere.</t>
+          <t>The Corporation is constructing the Metro rail</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Credit cards do not accept them everywhere.</t>
+          <t>The Corporation has constructed the Metro rail</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Credit cards are not accepted everywhere.</t>
+          <t>The Corporation was constructing the Metro rail</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Credit cards are not accepted everywhere.</t>
+          <t>The Corporation is constructing the Metro rail</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>"They" is the subject, and "credit cards" is the object. In passive voice, the object becomes the subject, and the verb changes to "are not accepted."</t>
+          <t>The subject "the corporation" becomes active, and "is being constructed" changes to "is constructing."</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>30</v>
+        <v>81</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>He would have written this essay in time.</t>
+          <t>She was advised 15 days’ rest after her surgery.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>The essay was written on time.</t>
+          <t>The doctor was advised her 15 days’ rest after</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>This essay would have been written by him in time</t>
+          <t>The doctor has advised her 15 days’ rest after</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>The essay was written by him in time.</t>
+          <t>The doctor advised her 15 days’ rest after</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>He wrote the essay on time.</t>
+          <t>The doctor had advised her 15 days’ rest after</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>This essay would have been written by him in time</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>The object "this essay" becomes the subject, and "would have written" changes to "would have been written."</t>
-        </is>
-      </c>
+          <t>The doctor advised her 15 days’ rest after</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>The boy laughed at the beggar.</t>
+          <t>The loan will be sanctioned by the bank.</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>The beggar was laughed by the boy.</t>
+          <t>The bank sanctioned the loan.</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>The beggar was being laughed by the boy.</t>
+          <t>The bank is going to sanction the loan.</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>The beggar was being laughed at by the boy.</t>
+          <t>The bank would sanction the loan.</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>The beggar was laughed at by the boy.</t>
+          <t>The bank will sanction the loan.</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>The beggar was laughed at by the boy.</t>
+          <t>The bank will sanction the loan.</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>The object "the beggar" becomes the subject, and "laughed at" changes to "was laughed at.</t>
+          <t>The subject "the bank" performs the action, and "will be sanctioned" changes to "will sanction."</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>94</v>
+        <v>45</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>One should keep one’s promises.</t>
+          <t>He teaches us grammar.</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Promises should be kept.</t>
+          <t>Grammar is taught to us by him</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>One’s promises should be kept.</t>
+          <t>We are taught grammar by him.</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Keep the promises made by you.</t>
+          <t>Grammar will be taught of us by him.</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Promises be kept.</t>
+          <t>We were teached grammar by him.</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>One’s promises should be kept.</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr"/>
+          <t>Grammar is taught to us by him</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>The object "grammar" becomes the subject, and "teaches" changes to "is taught."</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>20</v>
+        <v>130</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>One cannot expect children to understand these problems</t>
+          <t>Sameer shut the door with a bang.</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Children cannot be expected to understand</t>
+          <t>The door was shut with a bang by Sameer.</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Children to understand these problems</t>
+          <t>The door with a bang shut by Sameer.</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Children cannot be expected to understand these problems</t>
+          <t>The door shut Sameer with a bang.</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>To understand these problems cannot be</t>
+          <t>The door had been shut with a bang by</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Children cannot be expected to understand these problems</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>The object "children" becomes the subject, and "cannot expect" changes to "cannot be expected."</t>
-        </is>
-      </c>
+          <t>The door was shut with a bang by Sameer.</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130</v>
+        <v>20</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Sameer shut the door with a bang.</t>
+          <t>One cannot expect children to understand these problems</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>The door was shut with a bang by Sameer.</t>
+          <t>Children cannot be expected to understand</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>The door with a bang shut by Sameer.</t>
+          <t>Children to understand these problems</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>The door shut Sameer with a bang.</t>
+          <t>Children cannot be expected to understand these problems</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>The door had been shut with a bang by</t>
+          <t>To understand these problems cannot be</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>The door was shut with a bang by Sameer.</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr"/>
+          <t>Children cannot be expected to understand these problems</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>The object "children" becomes the subject, and "cannot expect" changes to "cannot be expected."</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>45</v>
+        <v>94</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>He teaches us grammar.</t>
+          <t>One should keep one’s promises.</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Grammar is taught to us by him</t>
+          <t>Promises should be kept.</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>We are taught grammar by him.</t>
+          <t>One’s promises should be kept.</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Grammar will be taught of us by him.</t>
+          <t>Keep the promises made by you.</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>We were teached grammar by him.</t>
+          <t>Promises be kept.</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Grammar is taught to us by him</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>The object "grammar" becomes the subject, and "teaches" changes to "is taught."</t>
-        </is>
-      </c>
+          <t>One’s promises should be kept.</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>The loan will be sanctioned by the bank.</t>
+          <t>The boy laughed at the beggar.</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>The bank sanctioned the loan.</t>
+          <t>The beggar was laughed by the boy.</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>The bank is going to sanction the loan.</t>
+          <t>The beggar was being laughed by the boy.</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>The bank would sanction the loan.</t>
+          <t>The beggar was being laughed at by the boy.</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>The bank will sanction the loan.</t>
+          <t>The beggar was laughed at by the boy.</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>The bank will sanction the loan.</t>
+          <t>The beggar was laughed at by the boy.</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>The subject "the bank" performs the action, and "will be sanctioned" changes to "will sanction."</t>
+          <t>The object "the beggar" becomes the subject, and "laughed at" changes to "was laughed at.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>81</v>
+        <v>30</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>She was advised 15 days’ rest after her surgery.</t>
+          <t>He would have written this essay in time.</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>The doctor was advised her 15 days’ rest after</t>
+          <t>The essay was written on time.</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>The doctor has advised her 15 days’ rest after</t>
+          <t>This essay would have been written by him in time</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>The doctor advised her 15 days’ rest after</t>
+          <t>The essay was written by him in time.</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>The doctor had advised her 15 days’ rest after</t>
+          <t>He wrote the essay on time.</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>The doctor advised her 15 days’ rest after</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr"/>
+          <t>This essay would have been written by him in time</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>The object "this essay" becomes the subject, and "would have written" changes to "would have been written."</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>57</v>
+        <v>1</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>The Metro Rail is being constructed by the corporation</t>
+          <t>They do not accept credit cards everywhere.</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>The Corporation has been constructing the metro rail</t>
+          <t>Credit cards are not being accepted</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>The Corporation is constructing the Metro rail</t>
+          <t>Credit cards were not accepted everywhere.</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>The Corporation has constructed the Metro rail</t>
+          <t>Credit cards do not accept them everywhere.</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>The Corporation was constructing the Metro rail</t>
+          <t>Credit cards are not accepted everywhere.</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>The Corporation is constructing the Metro rail</t>
+          <t>Credit cards are not accepted everywhere.</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>The subject "the corporation" becomes active, and "is being constructed" changes to "is constructing."</t>
+          <t>"They" is the subject, and "credit cards" is the object. In passive voice, the object becomes the subject, and the verb changes to "are not accepted."</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121</v>
+        <v>60</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Nobody has answered my question.</t>
+          <t>My books have been stolen.</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>My question has been answered by</t>
+          <t>Someone has stolen my books.</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>My question has not been answered by</t>
+          <t>Someone stole my books.</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>My question was not answered.</t>
+          <t>Someone have stolen my books.</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>My question remains unanswered.</t>
+          <t>They stole my books.</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>My question has not been answered by</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr"/>
+          <t>Someone has stolen my books.</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>The subject "someone" is added, and "have been stolen" changes to "has stolen."</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>93</v>
+        <v>55</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>He abandoned his medical studies.</t>
+          <t>Your little boy broke my kitchen window this</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>His medical studies had abandoned.</t>
+          <t>My kitchen window was broken by your little boy this morning.</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>His medical studies are abandoned.</t>
+          <t>My kitchen window had been broken by your</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>His medical studies have been abandoned.</t>
+          <t>My kitchen window is broken by you little</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>His medical studies were abandoned.</t>
+          <t>My kitchen window was being broken by</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>His medical studies were abandoned.</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr"/>
+          <t>My kitchen window was broken by your little boy this morning.</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>The object "my kitchen window" becomes the subject, and "broke" changes to "was broken."</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>112</v>
+        <v>100</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>The purity of justice is maintained by the reports</t>
+          <t>When did he finish this work?</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>The law courts maintain purity of justice in</t>
+          <t>When this work was finished by him?</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>The reports of the proceedings of the law</t>
+          <t>When was this work finished by him?</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Pure justice is maintained in the proceedings</t>
+          <t>When will this work be finished by him?</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>The maintenance of justice is pure in the</t>
+          <t>When he finished this work?</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>The reports of the proceedings of the law</t>
+          <t>When was this work finished by him?</t>
         </is>
       </c>
       <c r="H14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>89</v>
+        <v>68</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>One should not give unsolicited advice.</t>
+          <t>They are painting the walls.</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Unsolicited advice is not to be given.</t>
+          <t>The walls are painting them.</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Unsolicited advice can’t be given.</t>
+          <t>The walls are painted by them.</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Unsolicited advice may not be given.</t>
+          <t>The walls are being painted by them.</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Unsolicited advice should not be given.</t>
+          <t>The walls in painted by them.</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Unsolicited advice should not be given.</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr"/>
+          <t>The walls are being painted by them.</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>The object "the walls" becomes the subject, and "are painting" changes to "are being painted.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>115</v>
+        <v>96</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Ads on TV increase the sale of any commodity.</t>
+          <t>One should not question his integrity.</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>The sale of any commodity is being increased</t>
+          <t>His integrity should not be questioned by</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>The sale of any commodity are increased by</t>
+          <t>His integrity should not be questioned.</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>The sale of any commodity are being</t>
+          <t>How can his integrity be questioned ?</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>The sale of any commodity is increased by</t>
+          <t>Who can doubt his integrity ?</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>The sale of any commodity is increased by</t>
+          <t>His integrity should not be questioned.</t>
         </is>
       </c>
       <c r="H16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>96</v>
+        <v>115</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>One should not question his integrity.</t>
+          <t>Ads on TV increase the sale of any commodity.</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>His integrity should not be questioned by</t>
+          <t>The sale of any commodity is being increased</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>His integrity should not be questioned.</t>
+          <t>The sale of any commodity are increased by</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>How can his integrity be questioned ?</t>
+          <t>The sale of any commodity are being</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Who can doubt his integrity ?</t>
+          <t>The sale of any commodity is increased by</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>His integrity should not be questioned.</t>
+          <t>The sale of any commodity is increased by</t>
         </is>
       </c>
       <c r="H17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>68</v>
+        <v>89</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>They are painting the walls.</t>
+          <t>One should not give unsolicited advice.</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>The walls are painting them.</t>
+          <t>Unsolicited advice is not to be given.</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>The walls are painted by them.</t>
+          <t>Unsolicited advice can’t be given.</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>The walls are being painted by them.</t>
+          <t>Unsolicited advice may not be given.</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>The walls in painted by them.</t>
+          <t>Unsolicited advice should not be given.</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>The walls are being painted by them.</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>The object "the walls" becomes the subject, and "are painting" changes to "are being painted.</t>
-        </is>
-      </c>
+          <t>Unsolicited advice should not be given.</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>100</v>
+        <v>112</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>When did he finish this work?</t>
+          <t>The purity of justice is maintained by the reports</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>When this work was finished by him?</t>
+          <t>The law courts maintain purity of justice in</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>When was this work finished by him?</t>
+          <t>The reports of the proceedings of the law</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>When will this work be finished by him?</t>
+          <t>Pure justice is maintained in the proceedings</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>When he finished this work?</t>
+          <t>The maintenance of justice is pure in the</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>When was this work finished by him?</t>
+          <t>The reports of the proceedings of the law</t>
         </is>
       </c>
       <c r="H19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>55</v>
+        <v>93</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Your little boy broke my kitchen window this</t>
+          <t>He abandoned his medical studies.</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>My kitchen window was broken by your little boy this morning.</t>
+          <t>His medical studies had abandoned.</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>My kitchen window had been broken by your</t>
+          <t>His medical studies are abandoned.</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>My kitchen window is broken by you little</t>
+          <t>His medical studies have been abandoned.</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>My kitchen window was being broken by</t>
+          <t>His medical studies were abandoned.</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>My kitchen window was broken by your little boy this morning.</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>The object "my kitchen window" becomes the subject, and "broke" changes to "was broken."</t>
-        </is>
-      </c>
+          <t>His medical studies were abandoned.</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>60</v>
+        <v>121</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>My books have been stolen.</t>
+          <t>Nobody has answered my question.</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Someone has stolen my books.</t>
+          <t>My question has been answered by</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Someone stole my books.</t>
+          <t>My question has not been answered by</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Someone have stolen my books.</t>
+          <t>My question was not answered.</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>They stole my books.</t>
+          <t>My question remains unanswered.</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Someone has stolen my books.</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>The subject "someone" is added, and "have been stolen" changes to "has stolen."</t>
-        </is>
-      </c>
+          <t>My question has not been answered by</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>82</v>
+        <v>8</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>When did he return my books ?</t>
+          <t>The comic scenes in the play were overdone by the actor</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>When were my books returned by him ?</t>
+          <t>The actors overdid the comic scenes in the</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>When will my books be returned by him ?</t>
+          <t>The actors overacted the comic scenes in the play</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>When has he returned my books ?</t>
+          <t>The play was full of comic scenes.</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>When are my books returned by him ?</t>
+          <t>The actors comically performed the play.</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>When were my books returned by him ?</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr"/>
+          <t>The actors overacted the comic scenes in the play</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>The subject "the actors" becomes active, and "were overdone" changes to "overdid."</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>83</v>
+        <v>40</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>We had to stop all other work to complete our</t>
+          <t>Has anybody answered your question?</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>All other work has to be stopped by us to</t>
+          <t>Your question has been answered?</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>All other work has stopped by us to complete</t>
+          <t>Anybody has answered your question?</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>All other work had to be stopped by us to</t>
+          <t>Has your question been answered by anybody?</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>All other work was stopped by us to complete</t>
+          <t>Have your answered you question ?</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>All other work had to be stopped by us to</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr"/>
+          <t>Has your question been answered by anybody?</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>The object "your question" becomes the subject, and "has answered" changes to "has been answered."</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>51</v>
+        <v>27</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>They are considering your proposal,</t>
+          <t>You will be taken care of by me.</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Your proposal is being considered by them.</t>
+          <t>I will be taking care of you.</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>You proposal was being considered by them.</t>
+          <t>I would take care of you.</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Your proposal was considered by them.</t>
+          <t>I will take care of you.</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Your proposal is considered by them.</t>
+          <t>I will being take care of you.</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Your proposal is being considered by them.</t>
+          <t>I will take care of you.</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>The object "your proposal" becomes the subject, and "are considering" changes to "is being considered.</t>
+          <t>The subject "you" becomes the object, and "will be taken care of" changes to "will take care of."</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>52</v>
+        <v>118</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Two hundred people were arrested by the police.</t>
+          <t>Call the police at once</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>The police have arrested two hundred people.</t>
+          <t>Let the police be called at once.</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>The police arrested two hundred people.</t>
+          <t>The police was to be called at once.</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>The police had arrested two hundred people.</t>
+          <t>The police is to be called at once.</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>The police has arrested two hundred people.</t>
+          <t>Let the police called at once.</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>The police arrested two hundred people.</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>The subject "the police" becomes active, and "were arrested" changes to "arrested."</t>
-        </is>
-      </c>
+          <t>Let the police be called at once.</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Do not insult him.</t>
+          <t>People use computers for various purposes.</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Let he not be insulted.</t>
+          <t>Computers are being used by people for</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Let him not be insulted.</t>
+          <t>Computers have been used by people for</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Let not he be insulted.</t>
+          <t>Computers are used by people for various</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Let not him be insulted.</t>
+          <t>Computers will be used by people for various</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Let him not be insulted.</t>
+          <t>Computers are used by people for various</t>
         </is>
       </c>
       <c r="H26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>People use computers for various purposes.</t>
+          <t>Do not insult him.</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Computers are being used by people for</t>
+          <t>Let he not be insulted.</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Computers have been used by people for</t>
+          <t>Let him not be insulted.</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Computers are used by people for various</t>
+          <t>Let not he be insulted.</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Computers will be used by people for various</t>
+          <t>Let not him be insulted.</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Computers are used by people for various</t>
+          <t>Let him not be insulted.</t>
         </is>
       </c>
       <c r="H27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>118</v>
+        <v>52</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Call the police at once</t>
+          <t>Two hundred people were arrested by the police.</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Let the police be called at once.</t>
+          <t>The police have arrested two hundred people.</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>The police was to be called at once.</t>
+          <t>The police arrested two hundred people.</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>The police is to be called at once.</t>
+          <t>The police had arrested two hundred people.</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Let the police called at once.</t>
+          <t>The police has arrested two hundred people.</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Let the police be called at once.</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr"/>
+          <t>The police arrested two hundred people.</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>The subject "the police" becomes active, and "were arrested" changes to "arrested."</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>27</v>
+        <v>51</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>You will be taken care of by me.</t>
+          <t>They are considering your proposal,</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>I will be taking care of you.</t>
+          <t>Your proposal is being considered by them.</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>I would take care of you.</t>
+          <t>You proposal was being considered by them.</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>I will take care of you.</t>
+          <t>Your proposal was considered by them.</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>I will being take care of you.</t>
+          <t>Your proposal is considered by them.</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>I will take care of you.</t>
+          <t>Your proposal is being considered by them.</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>The subject "you" becomes the object, and "will be taken care of" changes to "will take care of."</t>
+          <t>The object "your proposal" becomes the subject, and "are considering" changes to "is being considered.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Has anybody answered your question?</t>
+          <t>We had to stop all other work to complete our</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Your question has been answered?</t>
+          <t>All other work has to be stopped by us to</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Anybody has answered your question?</t>
+          <t>All other work has stopped by us to complete</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Has your question been answered by anybody?</t>
+          <t>All other work had to be stopped by us to</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Have your answered you question ?</t>
+          <t>All other work was stopped by us to complete</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Has your question been answered by anybody?</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>The object "your question" becomes the subject, and "has answered" changes to "has been answered."</t>
-        </is>
-      </c>
+          <t>All other work had to be stopped by us to</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>8</v>
+        <v>82</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>The comic scenes in the play were overdone by the actor</t>
+          <t>When did he return my books ?</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>The actors overdid the comic scenes in the</t>
+          <t>When were my books returned by him ?</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>The actors overacted the comic scenes in the play</t>
+          <t>When will my books be returned by him ?</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>The play was full of comic scenes.</t>
+          <t>When has he returned my books ?</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>The actors comically performed the play.</t>
+          <t>When are my books returned by him ?</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>The actors overacted the comic scenes in the play</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>The subject "the actors" becomes active, and "were overdone" changes to "overdid."</t>
-        </is>
-      </c>
+          <t>When were my books returned by him ?</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>We have warned you.</t>
+          <t>One must keep one’s promises.</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>You have been warned by us</t>
+          <t>One’s promises are kept</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>We have you warned.</t>
+          <t>One’s promises must kept</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Warned you have been.</t>
+          <t>One’s promises were kept</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Have you been warned.</t>
+          <t>One’s promises must be kept</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>You have been warned by us</t>
+          <t>One’s promises must be kept</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>The object "you" becomes the subject, and "have warned" changes to "have been warned.</t>
+          <t>The object "promises" becomes the subject, and "must keep" changes to "must be kept."</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>102</v>
+        <v>43</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Who helps you in your daily chores?</t>
+          <t>The government has not approved the new drug</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>By who are you helped in your daily chores?</t>
+          <t>The government approval for the sale of the</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>By whom are you helped in your daily</t>
+          <t>The new drug has not been approved by the government</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>By who you are helped in your daily chores?</t>
+          <t>For the sale of the new drug we have not</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>By whom you were helped in your daily</t>
+          <t>The new drug was not approved by the</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>By whom are you helped in your daily</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr"/>
+          <t>The new drug has not been approved by the government</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>The object "the new drug" becomes the subject, and "has not approved" changes to "has not been approved."</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>101</v>
+        <v>14</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>I was given a watch by my father.</t>
+          <t>The most useful training of my career was given to me by my boss</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>My father gives me a watch.</t>
+          <t>My boss has been giving me the most useful</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>My father has given me a watch.</t>
+          <t>My boss gives me the most useful training.</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>My father had given me a watch.</t>
+          <t>My boss is giving me the most usefully</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>My father gave me a watch.</t>
+          <t>My boss gave me the most useful training of my career</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>My father gave me a watch.</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr"/>
+          <t>My boss gave me the most useful training of my career</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>The subject "the mentor" becomes active, and "was given" changes to "gave."</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>114</v>
+        <v>105</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>An awareness is being created among the people</t>
+          <t>They are looking after the child jointly.</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>The Government is creating an awareness</t>
+          <t>The child is being looked after by them</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>The Government are creating an awareness</t>
+          <t>The child is looked after by them jointly</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>The Government creates an awareness</t>
+          <t>The child was being looked after by them</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>The Government created an awareness</t>
+          <t>The child had been looked after by them</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>The Government is creating an awareness</t>
+          <t>The child is being looked after by them</t>
         </is>
       </c>
       <c r="H35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>49</v>
+        <v>103</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>It is impossible to do this.</t>
+          <t>Jane Austen devoted her whole life to her</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Doing this is impossible.</t>
+          <t>Jane Austen’s whole life is devoted to her</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>This is impossible to be done</t>
+          <t>Jane Austen’s whole life had been devoted</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>This must not be done</t>
+          <t>Jane Austen’s whole life was devoted to her</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>This can’t be done</t>
+          <t>Jane Austen’s whole life has devoted to her</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>This is impossible to be done</t>
+          <t>Jane Austen’s whole life was devoted to her</t>
         </is>
       </c>
       <c r="H36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>103</v>
+        <v>49</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Jane Austen devoted her whole life to her</t>
+          <t>It is impossible to do this.</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Jane Austen’s whole life is devoted to her</t>
+          <t>Doing this is impossible.</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Jane Austen’s whole life had been devoted</t>
+          <t>This is impossible to be done</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Jane Austen’s whole life was devoted to her</t>
+          <t>This must not be done</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Jane Austen’s whole life has devoted to her</t>
+          <t>This can’t be done</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Jane Austen’s whole life was devoted to her</t>
+          <t>This is impossible to be done</t>
         </is>
       </c>
       <c r="H37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>105</v>
+        <v>114</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>They are looking after the child jointly.</t>
+          <t>An awareness is being created among the people</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>The child is being looked after by them</t>
+          <t>The Government is creating an awareness</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>The child is looked after by them jointly</t>
+          <t>The Government are creating an awareness</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>The child was being looked after by them</t>
+          <t>The Government creates an awareness</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>The child had been looked after by them</t>
+          <t>The Government created an awareness</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>The child is being looked after by them</t>
+          <t>The Government is creating an awareness</t>
         </is>
       </c>
       <c r="H38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>14</v>
+        <v>101</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>The most useful training of my career was given to me by my boss</t>
+          <t>I was given a watch by my father.</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>My boss has been giving me the most useful</t>
+          <t>My father gives me a watch.</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>My boss gives me the most useful training.</t>
+          <t>My father has given me a watch.</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>My boss is giving me the most usefully</t>
+          <t>My father had given me a watch.</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>My boss gave me the most useful training of my career</t>
+          <t>My father gave me a watch.</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>My boss gave me the most useful training of my career</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>The subject "the mentor" becomes active, and "was given" changes to "gave."</t>
-        </is>
-      </c>
+          <t>My father gave me a watch.</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>43</v>
+        <v>102</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>The government has not approved the new drug</t>
+          <t>Who helps you in your daily chores?</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>The government approval for the sale of the</t>
+          <t>By who are you helped in your daily chores?</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>The new drug has not been approved by the government</t>
+          <t>By whom are you helped in your daily</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>For the sale of the new drug we have not</t>
+          <t>By who you are helped in your daily chores?</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>The new drug was not approved by the</t>
+          <t>By whom you were helped in your daily</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>The new drug has not been approved by the government</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>The object "the new drug" becomes the subject, and "has not approved" changes to "has not been approved."</t>
-        </is>
-      </c>
+          <t>By whom are you helped in your daily</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>One must keep one’s promises.</t>
+          <t>We have warned you.</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>One’s promises are kept</t>
+          <t>You have been warned by us</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>One’s promises must kept</t>
+          <t>We have you warned.</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>One’s promises were kept</t>
+          <t>Warned you have been.</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>One’s promises must be kept</t>
+          <t>Have you been warned.</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>One’s promises must be kept</t>
+          <t>You have been warned by us</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>The object "promises" becomes the subject, and "must keep" changes to "must be kept."</t>
+          <t>The object "you" becomes the subject, and "have warned" changes to "have been warned.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>78</v>
+        <v>66</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>The lightning caused a serious forest fire and</t>
+          <t>The news surprised me.</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>A serious forest fire has been caused by</t>
+          <t>I am surprised by the news.</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>A serious forest fire has been caused by lightning</t>
+          <t>I was surprised by the news.</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>A serious forest fire had been caused by</t>
+          <t>The news was surprised by me.</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>A serious forest fire was caused by lightning</t>
+          <t>The news was a big surprise.</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>A serious forest fire was caused by lightning</t>
-        </is>
-      </c>
-      <c r="H42" t="inlineStr"/>
+          <t>I was surprised by the news.</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>The object "me" becomes the subject, and "surprised" changes to "was surprised."</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>They drew a circle in the morning.</t>
+          <t>The burglar destroyed several items in the room.</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>A circle was being drawn by them in the</t>
+          <t>Several items destroyed in the room by the</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>A circle was drawn by them in the morning.</t>
+          <t>Several items in the room were destroyed by the burglar</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>In the morning a circle have been drawn by</t>
+          <t>Including the carpet, several items in the</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>A circle has been drawing since morning.</t>
+          <t>The burglar, being destroyed several items</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>A circle was drawn by them in the morning.</t>
+          <t>Several items in the room were destroyed by the burglar</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>The object "a circle" becomes the subject, and "drew" changes to "was drawn."</t>
+          <t>The object "several items in the room" becomes the subject, and "destroyed" changes to "were destroyed."</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>2</v>
+        <v>67</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>The police caught the thief at last.</t>
+          <t>I will have completed the task by tomorrow.</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>At last the thief was caught by the police</t>
+          <t>The task will be completed by me by</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>The thief at last caught the police.</t>
+          <t>By tomorrow the task will have been completed</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>The thief was at last caught by the police.</t>
+          <t>The task would be completed by me by tomorrow</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>At last the thief by the police was caught.</t>
+          <t>By tomorrow the task would have been  completed</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>At last the thief was caught by the police</t>
+          <t>By tomorrow the task will have been completed</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>"The police" is the subject, and "the thief" is the object. The verb "caught" changes to "was caught" in the passive form.</t>
+          <t>The object "the task" becomes the subject, and "will have completed" changes to "will have been completed</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>48</v>
+        <v>21</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Please shut the door and go to sleep.</t>
+          <t>Why did she break the garden wall?</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>The door is to be shut and you are to go to sleep</t>
+          <t>Why the garden wall was broken by her?</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Let the door be shut and you be asleep</t>
+          <t>Why had the garden wall been broken by</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>You are requested to shut the door and go to sleep</t>
+          <t>Why was the garden wall broken by her?</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>The door is to be shut and you are requested</t>
+          <t>Why will the garden wall be broken by her?</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>You are requested to shut the door and go to sleep</t>
-        </is>
-      </c>
-      <c r="H45" t="inlineStr"/>
+          <t>Why was the garden wall broken by her?</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>The object "the garden wall" becomes the subject, and "did break" changes to "was broken."</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>91</v>
+        <v>47</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>They were pulling down the old building.</t>
+          <t>Prepare yourself for the worst.</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>The old building has been pulled down.</t>
+          <t>You be prepared for the worst.</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>The old building is being pulled down.</t>
+          <t>The worst should be prepared by yourself.</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>The old building was being pulled down.</t>
+          <t>Let yourself be prepared for the worst.</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>The old building was pulled down.</t>
+          <t>For the worst, preparation should be made</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>The old building was being pulled down.</t>
-        </is>
-      </c>
-      <c r="H46" t="inlineStr"/>
+          <t>Let yourself be prepared for the worst.</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Imperative sentences use "let" in passive voice</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>47</v>
+        <v>91</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Prepare yourself for the worst.</t>
+          <t>They were pulling down the old building.</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>You be prepared for the worst.</t>
+          <t>The old building has been pulled down.</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>The worst should be prepared by yourself.</t>
+          <t>The old building is being pulled down.</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Let yourself be prepared for the worst.</t>
+          <t>The old building was being pulled down.</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>For the worst, preparation should be made</t>
+          <t>The old building was pulled down.</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Let yourself be prepared for the worst.</t>
-        </is>
-      </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>Imperative sentences use "let" in passive voice</t>
-        </is>
-      </c>
+          <t>The old building was being pulled down.</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>21</v>
+        <v>48</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Why did she break the garden wall?</t>
+          <t>Please shut the door and go to sleep.</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Why the garden wall was broken by her?</t>
+          <t>The door is to be shut and you are to go to sleep</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Why had the garden wall been broken by</t>
+          <t>Let the door be shut and you be asleep</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Why was the garden wall broken by her?</t>
+          <t>You are requested to shut the door and go to sleep</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Why will the garden wall be broken by her?</t>
+          <t>The door is to be shut and you are requested</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Why was the garden wall broken by her?</t>
-        </is>
-      </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>The object "the garden wall" becomes the subject, and "did break" changes to "was broken."</t>
-        </is>
-      </c>
+          <t>You are requested to shut the door and go to sleep</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>67</v>
+        <v>2</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>I will have completed the task by tomorrow.</t>
+          <t>The police caught the thief at last.</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>The task will be completed by me by</t>
+          <t>At last the thief was caught by the police</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>By tomorrow the task will have been completed</t>
+          <t>The thief at last caught the police.</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>The task would be completed by me by tomorrow</t>
+          <t>The thief was at last caught by the police.</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>By tomorrow the task would have been  completed</t>
+          <t>At last the thief by the police was caught.</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>By tomorrow the task will have been completed</t>
+          <t>At last the thief was caught by the police</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>The object "the task" becomes the subject, and "will have completed" changes to "will have been completed</t>
+          <t>"The police" is the subject, and "the thief" is the object. The verb "caught" changes to "was caught" in the passive form.</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>The burglar destroyed several items in the room.</t>
+          <t>They drew a circle in the morning.</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Several items destroyed in the room by the</t>
+          <t>A circle was being drawn by them in the</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Several items in the room were destroyed by the burglar</t>
+          <t>A circle was drawn by them in the morning.</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Including the carpet, several items in the</t>
+          <t>In the morning a circle have been drawn by</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>The burglar, being destroyed several items</t>
+          <t>A circle has been drawing since morning.</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Several items in the room were destroyed by the burglar</t>
+          <t>A circle was drawn by them in the morning.</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>The object "several items in the room" becomes the subject, and "destroyed" changes to "were destroyed."</t>
+          <t>The object "a circle" becomes the subject, and "drew" changes to "was drawn."</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>66</v>
+        <v>78</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>The news surprised me.</t>
+          <t>The lightning caused a serious forest fire and</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>I am surprised by the news.</t>
+          <t>A serious forest fire has been caused by</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>I was surprised by the news.</t>
+          <t>A serious forest fire has been caused by lightning</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>The news was surprised by me.</t>
+          <t>A serious forest fire had been caused by</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>The news was a big surprise.</t>
+          <t>A serious forest fire was caused by lightning</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>I was surprised by the news.</t>
-        </is>
-      </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>The object "me" becomes the subject, and "surprised" changes to "was surprised."</t>
-        </is>
-      </c>
+          <t>A serious forest fire was caused by lightning</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>65</v>
+        <v>104</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>The house has been painted yellow by Nikil.</t>
+          <t>Hamlet was written by Shakespeare.</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Nikil had painted the house yellow.</t>
+          <t>Shakespeare has written Hamlet.</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Nikil has painted the house yellow.</t>
+          <t>Shakespeare had written Hamlet.</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Nikil was painting yellow the house.</t>
+          <t>Shakespeare wrote Hamlet.</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Nikil has been painting yellow the house.</t>
+          <t>Shakespeare writes Hamlet.</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Nikil has painted the house yellow.</t>
-        </is>
-      </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>The subject "Nikhil" becomes active, and "has been painted" changes to "has painted."</t>
-        </is>
-      </c>
+          <t>Shakespeare wrote Hamlet.</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>123</v>
+        <v>106</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Shut all the doors and windows in the night.</t>
+          <t>How many languages are spoken in India?</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Let all the doors and windows be shut in the</t>
+          <t>How many languages Indians are speaking</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>All the doors and windows may be shut in</t>
+          <t>How many languages Indians speak?</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Let all the doors and windows remain shut</t>
+          <t>How many languages do Indians speak?</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>All the doors and windows be shutted in</t>
+          <t>How many languages did Indians speak?</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Let all the doors and windows be shut in the</t>
+          <t>How many languages do Indians speak?</t>
         </is>
       </c>
       <c r="H53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>18</v>
+        <v>70</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>The traitors should be shot dead.</t>
+          <t>She learns music.</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>They should have shot the traitors dead.</t>
+          <t>Music was learnt by her.</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>They shall shoot the traitors dead.</t>
+          <t>Music was being learnt by her.</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>They should shoot the traitors dead.</t>
+          <t>Music is being learnt by her.</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>They shot the traitors dead.</t>
+          <t>Music is leant by her.</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>They should shoot the traitors dead.</t>
-        </is>
-      </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>The subject "someone" performs the action, and "should be shot" changes to "should shoot."</t>
-        </is>
-      </c>
+          <t>Music is leant by her.</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>23</v>
+        <v>56</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>He admonished her for the error.</t>
+          <t>The criminal has to obey the court.</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>She was admonished by him for the error.</t>
+          <t>The court has to be obeyed by the criminal.</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>She has been admonished by him for the</t>
+          <t>The court will have to be obeyed by the</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>She would be admonished by him for the</t>
+          <t>The court must be obeyed.</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>She is admonished by him for the error.</t>
+          <t>The court will be obeyed.</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>She was admonished by him for the error.</t>
+          <t>The court has to be obeyed by the criminal.</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>The object "her" becomes the subject, and "admonished" changes to "was admonished."</t>
+          <t>The object "the court" becomes the subject, and "has to obey" changes to "has to be obeyed."</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>98</v>
+        <v>15</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Cigarettes cannot be sold here.</t>
+          <t>We have decided to open a new branch</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Nobody sold cigarettes here.</t>
+          <t>To open a new branch was decided by us.</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Nobody could sell cigarettes here.</t>
+          <t>To be opened a new branch has been decided.</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Nobody can sell cigarettes here.</t>
+          <t>It has been decided to open a new branch.</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Anybody can’t sell cigarettes here.</t>
+          <t>It may be decided to open a new branch by</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Nobody can sell cigarettes here.</t>
-        </is>
-      </c>
-      <c r="H56" t="inlineStr"/>
+          <t>It has been decided to open a new branch.</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>The object "a new branch" becomes the subject, and "have decided" changes to "has been decided to be open."</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>15</v>
+        <v>98</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>We have decided to open a new branch</t>
+          <t>Cigarettes cannot be sold here.</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>To open a new branch was decided by us.</t>
+          <t>Nobody sold cigarettes here.</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>To be opened a new branch has been decided.</t>
+          <t>Nobody could sell cigarettes here.</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>It has been decided to open a new branch.</t>
+          <t>Nobody can sell cigarettes here.</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>It may be decided to open a new branch by</t>
+          <t>Anybody can’t sell cigarettes here.</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>It has been decided to open a new branch.</t>
-        </is>
-      </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>The object "a new branch" becomes the subject, and "have decided" changes to "has been decided to be open."</t>
-        </is>
-      </c>
+          <t>Nobody can sell cigarettes here.</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>56</v>
+        <v>23</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>The criminal has to obey the court.</t>
+          <t>He admonished her for the error.</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>The court has to be obeyed by the criminal.</t>
+          <t>She was admonished by him for the error.</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>The court will have to be obeyed by the</t>
+          <t>She has been admonished by him for the</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>The court must be obeyed.</t>
+          <t>She would be admonished by him for the</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>The court will be obeyed.</t>
+          <t>She is admonished by him for the error.</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>The court has to be obeyed by the criminal.</t>
+          <t>She was admonished by him for the error.</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>The object "the court" becomes the subject, and "has to obey" changes to "has to be obeyed."</t>
+          <t>The object "her" becomes the subject, and "admonished" changes to "was admonished."</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>70</v>
+        <v>18</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>She learns music.</t>
+          <t>The traitors should be shot dead.</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Music was learnt by her.</t>
+          <t>They should have shot the traitors dead.</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Music was being learnt by her.</t>
+          <t>They shall shoot the traitors dead.</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Music is being learnt by her.</t>
+          <t>They should shoot the traitors dead.</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Music is leant by her.</t>
+          <t>They shot the traitors dead.</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Music is leant by her.</t>
-        </is>
-      </c>
-      <c r="H59" t="inlineStr"/>
+          <t>They should shoot the traitors dead.</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>The subject "someone" performs the action, and "should be shot" changes to "should shoot."</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>106</v>
+        <v>123</v>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>How many languages are spoken in India?</t>
+          <t>Shut all the doors and windows in the night.</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>How many languages Indians are speaking</t>
+          <t>Let all the doors and windows be shut in the</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>How many languages Indians speak?</t>
+          <t>All the doors and windows may be shut in</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>How many languages do Indians speak?</t>
+          <t>Let all the doors and windows remain shut</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>How many languages did Indians speak?</t>
+          <t>All the doors and windows be shutted in</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>How many languages do Indians speak?</t>
+          <t>Let all the doors and windows be shut in the</t>
         </is>
       </c>
       <c r="H60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>104</v>
+        <v>65</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Hamlet was written by Shakespeare.</t>
+          <t>The house has been painted yellow by Nikil.</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Shakespeare has written Hamlet.</t>
+          <t>Nikil had painted the house yellow.</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Shakespeare had written Hamlet.</t>
+          <t>Nikil has painted the house yellow.</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Shakespeare wrote Hamlet.</t>
+          <t>Nikil was painting yellow the house.</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Shakespeare writes Hamlet.</t>
+          <t>Nikil has been painting yellow the house.</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Shakespeare wrote Hamlet.</t>
-        </is>
-      </c>
-      <c r="H61" t="inlineStr"/>
+          <t>Nikil has painted the house yellow.</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>The subject "Nikhil" becomes active, and "has been painted" changes to "has painted."</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>62</v>
+        <v>13</v>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>We waste much time on social websites.</t>
+          <t>He had committed a mistake.</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Much time was wasted on social websites.</t>
+          <t>A mistake had committed by him.</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Much time will be wasted on social websites.</t>
+          <t>A mistake was committed by him.</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Much time is wasted by us on social websites</t>
+          <t>A mistake had been committed by him.</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Much time is being wasted y us on social websites</t>
+          <t>A mistake has been committed by him</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Much time is wasted by us on social websites</t>
+          <t>A mistake had been committed by him.</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>The object "much time" becomes the subject, and "waste" changes to "is wasted."</t>
+          <t>The object "a mistake" becomes the subject, and "had committed" changes to "had been committed."</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>31</v>
+        <v>71</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Our task had been completed before sunset.</t>
+          <t>They are going to build a new airport near the old</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>We completed our task before sunset.</t>
+          <t>A new airport going to be built near the old</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>We have completed our task before sunset.</t>
+          <t>A new airport is being built near the old one.</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>We complete our task before sunset.</t>
+          <t>A new airport will be built near the old one.</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>We had completed our task before sunset.</t>
+          <t>A new airport is going to be built near the</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>We had completed our task before sunset.</t>
-        </is>
-      </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>The subject "our task" becomes the object, and "had been completed" changes to "had completed</t>
-        </is>
-      </c>
+          <t>A new airport is going to be built near the</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>46</v>
+        <v>84</v>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>The manager could not accept the union leader’s proposal</t>
+          <t>Gandhiji started the Quit India Movement in 1942.</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>The union leader’s proposal could not be accepted by the manager</t>
+          <t>The Quit India Movement was started by</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>The union leader’s proposals were not</t>
+          <t>The Quit India Movement was been started</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>The union leader’s proposals will not be</t>
+          <t>The Quit India Movement had been started</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>The union leader’s proposals would not be</t>
+          <t>The Quit India Movement started by</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>The union leader’s proposal could not be accepted by the manager</t>
-        </is>
-      </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>The object "the union leader’s proposal" becomes the subject, and "could not accept" changes to "could not be accepted."</t>
-        </is>
-      </c>
+          <t>The Quit India Movement was started by</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>126</v>
+        <v>69</v>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>She always cooks delicious food.</t>
+          <t>The box was dropped by the boy.</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Delicious food is always cooked by her.</t>
+          <t>The boy dropped the box.</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Delicious food is always being cooked by</t>
+          <t>The boy drops the box.</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Delicious food has been cooked by her.</t>
+          <t>The boy has dropped the box.</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Delicious food was being cooked by her.</t>
+          <t>The boy is dropping the box.</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Delicious food is always cooked by her.</t>
-        </is>
-      </c>
-      <c r="H65" t="inlineStr"/>
+          <t>The boy dropped the box.</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>The subject "the boy" becomes active, and "was dropped" changes to "dropped."</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>19</v>
+        <v>92</v>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Rahul is teaching the children in the slum areas.</t>
+          <t>Where did you buy this pen ?</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>The children in the slum areas are taught by</t>
+          <t>Where shall you buy this pen ?</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>The children are taught by Rahul in the slum</t>
+          <t>Where is this pen bought by you ?</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>In the slum areas the children are learning</t>
+          <t>Where was this pen bought ?</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>The children in the slum areas are being taught by Rahul</t>
+          <t>Where will you buy this pen ?</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>The children in the slum areas are being taught by Rahul</t>
-        </is>
-      </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>The object "the children in the slum areas" becomes the subject, and "is teaching" changes to "are being taught."</t>
-        </is>
-      </c>
+          <t>Where was this pen bought ?</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>92</v>
+        <v>19</v>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Where did you buy this pen ?</t>
+          <t>Rahul is teaching the children in the slum areas.</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Where shall you buy this pen ?</t>
+          <t>The children in the slum areas are taught by</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Where is this pen bought by you ?</t>
+          <t>The children are taught by Rahul in the slum</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Where was this pen bought ?</t>
+          <t>In the slum areas the children are learning</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Where will you buy this pen ?</t>
+          <t>The children in the slum areas are being taught by Rahul</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Where was this pen bought ?</t>
-        </is>
-      </c>
-      <c r="H67" t="inlineStr"/>
+          <t>The children in the slum areas are being taught by Rahul</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>The object "the children in the slum areas" becomes the subject, and "is teaching" changes to "are being taught."</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>69</v>
+        <v>126</v>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>The box was dropped by the boy.</t>
+          <t>She always cooks delicious food.</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>The boy dropped the box.</t>
+          <t>Delicious food is always cooked by her.</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>The boy drops the box.</t>
+          <t>Delicious food is always being cooked by</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>The boy has dropped the box.</t>
+          <t>Delicious food has been cooked by her.</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>The boy is dropping the box.</t>
+          <t>Delicious food was being cooked by her.</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>The boy dropped the box.</t>
-        </is>
-      </c>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t>The subject "the boy" becomes active, and "was dropped" changes to "dropped."</t>
-        </is>
-      </c>
+          <t>Delicious food is always cooked by her.</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>84</v>
+        <v>46</v>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Gandhiji started the Quit India Movement in 1942.</t>
+          <t>The manager could not accept the union leader’s proposal</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>The Quit India Movement was started by</t>
+          <t>The union leader’s proposal could not be accepted by the manager</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>The Quit India Movement was been started</t>
+          <t>The union leader’s proposals were not</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>The Quit India Movement had been started</t>
+          <t>The union leader’s proposals will not be</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>The Quit India Movement started by</t>
+          <t>The union leader’s proposals would not be</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>The Quit India Movement was started by</t>
-        </is>
-      </c>
-      <c r="H69" t="inlineStr"/>
+          <t>The union leader’s proposal could not be accepted by the manager</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>The object "the union leader’s proposal" becomes the subject, and "could not accept" changes to "could not be accepted."</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>71</v>
+        <v>31</v>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>They are going to build a new airport near the old</t>
+          <t>Our task had been completed before sunset.</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>A new airport going to be built near the old</t>
+          <t>We completed our task before sunset.</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>A new airport is being built near the old one.</t>
+          <t>We have completed our task before sunset.</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>A new airport will be built near the old one.</t>
+          <t>We complete our task before sunset.</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>A new airport is going to be built near the</t>
+          <t>We had completed our task before sunset.</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>A new airport is going to be built near the</t>
-        </is>
-      </c>
-      <c r="H70" t="inlineStr"/>
+          <t>We had completed our task before sunset.</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>The subject "our task" becomes the object, and "had been completed" changes to "had completed</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>13</v>
+        <v>62</v>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>He had committed a mistake.</t>
+          <t>We waste much time on social websites.</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>A mistake had committed by him.</t>
+          <t>Much time was wasted on social websites.</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>A mistake was committed by him.</t>
+          <t>Much time will be wasted on social websites.</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>A mistake had been committed by him.</t>
+          <t>Much time is wasted by us on social websites</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>A mistake has been committed by him</t>
+          <t>Much time is being wasted y us on social websites</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>A mistake had been committed by him.</t>
+          <t>Much time is wasted by us on social websites</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>The object "a mistake" becomes the subject, and "had committed" changes to "had been committed."</t>
+          <t>The object "much time" becomes the subject, and "waste" changes to "is wasted."</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>117</v>
+        <v>36</v>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>He handed her a chair.</t>
+          <t>They will demolish the entire block.</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>She was handed a chair by him.</t>
+          <t>The entire block is being demolished</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>He handed a chair to her.</t>
+          <t>The block may be demolished entirely.</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>He will hand a chair to her.</t>
+          <t>The entire block will have to be demolished</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>A chair will be handed to her by him</t>
+          <t>The entire block will be demolished by them.</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>She was handed a chair by him.</t>
-        </is>
-      </c>
-      <c r="H72" t="inlineStr"/>
+          <t>The entire block will be demolished by them.</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>The object "the entire block" becomes the subject, and "will demolish" changes to "will be demolished.</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>87</v>
+        <v>26</v>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>The modern means of communication have made</t>
+          <t>We found him a good wife.</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Life had been made so much easier by the</t>
+          <t>He was found a good wife by us.</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Life is being so much easier by the modern</t>
+          <t>A good wife was found out by them.</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Life has been made so much easier by the</t>
+          <t>A good wife found him.</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Life was made so much easier by the modern</t>
+          <t>A good wife was being found by us.</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Life has been made so much easier by the</t>
-        </is>
-      </c>
-      <c r="H73" t="inlineStr"/>
+          <t>He was found a good wife by us.</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>The object "him" becomes the subject, and "found" changes to "was found."</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>7</v>
+        <v>29</v>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>‘The Titanic’ was hit by an iceberg.</t>
+          <t>Circumstances forced him to resign his post.</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>An iceberg hit “The Titanic’.</t>
+          <t>Circumstances make him to resign his post.</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>An iceberg was hit by ‘The Titanic.’`</t>
+          <t>He was forced to resign his post by circumstances</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>An iceberg was being hit by ‘The Titanic’.</t>
+          <t>He is forced to resign his post.</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>An iceberg was hitting ‘The Titanic.’</t>
+          <t>He is forced and resigned his post.</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>An iceberg hit “The Titanic’.</t>
+          <t>He was forced to resign his post by circumstances</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>he subject "The Titanic" becomes the object, and "was hit" changes to "hit."</t>
+          <t>The object "him" becomes the subject, and "forced" changes to "was forced."</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>38</v>
+        <v>25</v>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>We must respect the elders.</t>
+          <t>The boys saved many elders from drowning.</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>The elders deserve respect from us.</t>
+          <t>Many elders are saved from drowning by the</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>The elders must be respected.</t>
+          <t>Many elders are being saved from drowning</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>The elders must be respected by us.</t>
+          <t>Many elders were saved from drowning by the boys</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Respect the elders we must.</t>
+          <t>Many elders have been saved from drowning</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>The elders must be respected by us.</t>
+          <t>Many elders were saved from drowning by the boys</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>The object "the elders" becomes the subject, and "must respect" changes to "must be respected."</t>
+          <t>The object "many elders" becomes the subject, and "saved" changes to "were saved</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>10</v>
+        <v>99</v>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>The doctor advised her to take rest.</t>
+          <t>A big variety store was inaugurated by Sachin.</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>She has been advised rest by the doctor.</t>
+          <t>Sachin inaugurated a big variety store.</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>She was advised to be taken ret by the doctor.</t>
+          <t>Sachin had inaugurated a big variety store.</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>She was advised to take rest by the doctor.</t>
+          <t>Sachin has inaugurated a big variety store.</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>She has been advised to take rest by the</t>
+          <t>Sachin inaugurate a big variety store.</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>She was advised to take rest by the doctor.</t>
-        </is>
-      </c>
-      <c r="H76" t="inlineStr">
-        <is>
-          <t>The object "her" becomes the subject, and "advised" changes to "was advised."</t>
-        </is>
-      </c>
+          <t>Sachin inaugurated a big variety store.</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>99</v>
+        <v>10</v>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>A big variety store was inaugurated by Sachin.</t>
+          <t>The doctor advised her to take rest.</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Sachin inaugurated a big variety store.</t>
+          <t>She has been advised rest by the doctor.</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Sachin had inaugurated a big variety store.</t>
+          <t>She was advised to be taken ret by the doctor.</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Sachin has inaugurated a big variety store.</t>
+          <t>She was advised to take rest by the doctor.</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Sachin inaugurate a big variety store.</t>
+          <t>She has been advised to take rest by the</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Sachin inaugurated a big variety store.</t>
-        </is>
-      </c>
-      <c r="H77" t="inlineStr"/>
+          <t>She was advised to take rest by the doctor.</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>The object "her" becomes the subject, and "advised" changes to "was advised."</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>The boys saved many elders from drowning.</t>
+          <t>We must respect the elders.</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Many elders are saved from drowning by the</t>
+          <t>The elders deserve respect from us.</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Many elders are being saved from drowning</t>
+          <t>The elders must be respected.</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Many elders were saved from drowning by the boys</t>
+          <t>The elders must be respected by us.</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Many elders have been saved from drowning</t>
+          <t>Respect the elders we must.</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Many elders were saved from drowning by the boys</t>
+          <t>The elders must be respected by us.</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>The object "many elders" becomes the subject, and "saved" changes to "were saved</t>
+          <t>The object "the elders" becomes the subject, and "must respect" changes to "must be respected."</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>29</v>
+        <v>7</v>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Circumstances forced him to resign his post.</t>
+          <t>‘The Titanic’ was hit by an iceberg.</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Circumstances make him to resign his post.</t>
+          <t>An iceberg hit “The Titanic’.</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>He was forced to resign his post by circumstances</t>
+          <t>An iceberg was hit by ‘The Titanic.’`</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>He is forced to resign his post.</t>
+          <t>An iceberg was being hit by ‘The Titanic’.</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>He is forced and resigned his post.</t>
+          <t>An iceberg was hitting ‘The Titanic.’</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>He was forced to resign his post by circumstances</t>
+          <t>An iceberg hit “The Titanic’.</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>The object "him" becomes the subject, and "forced" changes to "was forced."</t>
+          <t>he subject "The Titanic" becomes the object, and "was hit" changes to "hit."</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>26</v>
+        <v>87</v>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>We found him a good wife.</t>
+          <t>The modern means of communication have made</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>He was found a good wife by us.</t>
+          <t>Life had been made so much easier by the</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>A good wife was found out by them.</t>
+          <t>Life is being so much easier by the modern</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>A good wife found him.</t>
+          <t>Life has been made so much easier by the</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>A good wife was being found by us.</t>
+          <t>Life was made so much easier by the modern</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>He was found a good wife by us.</t>
-        </is>
-      </c>
-      <c r="H80" t="inlineStr">
-        <is>
-          <t>The object "him" becomes the subject, and "found" changes to "was found."</t>
-        </is>
-      </c>
+          <t>Life has been made so much easier by the</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>36</v>
+        <v>117</v>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>They will demolish the entire block.</t>
+          <t>He handed her a chair.</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>The entire block is being demolished</t>
+          <t>She was handed a chair by him.</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>The block may be demolished entirely.</t>
+          <t>He handed a chair to her.</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>The entire block will have to be demolished</t>
+          <t>He will hand a chair to her.</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>The entire block will be demolished by them.</t>
+          <t>A chair will be handed to her by him</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>The entire block will be demolished by them.</t>
-        </is>
-      </c>
-      <c r="H81" t="inlineStr">
-        <is>
-          <t>The object "the entire block" becomes the subject, and "will demolish" changes to "will be demolished.</t>
-        </is>
-      </c>
+          <t>She was handed a chair by him.</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>12</v>
+        <v>128</v>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>It is being read by us.</t>
+          <t>The company paid her a meagre salary.</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>We are reading it.</t>
+          <t>She was paid a meagre salary by the</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>It will be read by us.</t>
+          <t>A meagre salary has been paid to her by the</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>We can read it.</t>
+          <t>She was being paid a meagre salary by the</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>We have to read it.</t>
+          <t>A meagre salary was to be paid to her by the</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>We are reading it.</t>
-        </is>
-      </c>
-      <c r="H82" t="inlineStr">
-        <is>
-          <t>The subject "we" performs the action, and "is being read" changes to "are reading."</t>
-        </is>
-      </c>
+          <t>She was paid a meagre salary by the</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>I have been sent here by the editor of Tribune.</t>
+          <t>The scheme permits investors to buy the shares</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>The editor of Tribune has send me here.</t>
+          <t>Under the scheme the investors may be</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>The editor of Tribune sent me here.</t>
+          <t>Under the scheme the investors have been</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>The editor of Tribune has sent me here.</t>
+          <t>Under the scheme the investors are permitted</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>The editor of Tribune send me here.</t>
+          <t>Under the scheme the investors were</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>The editor of Tribune has sent me here.</t>
+          <t>Under the scheme the investors are permitted</t>
         </is>
       </c>
       <c r="H83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>17</v>
+        <v>113</v>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Paint the windows.</t>
+          <t>Newton wrote this letter yesterday.</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Windows should be painted.</t>
+          <t>Yesterday was written letter by Newton.</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Let the windows be painted.</t>
+          <t>This letter is written by Newton yesterday.</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Let be the windows painted.</t>
+          <t>This letter was written by Newton yesterday.</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Windows are let to be painted.</t>
+          <t>This letter was wrote by Newton yesterday.</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Let the windows be painted.</t>
-        </is>
-      </c>
-      <c r="H84" t="inlineStr">
-        <is>
-          <t>In imperative sentences, "let" is used for passive voice.</t>
-        </is>
-      </c>
+          <t>This letter was written by Newton yesterday.</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>74</v>
+        <v>95</v>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Could you pass the salt ?</t>
+          <t>The thief was caught.</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Could the salt been passed ?</t>
+          <t>The policeman may have caught the thief.</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Could the salt be passed by anyone ?</t>
+          <t>The policeman caught the thief.</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Could the salt be past ?</t>
+          <t>The policeman has caught the thief.</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Could the salt be passed ?</t>
+          <t>The policeman had caught the thief.</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Could the salt be passed ?</t>
+          <t>The policeman caught the thief.</t>
         </is>
       </c>
       <c r="H85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>50</v>
+        <v>116</v>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>We must take care of all living species on Earth.</t>
+          <t>The Indian Government is encouraging the</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>All living species on Earth are taken care of</t>
+          <t>The Europeans are encouraged by the Indian</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>All living species on Earth must be taken care of by us</t>
+          <t>The Europeans are encouraging by the Indian</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>All living species on Earth had been taken</t>
+          <t>The Europeans are being encouraged by the</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>All living species on Earth will be taken care</t>
+          <t>The Europeans is being encouraged by the</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>All living species on Earth must be taken care of by us</t>
-        </is>
-      </c>
-      <c r="H86" t="inlineStr">
-        <is>
-          <t>The object "all living species on Earth" becomes the subject, and "must take care of" changes to "must be taken care of</t>
-        </is>
-      </c>
+          <t>The Europeans are being encouraged by the</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>116</v>
+        <v>50</v>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>The Indian Government is encouraging the</t>
+          <t>We must take care of all living species on Earth.</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>The Europeans are encouraged by the Indian</t>
+          <t>All living species on Earth are taken care of</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>The Europeans are encouraging by the Indian</t>
+          <t>All living species on Earth must be taken care of by us</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>The Europeans are being encouraged by the</t>
+          <t>All living species on Earth had been taken</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>The Europeans is being encouraged by the</t>
+          <t>All living species on Earth will be taken care</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>The Europeans are being encouraged by the</t>
-        </is>
-      </c>
-      <c r="H87" t="inlineStr"/>
+          <t>All living species on Earth must be taken care of by us</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>The object "all living species on Earth" becomes the subject, and "must take care of" changes to "must be taken care of</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>95</v>
+        <v>74</v>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>The thief was caught.</t>
+          <t>Could you pass the salt ?</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>The policeman may have caught the thief.</t>
+          <t>Could the salt been passed ?</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>The policeman caught the thief.</t>
+          <t>Could the salt be passed by anyone ?</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>The policeman has caught the thief.</t>
+          <t>Could the salt be past ?</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>The policeman had caught the thief.</t>
+          <t>Could the salt be passed ?</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>The policeman caught the thief.</t>
+          <t>Could the salt be passed ?</t>
         </is>
       </c>
       <c r="H88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>113</v>
+        <v>17</v>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Newton wrote this letter yesterday.</t>
+          <t>Paint the windows.</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Yesterday was written letter by Newton.</t>
+          <t>Windows should be painted.</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>This letter is written by Newton yesterday.</t>
+          <t>Let the windows be painted.</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>This letter was written by Newton yesterday.</t>
+          <t>Let be the windows painted.</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>This letter was wrote by Newton yesterday.</t>
+          <t>Windows are let to be painted.</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>This letter was written by Newton yesterday.</t>
-        </is>
-      </c>
-      <c r="H89" t="inlineStr"/>
+          <t>Let the windows be painted.</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>In imperative sentences, "let" is used for passive voice.</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>90</v>
+        <v>97</v>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>The scheme permits investors to buy the shares</t>
+          <t>I have been sent here by the editor of Tribune.</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Under the scheme the investors may be</t>
+          <t>The editor of Tribune has send me here.</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Under the scheme the investors have been</t>
+          <t>The editor of Tribune sent me here.</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Under the scheme the investors are permitted</t>
+          <t>The editor of Tribune has sent me here.</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Under the scheme the investors were</t>
+          <t>The editor of Tribune send me here.</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Under the scheme the investors are permitted</t>
+          <t>The editor of Tribune has sent me here.</t>
         </is>
       </c>
       <c r="H90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>128</v>
+        <v>12</v>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>The company paid her a meagre salary.</t>
+          <t>It is being read by us.</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>She was paid a meagre salary by the</t>
+          <t>We are reading it.</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>A meagre salary has been paid to her by the</t>
+          <t>It will be read by us.</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>She was being paid a meagre salary by the</t>
+          <t>We can read it.</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>A meagre salary was to be paid to her by the</t>
+          <t>We have to read it.</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>She was paid a meagre salary by the</t>
-        </is>
-      </c>
-      <c r="H91" t="inlineStr"/>
+          <t>We are reading it.</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>The subject "we" performs the action, and "is being read" changes to "are reading."</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>76</v>
+        <v>4</v>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Who asked you to draft this letter ?</t>
+          <t>Somebody has stolen his book.</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>By who you are asked to draft this letter.</t>
+          <t>His book was stolen.</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>By who have you been asked to draft this</t>
+          <t>His book was stolen by somebody.</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>By whom were you asked to draft this letter</t>
+          <t>His book has been stolen.</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>By whom you were asked to draft this letter.</t>
+          <t>His book had been stolen by somebody.</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>By whom were you asked to draft this letter</t>
-        </is>
-      </c>
-      <c r="H92" t="inlineStr"/>
+          <t>His book has been stolen.</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>The object "his book" becomes the subject, and the verb changes to "has been stolen."</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>109</v>
+        <v>79</v>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>They should shoot the terrorists dead.</t>
+          <t>Today I accomplished my task successfully.</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>The terrorists been shot dead by them.</t>
+          <t>Today my task is accomplished successfully</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>The terrorists should have been shot dead</t>
+          <t>Today my task accomplished successfully.</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>The terrorists should be shot dead by them.</t>
+          <t>Today my task was accomplished</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>The terrorists have been shot dead by them.</t>
+          <t>Today my task was accomplished
+successfully</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>The terrorists should be shot dead by them.</t>
+          <t>Today my task was accomplished
+successfully</t>
         </is>
       </c>
       <c r="H93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>53</v>
+        <v>75</v>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>The storm damaged the roof.</t>
+          <t>Don’t subject the animals to cruelty.</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>The roof is damaged by the storm.</t>
+          <t>The animals are not to be subjected to</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>The roof was damage by the storm.</t>
+          <t>The animals shall not be subjected to cruelty.</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>The roof was damaged by the storm.</t>
+          <t>The animals will not be subjected to cruelty.</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>The roof would be damaged by the storm</t>
+          <t>The animals should not be subjected to</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>The roof was damaged by the storm.</t>
-        </is>
-      </c>
-      <c r="H94" t="inlineStr">
-        <is>
-          <t>The object "the roof" becomes the subject, and "damaged" changes to "was damaged."</t>
-        </is>
-      </c>
+          <t>The animals should not be subjected to</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>120</v>
+        <v>54</v>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Who painted it?</t>
+          <t>People speak English all over the world.</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>It was painted?</t>
+          <t>English was spoken all over the world.</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Was it painted?</t>
+          <t>English have been spoken all over the world.</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Had it been painted by?</t>
+          <t>English has been spoken all over the world.</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>By whom was it painted?</t>
+          <t>English is spoken all over the world by people</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>By whom was it painted?</t>
-        </is>
-      </c>
-      <c r="H95" t="inlineStr"/>
+          <t>English is spoken all over the world by people</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>The object "English" becomes the subject, and "speak" changes to "is spoken."</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>111</v>
+        <v>63</v>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>The whole village was ravaged by the man-eater.</t>
+          <t>A great deal of harm is caused to the environment</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>The man-eater ravages the whole village.</t>
+          <t>We have caused a great deal of harm to the environment</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>The whole village is ravaged by the maneater.</t>
+          <t>The environment causes a great deal of harm</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>The man-eater ravaged the whole village.</t>
+          <t>We cause a great deal of harm to the environment</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>The whole village is being ravaged by the</t>
+          <t>The environment is being caused a great deal harm</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>The man-eater ravaged the whole village.</t>
-        </is>
-      </c>
-      <c r="H96" t="inlineStr"/>
+          <t>We cause a great deal of harm to the environment</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>The subject "human activities" becomes active, and "is caused" changes to "cause."</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>63</v>
+        <v>111</v>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>A great deal of harm is caused to the environment</t>
+          <t>The whole village was ravaged by the man-eater.</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>We have caused a great deal of harm to the environment</t>
+          <t>The man-eater ravages the whole village.</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>The environment causes a great deal of harm</t>
+          <t>The whole village is ravaged by the maneater.</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>We cause a great deal of harm to the environment</t>
+          <t>The man-eater ravaged the whole village.</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>The environment is being caused a great deal harm</t>
+          <t>The whole village is being ravaged by the</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>We cause a great deal of harm to the environment</t>
-        </is>
-      </c>
-      <c r="H97" t="inlineStr">
-        <is>
-          <t>The subject "human activities" becomes active, and "is caused" changes to "cause."</t>
-        </is>
-      </c>
+          <t>The man-eater ravaged the whole village.</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>54</v>
+        <v>120</v>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>People speak English all over the world.</t>
+          <t>Who painted it?</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>English was spoken all over the world.</t>
+          <t>It was painted?</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>English have been spoken all over the world.</t>
+          <t>Was it painted?</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>English has been spoken all over the world.</t>
+          <t>Had it been painted by?</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>English is spoken all over the world by people</t>
+          <t>By whom was it painted?</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>English is spoken all over the world by people</t>
-        </is>
-      </c>
-      <c r="H98" t="inlineStr">
-        <is>
-          <t>The object "English" becomes the subject, and "speak" changes to "is spoken."</t>
-        </is>
-      </c>
+          <t>By whom was it painted?</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>75</v>
+        <v>53</v>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Don’t subject the animals to cruelty.</t>
+          <t>The storm damaged the roof.</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>The animals are not to be subjected to</t>
+          <t>The roof is damaged by the storm.</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>The animals shall not be subjected to cruelty.</t>
+          <t>The roof was damage by the storm.</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>The animals will not be subjected to cruelty.</t>
+          <t>The roof was damaged by the storm.</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>The animals should not be subjected to</t>
+          <t>The roof would be damaged by the storm</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>The animals should not be subjected to</t>
-        </is>
-      </c>
-      <c r="H99" t="inlineStr"/>
+          <t>The roof was damaged by the storm.</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>The object "the roof" becomes the subject, and "damaged" changes to "was damaged."</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>79</v>
+        <v>109</v>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Today I accomplished my task successfully.</t>
+          <t>They should shoot the terrorists dead.</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Today my task is accomplished successfully</t>
+          <t>The terrorists been shot dead by them.</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Today my task accomplished successfully.</t>
+          <t>The terrorists should have been shot dead</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Today my task was accomplished</t>
+          <t>The terrorists should be shot dead by them.</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Today my task was accomplished
-successfully</t>
+          <t>The terrorists have been shot dead by them.</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Today my task was accomplished
-successfully</t>
+          <t>The terrorists should be shot dead by them.</t>
         </is>
       </c>
       <c r="H100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>4</v>
+        <v>76</v>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Somebody has stolen his book.</t>
+          <t>Who asked you to draft this letter ?</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>His book was stolen.</t>
+          <t>By who you are asked to draft this letter.</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>His book was stolen by somebody.</t>
+          <t>By who have you been asked to draft this</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>His book has been stolen.</t>
+          <t>By whom were you asked to draft this letter</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>His book had been stolen by somebody.</t>
+          <t>By whom you were asked to draft this letter.</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>His book has been stolen.</t>
-        </is>
-      </c>
-      <c r="H101" t="inlineStr">
-        <is>
-          <t>The object "his book" becomes the subject, and the verb changes to "has been stolen."</t>
-        </is>
-      </c>
+          <t>By whom were you asked to draft this letter</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>110</v>
+        <v>34</v>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Honey is made by bees.</t>
+          <t>The boys were playing cricket.</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Bees makes honey.</t>
+          <t>Cricket had been played by the boys.</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Bees made honey.</t>
+          <t>Cricket has been played by the boys.</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Bees are making honey.</t>
+          <t>Cricket was played by the boys.</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Bees make honey.</t>
+          <t>Cricket was being played by the boys.</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Bees make honey.</t>
-        </is>
-      </c>
-      <c r="H102" t="inlineStr"/>
+          <t>Cricket was being played by the boys.</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>The object "cricket" becomes the subject, and "were playing" changes to "was being played.</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>59</v>
+        <v>86</v>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>The CEO’s son was kidnapped.</t>
+          <t>Gagan Narang and Vijay won bronze medals in</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Someone kidnapped the CEO’s son.</t>
+          <t>Bronze medals won by Gagan Narang and</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Someone has kidnapped the CEO’s son.</t>
+          <t>Bronze medals had been won by Gagan</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Someone is going to kidnap the CEO’s son.</t>
+          <t>Bronze medals were won by Gagan Narang</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Someone is kidnapping the CEO’s son.</t>
+          <t>Bronze medals have been won by Gagan</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Someone kidnapped the CEO’s son.</t>
-        </is>
-      </c>
-      <c r="H103" t="inlineStr">
-        <is>
-          <t>The subject "someone" is added to make the sentence active, and "was kidnapped" changes to "kidnapped."</t>
-        </is>
-      </c>
+          <t>Bronze medals were won by Gagan Narang</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>41</v>
+        <v>108</v>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>The shopkeeper lowered the prices.</t>
+          <t>The Manager granted me two days leave.</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>The prices lowered the shopkeeper</t>
+          <t>I had been granted two days’ leave by the</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>The prices were lowered by the shopkeeper</t>
+          <t>I have been granted two days’ leave by the</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Down went the prices</t>
+          <t>I granted two days’ leave by the Manager.</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>The shopkeeper got down the prices</t>
+          <t>I was granted two days’ leave by the</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>The prices were lowered by the shopkeeper</t>
-        </is>
-      </c>
-      <c r="H104" t="inlineStr">
-        <is>
-          <t>The object "the prices" becomes the subject, and "lowered" changes to "were lowered."</t>
-        </is>
-      </c>
+          <t>I was granted two days’ leave by the</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>33</v>
+        <v>127</v>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>The government has launched a massive tribal</t>
+          <t>Mother gave him a little puppy.</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>A massive tribal welfare programme is</t>
+          <t>He was given a little puppy by mother.</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>A massive tribal welfare program has been launched by the government.</t>
+          <t>A little puppy was being given to him by</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Jharkhand government has launched a</t>
+          <t>He had been given a little puppy by mother.</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>The government in Jharkhand has launched</t>
+          <t>A little puppy is given to him by his mother.</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>A massive tribal welfare program has been launched by the government.</t>
-        </is>
-      </c>
-      <c r="H105" t="inlineStr">
-        <is>
-          <t>The object "a massive tribal welfare program" becomes the subject, and "has launched" changes to "has been launched</t>
-        </is>
-      </c>
+          <t>He was given a little puppy by mother.</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>My watch has been stolen.</t>
+          <t>We will telecast the programme next Sunday at 4</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Someone has stolen my watch.</t>
+          <t>The programme will be telecast by us next sunday at 4pm</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>They have stolen my watch.</t>
+          <t>The programme would be telecast by us next</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>The watch has been stolen by him.</t>
+          <t>The programme will be telecasted by us next</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Somebody have stolen my watch.</t>
+          <t>The programme would be telecasted by us</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Someone has stolen my watch.</t>
+          <t>The programme will be telecast by us next sunday at 4pm</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>The subject "someone" becomes explicit, and "has been stolen" changes to "has stolen."</t>
+          <t>The object "the programme" becomes the subject, and the verb changes to "will be telecast."</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>We will telecast the programme next Sunday at 4</t>
+          <t>My watch has been stolen.</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>The programme will be telecast by us next sunday at 4pm</t>
+          <t>Someone has stolen my watch.</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>The programme would be telecast by us next</t>
+          <t>They have stolen my watch.</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>The programme will be telecasted by us next</t>
+          <t>The watch has been stolen by him.</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>The programme would be telecasted by us</t>
+          <t>Somebody have stolen my watch.</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>The programme will be telecast by us next sunday at 4pm</t>
+          <t>Someone has stolen my watch.</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>The object "the programme" becomes the subject, and the verb changes to "will be telecast."</t>
+          <t>The subject "someone" becomes explicit, and "has been stolen" changes to "has stolen."</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>127</v>
+        <v>33</v>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Mother gave him a little puppy.</t>
+          <t>The government has launched a massive tribal</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>He was given a little puppy by mother.</t>
+          <t>A massive tribal welfare programme is</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>A little puppy was being given to him by</t>
+          <t>A massive tribal welfare program has been launched by the government.</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>He had been given a little puppy by mother.</t>
+          <t>Jharkhand government has launched a</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>A little puppy is given to him by his mother.</t>
+          <t>The government in Jharkhand has launched</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>He was given a little puppy by mother.</t>
-        </is>
-      </c>
-      <c r="H108" t="inlineStr"/>
+          <t>A massive tribal welfare program has been launched by the government.</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>The object "a massive tribal welfare program" becomes the subject, and "has launched" changes to "has been launched</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>108</v>
+        <v>41</v>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>The Manager granted me two days leave.</t>
+          <t>The shopkeeper lowered the prices.</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>I had been granted two days’ leave by the</t>
+          <t>The prices lowered the shopkeeper</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>I have been granted two days’ leave by the</t>
+          <t>The prices were lowered by the shopkeeper</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>I granted two days’ leave by the Manager.</t>
+          <t>Down went the prices</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>I was granted two days’ leave by the</t>
+          <t>The shopkeeper got down the prices</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>I was granted two days’ leave by the</t>
-        </is>
-      </c>
-      <c r="H109" t="inlineStr"/>
+          <t>The prices were lowered by the shopkeeper</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>The object "the prices" becomes the subject, and "lowered" changes to "were lowered."</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>86</v>
+        <v>59</v>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Gagan Narang and Vijay won bronze medals in</t>
+          <t>The CEO’s son was kidnapped.</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Bronze medals won by Gagan Narang and</t>
+          <t>Someone kidnapped the CEO’s son.</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Bronze medals had been won by Gagan</t>
+          <t>Someone has kidnapped the CEO’s son.</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Bronze medals were won by Gagan Narang</t>
+          <t>Someone is going to kidnap the CEO’s son.</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Bronze medals have been won by Gagan</t>
+          <t>Someone is kidnapping the CEO’s son.</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Bronze medals were won by Gagan Narang</t>
-        </is>
-      </c>
-      <c r="H110" t="inlineStr"/>
+          <t>Someone kidnapped the CEO’s son.</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>The subject "someone" is added to make the sentence active, and "was kidnapped" changes to "kidnapped."</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>34</v>
+        <v>110</v>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>The boys were playing cricket.</t>
+          <t>Honey is made by bees.</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Cricket had been played by the boys.</t>
+          <t>Bees makes honey.</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Cricket has been played by the boys.</t>
+          <t>Bees made honey.</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Cricket was played by the boys.</t>
+          <t>Bees are making honey.</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Cricket was being played by the boys.</t>
+          <t>Bees make honey.</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Cricket was being played by the boys.</t>
-        </is>
-      </c>
-      <c r="H111" t="inlineStr">
-        <is>
-          <t>The object "cricket" becomes the subject, and "were playing" changes to "was being played.</t>
-        </is>
-      </c>
+          <t>Bees make honey.</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>People call him a fool.</t>
+          <t>The students were laughing at the old man.</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>He has been called a fool</t>
+          <t>The old man was being laughed at by the</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>He is called a fool by the people.</t>
+          <t>The old man was laughed at by the students.</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>The people have been calling him a fool.</t>
+          <t>The old man was being laughed by the</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>We all people have called him a fool</t>
+          <t>The old man is laughing at the students.</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>He is called a fool by the people.</t>
-        </is>
-      </c>
-      <c r="H112" t="inlineStr">
-        <is>
-          <t>The object "him" becomes the subject, and "call" changes to "is called."</t>
-        </is>
-      </c>
+          <t>The old man was being laughed at by the</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>24</v>
+        <v>61</v>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Can we send this big parcel by air?</t>
+          <t>My parents are advising me about my further studies</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Can this big parcel be sent by air?</t>
+          <t>I am being advised about my further studies by my parents.</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Can this big parcel sent by air?</t>
+          <t>I am advised by my parents about my further studies</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Could this big parcel be sent by air?</t>
+          <t>I was advised about my further studies by my parent</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Could this big parcel sent by us by air?</t>
+          <t>I had been advised about my further studies</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Can this big parcel be sent by air?</t>
+          <t>I am being advised about my further studies by my parents.</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>The object "this big parcel" becomes the subject, and "send" changes to "be sent."</t>
+          <t>The object "me" becomes the subject, and "are advising" changes to "am being advised."</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>88</v>
+        <v>73</v>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Thick clouds have overcast the sky.</t>
+          <t>Rosemary was moved to tears at the sight of the</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>The sky has been overcast by thick clouds.</t>
+          <t>The sight of the miserable beggar moved</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>The sky overcast by thick clouds.</t>
+          <t>The sight of the miserable beggar has moved</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>The sky is overcast by thick clouds.</t>
+          <t>The sight of the miserable beggar moves</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>The sky is being overcast by thick clouds.</t>
+          <t>The sight of the miserable beggar had moved</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>The sky has been overcast by thick clouds.</t>
+          <t>The sight of the miserable beggar moved</t>
         </is>
       </c>
       <c r="H114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>64</v>
+        <v>3</v>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Who wrote this article?</t>
+          <t>The question paper for the eleventh standard was set by the history teacher</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Whom was this article written?</t>
+          <t>The history teacher set the question paper.</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>By whom this article was written. ?</t>
+          <t>The history teacher set the eleventh question</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Who was written this article?</t>
+          <t>The history teacher set the question paper</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>By whom was this article written?</t>
+          <t>The history teacher had the question paper</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>By whom was this article written?</t>
+          <t>The history teacher set the question paper</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>The object "this article" becomes the subject, and "wrote" changes to "was written."</t>
+          <t>The subject "the history teacher" performs the action, and "was set" changes to "set."</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>6</v>
+        <v>58</v>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Open the door.</t>
+          <t>All the letters were posted by them.</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Let the door should open.</t>
+          <t>They have posted all the letters.</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Let the door is opened.</t>
+          <t>They had posted all the letters.</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Let open the door.</t>
+          <t>They were posting all the letters.</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Let the door be opened.</t>
+          <t>They posted all the letters.</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Let the door be opened.</t>
+          <t>They posted all the letters.</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>In imperative sentences, "let" is used to form the passive voice.</t>
+          <t>The subject "they" performs the action, and "were posted" changes to "posted."</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>58</v>
+        <v>6</v>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>All the letters were posted by them.</t>
+          <t>Open the door.</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>They have posted all the letters.</t>
+          <t>Let the door should open.</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>They had posted all the letters.</t>
+          <t>Let the door is opened.</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>They were posting all the letters.</t>
+          <t>Let open the door.</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>They posted all the letters.</t>
+          <t>Let the door be opened.</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>They posted all the letters.</t>
+          <t>Let the door be opened.</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>The subject "they" performs the action, and "were posted" changes to "posted."</t>
+          <t>In imperative sentences, "let" is used to form the passive voice.</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>3</v>
+        <v>64</v>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>The question paper for the eleventh standard was set by the history teacher</t>
+          <t>Who wrote this article?</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>The history teacher set the question paper.</t>
+          <t>Whom was this article written?</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>The history teacher set the eleventh question</t>
+          <t>By whom this article was written. ?</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>The history teacher set the question paper</t>
+          <t>Who was written this article?</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>The history teacher had the question paper</t>
+          <t>By whom was this article written?</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>The history teacher set the question paper</t>
+          <t>By whom was this article written?</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>The subject "the history teacher" performs the action, and "was set" changes to "set."</t>
+          <t>The object "this article" becomes the subject, and "wrote" changes to "was written."</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>73</v>
+        <v>88</v>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Rosemary was moved to tears at the sight of the</t>
+          <t>Thick clouds have overcast the sky.</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>The sight of the miserable beggar moved</t>
+          <t>The sky has been overcast by thick clouds.</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>The sight of the miserable beggar has moved</t>
+          <t>The sky overcast by thick clouds.</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>The sight of the miserable beggar moves</t>
+          <t>The sky is overcast by thick clouds.</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>The sight of the miserable beggar had moved</t>
+          <t>The sky is being overcast by thick clouds.</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>The sight of the miserable beggar moved</t>
+          <t>The sky has been overcast by thick clouds.</t>
         </is>
       </c>
       <c r="H119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>61</v>
+        <v>24</v>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>My parents are advising me about my further studies</t>
+          <t>Can we send this big parcel by air?</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>I am being advised about my further studies by my parents.</t>
+          <t>Can this big parcel be sent by air?</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>I am advised by my parents about my further studies</t>
+          <t>Can this big parcel sent by air?</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>I was advised about my further studies by my parent</t>
+          <t>Could this big parcel be sent by air?</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>I had been advised about my further studies</t>
+          <t>Could this big parcel sent by us by air?</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>I am being advised about my further studies by my parents.</t>
+          <t>Can this big parcel be sent by air?</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>The object "me" becomes the subject, and "are advising" changes to "am being advised."</t>
+          <t>The object "this big parcel" becomes the subject, and "send" changes to "be sent."</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>The students were laughing at the old man.</t>
+          <t>People call him a fool.</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>The old man was being laughed at by the</t>
+          <t>He has been called a fool</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>The old man was laughed at by the students.</t>
+          <t>He is called a fool by the people.</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>The old man was being laughed by the</t>
+          <t>The people have been calling him a fool.</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>The old man is laughing at the students.</t>
+          <t>We all people have called him a fool</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>The old man was being laughed at by the</t>
-        </is>
-      </c>
-      <c r="H121" t="inlineStr"/>
+          <t>He is called a fool by the people.</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>The object "him" becomes the subject, and "call" changes to "is called."</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Look! They have painted the door.</t>
+          <t>They created such a fuss over a trivial matter.</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Look! The door’s being painted.</t>
+          <t>Such a fuss is being created over a trivial</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>Look! The door had been painted.</t>
+          <t>Such a fuss was created over a trivial matter.</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Look! The door has been painted.</t>
+          <t>Such a fuss has been created over a trivial</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Look ! The door was painted.</t>
+          <t>By them such a fuss has been created over a</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Look! The door has been painted.</t>
+          <t>Such a fuss was created over a trivial matter.</t>
         </is>
       </c>
       <c r="H122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>107</v>
+        <v>125</v>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Everyone admires our principal.</t>
+          <t>The problem has been treated by numerous</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Our principal has been admired by everyone.</t>
+          <t>Numerous experts have been treating the</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>Our principal was admired by everyone.</t>
+          <t>Numerous experts have treated the problem.</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Our principal is being admired by everyone.</t>
+          <t>Numerous experts had been treating the</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Our principal is admired by everyone.</t>
+          <t>Numerous experts treated the problem.</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Our principal is admired by everyone.</t>
+          <t>Numerous experts have treated the problem.</t>
         </is>
       </c>
       <c r="H123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>85</v>
+        <v>72</v>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>One should avoid honking the horn unnecessarily.</t>
+          <t>My watch can’t be repaired by anyone.</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Unnecessary honking of horn ought to be</t>
+          <t>No one will repair my watch.</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>Unnecessary honking of horn can be avoided.</t>
+          <t>No one can repair my watch.</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Unnecessary honking of horn should be</t>
+          <t>No one can’t repair my watch.</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Unnecessary honking of horn must be</t>
+          <t>No one will be able to repair my watch.</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Unnecessary honking of horn should be</t>
+          <t>No one can repair my watch.</t>
         </is>
       </c>
       <c r="H124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>28</v>
+        <v>119</v>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Promises should be kept.</t>
+          <t>Post the letter.</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>You must keep the premises.</t>
+          <t>The letter is posted.</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>We must keep the promises</t>
+          <t>The letter was posted.</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Keep the promises</t>
+          <t>Let the letter be posted.</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>One should keep the promises</t>
+          <t>The letter will be posted.</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>One should keep the promises</t>
-        </is>
-      </c>
-      <c r="H125" t="inlineStr">
-        <is>
-          <t>The subject "promises" becomes the object, and "should be kept" changes to "should keep."</t>
-        </is>
-      </c>
+          <t>Let the letter be posted.</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>44</v>
+        <v>122</v>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>They have published all the details of the report</t>
+          <t>The judge delivered the sentence at the courtroom</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>All the details of the report have been published by them</t>
+          <t>The sentence been delivered yesterday by the</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>The publication of the details of invention</t>
+          <t>The sentence was delivered by the judge at</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>All the details have been invented by the</t>
+          <t>The sentence was being delivered at the</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>All the inventions have been detailed by</t>
+          <t>Yesterday, the sentence had been delivered</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>All the details of the report have been published by them</t>
-        </is>
-      </c>
-      <c r="H126" t="inlineStr">
-        <is>
-          <t>The object "all the details of the report" becomes the subject, and "have published" changes to "have been published."</t>
-        </is>
-      </c>
+          <t>The sentence was delivered by the judge at</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>122</v>
+        <v>44</v>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>The judge delivered the sentence at the courtroom</t>
+          <t>They have published all the details of the report</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>The sentence been delivered yesterday by the</t>
+          <t>All the details of the report have been published by them</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>The sentence was delivered by the judge at</t>
+          <t>The publication of the details of invention</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>The sentence was being delivered at the</t>
+          <t>All the details have been invented by the</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Yesterday, the sentence had been delivered</t>
+          <t>All the inventions have been detailed by</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>The sentence was delivered by the judge at</t>
-        </is>
-      </c>
-      <c r="H127" t="inlineStr"/>
+          <t>All the details of the report have been published by them</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>The object "all the details of the report" becomes the subject, and "have published" changes to "have been published."</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>119</v>
+        <v>28</v>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Post the letter.</t>
+          <t>Promises should be kept.</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>The letter is posted.</t>
+          <t>You must keep the premises.</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>The letter was posted.</t>
+          <t>We must keep the promises</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Let the letter be posted.</t>
+          <t>Keep the promises</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>The letter will be posted.</t>
+          <t>One should keep the promises</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Let the letter be posted.</t>
-        </is>
-      </c>
-      <c r="H128" t="inlineStr"/>
+          <t>One should keep the promises</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>The subject "promises" becomes the object, and "should be kept" changes to "should keep."</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>72</v>
+        <v>85</v>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>My watch can’t be repaired by anyone.</t>
+          <t>One should avoid honking the horn unnecessarily.</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>No one will repair my watch.</t>
+          <t>Unnecessary honking of horn ought to be</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>No one can repair my watch.</t>
+          <t>Unnecessary honking of horn can be avoided.</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>No one can’t repair my watch.</t>
+          <t>Unnecessary honking of horn should be</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>No one will be able to repair my watch.</t>
+          <t>Unnecessary honking of horn must be</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>No one can repair my watch.</t>
+          <t>Unnecessary honking of horn should be</t>
         </is>
       </c>
       <c r="H129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>125</v>
+        <v>107</v>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>The problem has been treated by numerous</t>
+          <t>Everyone admires our principal.</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Numerous experts have been treating the</t>
+          <t>Our principal has been admired by everyone.</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>Numerous experts have treated the problem.</t>
+          <t>Our principal was admired by everyone.</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Numerous experts had been treating the</t>
+          <t>Our principal is being admired by everyone.</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Numerous experts treated the problem.</t>
+          <t>Our principal is admired by everyone.</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Numerous experts have treated the problem.</t>
+          <t>Our principal is admired by everyone.</t>
         </is>
       </c>
       <c r="H130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>They created such a fuss over a trivial matter.</t>
+          <t>Look! They have painted the door.</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Such a fuss is being created over a trivial</t>
+          <t>Look! The door’s being painted.</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>Such a fuss was created over a trivial matter.</t>
+          <t>Look! The door had been painted.</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Such a fuss has been created over a trivial</t>
+          <t>Look! The door has been painted.</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>By them such a fuss has been created over a</t>
+          <t>Look ! The door was painted.</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Such a fuss was created over a trivial matter.</t>
+          <t>Look! The door has been painted.</t>
         </is>
       </c>
       <c r="H131" t="inlineStr"/>

--- a/Data/NDA_active_passive_voice1.xlsx
+++ b/Data/NDA_active_passive_voice1.xlsx
@@ -472,4874 +472,4870 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>57</v>
+        <v>23</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>The Metro Rail is being constructed by the corporation</t>
+          <t>He admonished her for the error.</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>The Corporation has been constructing the metro rail</t>
+          <t>She was admonished by him for the error.</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>The Corporation is constructing the Metro rail</t>
+          <t>She has been admonished by him for the</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>The Corporation has constructed the Metro rail</t>
+          <t>She would be admonished by him for the</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>The Corporation was constructing the Metro rail</t>
+          <t>She is admonished by him for the error.</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>The Corporation is constructing the Metro rail</t>
+          <t>She was admonished by him for the error.</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>The subject "the corporation" becomes active, and "is being constructed" changes to "is constructing."</t>
+          <t>The object "her" becomes the subject, and "admonished" changes to "was admonished."</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>81</v>
+        <v>2</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>She was advised 15 days’ rest after her surgery.</t>
+          <t>The police caught the thief at last.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>The doctor was advised her 15 days’ rest after</t>
+          <t>At last the thief was caught by the police</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>The doctor has advised her 15 days’ rest after</t>
+          <t>The thief at last caught the police.</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>The doctor advised her 15 days’ rest after</t>
+          <t>The thief was at last caught by the police.</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>The doctor had advised her 15 days’ rest after</t>
+          <t>At last the thief by the police was caught.</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>The doctor advised her 15 days’ rest after</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr"/>
+          <t>At last the thief was caught by the police</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>"The police" is the subject, and "the thief" is the object. The verb "caught" changes to "was caught" in the passive form.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>16</v>
+        <v>84</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>The loan will be sanctioned by the bank.</t>
+          <t>Gandhiji started the Quit India Movement in 1942.</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>The bank sanctioned the loan.</t>
+          <t>The Quit India Movement was started by</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>The bank is going to sanction the loan.</t>
+          <t>The Quit India Movement was been started</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>The bank would sanction the loan.</t>
+          <t>The Quit India Movement had been started</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>The bank will sanction the loan.</t>
+          <t>The Quit India Movement started by</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>The bank will sanction the loan.</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>The subject "the bank" performs the action, and "will be sanctioned" changes to "will sanction."</t>
-        </is>
-      </c>
+          <t>The Quit India Movement was started by</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>He teaches us grammar.</t>
+          <t>One must keep one’s promises.</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Grammar is taught to us by him</t>
+          <t>One’s promises are kept</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>We are taught grammar by him.</t>
+          <t>One’s promises must kept</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Grammar will be taught of us by him.</t>
+          <t>One’s promises were kept</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>We were teached grammar by him.</t>
+          <t>One’s promises must be kept</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Grammar is taught to us by him</t>
+          <t>One’s promises must be kept</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>The object "grammar" becomes the subject, and "teaches" changes to "is taught."</t>
+          <t>The object "promises" becomes the subject, and "must keep" changes to "must be kept."</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130</v>
+        <v>47</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Sameer shut the door with a bang.</t>
+          <t>Prepare yourself for the worst.</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>The door was shut with a bang by Sameer.</t>
+          <t>You be prepared for the worst.</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>The door with a bang shut by Sameer.</t>
+          <t>The worst should be prepared by yourself.</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>The door shut Sameer with a bang.</t>
+          <t>Let yourself be prepared for the worst.</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>The door had been shut with a bang by</t>
+          <t>For the worst, preparation should be made</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>The door was shut with a bang by Sameer.</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr"/>
+          <t>Let yourself be prepared for the worst.</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Imperative sentences use "let" in passive voice</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>20</v>
+        <v>128</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>One cannot expect children to understand these problems</t>
+          <t>The company paid her a meagre salary.</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Children cannot be expected to understand</t>
+          <t>She was paid a meagre salary by the</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Children to understand these problems</t>
+          <t>A meagre salary has been paid to her by the</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Children cannot be expected to understand these problems</t>
+          <t>She was being paid a meagre salary by the</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>To understand these problems cannot be</t>
+          <t>A meagre salary was to be paid to her by the</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Children cannot be expected to understand these problems</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>The object "children" becomes the subject, and "cannot expect" changes to "cannot be expected."</t>
-        </is>
-      </c>
+          <t>She was paid a meagre salary by the</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>94</v>
+        <v>27</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>One should keep one’s promises.</t>
+          <t>You will be taken care of by me.</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Promises should be kept.</t>
+          <t>I will be taking care of you.</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>One’s promises should be kept.</t>
+          <t>I would take care of you.</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Keep the promises made by you.</t>
+          <t>I will take care of you.</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Promises be kept.</t>
+          <t>I will being take care of you.</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>One’s promises should be kept.</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr"/>
+          <t>I will take care of you.</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>The subject "you" becomes the object, and "will be taken care of" changes to "will take care of."</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>The boy laughed at the beggar.</t>
+          <t>We have decided to open a new branch</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>The beggar was laughed by the boy.</t>
+          <t>To open a new branch was decided by us.</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>The beggar was being laughed by the boy.</t>
+          <t>To be opened a new branch has been decided.</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>The beggar was being laughed at by the boy.</t>
+          <t>It has been decided to open a new branch.</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>The beggar was laughed at by the boy.</t>
+          <t>It may be decided to open a new branch by</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>The beggar was laughed at by the boy.</t>
+          <t>It has been decided to open a new branch.</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>The object "the beggar" becomes the subject, and "laughed at" changes to "was laughed at.</t>
+          <t>The object "a new branch" becomes the subject, and "have decided" changes to "has been decided to be open."</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>He would have written this essay in time.</t>
+          <t>Has anybody answered your question?</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>The essay was written on time.</t>
+          <t>Your question has been answered?</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>This essay would have been written by him in time</t>
+          <t>Anybody has answered your question?</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>The essay was written by him in time.</t>
+          <t>Has your question been answered by anybody?</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>He wrote the essay on time.</t>
+          <t>Have your answered you question ?</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>This essay would have been written by him in time</t>
+          <t>Has your question been answered by anybody?</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>The object "this essay" becomes the subject, and "would have written" changes to "would have been written."</t>
+          <t>The object "your question" becomes the subject, and "has answered" changes to "has been answered."</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>They do not accept credit cards everywhere.</t>
+          <t>Paint the windows.</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Credit cards are not being accepted</t>
+          <t>Windows should be painted.</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Credit cards were not accepted everywhere.</t>
+          <t>Let the windows be painted.</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Credit cards do not accept them everywhere.</t>
+          <t>Let be the windows painted.</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Credit cards are not accepted everywhere.</t>
+          <t>Windows are let to be painted.</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Credit cards are not accepted everywhere.</t>
+          <t>Let the windows be painted.</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>"They" is the subject, and "credit cards" is the object. In passive voice, the object becomes the subject, and the verb changes to "are not accepted."</t>
+          <t>In imperative sentences, "let" is used for passive voice.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>60</v>
+        <v>78</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>My books have been stolen.</t>
+          <t>The lightning caused a serious forest fire and</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Someone has stolen my books.</t>
+          <t>A serious forest fire has been caused by</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Someone stole my books.</t>
+          <t>A serious forest fire has been caused by lightning</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Someone have stolen my books.</t>
+          <t>A serious forest fire had been caused by</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>They stole my books.</t>
+          <t>A serious forest fire was caused by lightning</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Someone has stolen my books.</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>The subject "someone" is added, and "have been stolen" changes to "has stolen."</t>
-        </is>
-      </c>
+          <t>A serious forest fire was caused by lightning</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>55</v>
+        <v>127</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Your little boy broke my kitchen window this</t>
+          <t>Mother gave him a little puppy.</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>My kitchen window was broken by your little boy this morning.</t>
+          <t>He was given a little puppy by mother.</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>My kitchen window had been broken by your</t>
+          <t>A little puppy was being given to him by</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>My kitchen window is broken by you little</t>
+          <t>He had been given a little puppy by mother.</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>My kitchen window was being broken by</t>
+          <t>A little puppy is given to him by his mother.</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>My kitchen window was broken by your little boy this morning.</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>The object "my kitchen window" becomes the subject, and "broke" changes to "was broken."</t>
-        </is>
-      </c>
+          <t>He was given a little puppy by mother.</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>When did he finish this work?</t>
+          <t>Where did you buy this pen ?</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>When this work was finished by him?</t>
+          <t>Where shall you buy this pen ?</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>When was this work finished by him?</t>
+          <t>Where is this pen bought by you ?</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>When will this work be finished by him?</t>
+          <t>Where was this pen bought ?</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>When he finished this work?</t>
+          <t>Where will you buy this pen ?</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>When was this work finished by him?</t>
+          <t>Where was this pen bought ?</t>
         </is>
       </c>
       <c r="H14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>They are painting the walls.</t>
+          <t>The CEO’s son was kidnapped.</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>The walls are painting them.</t>
+          <t>Someone kidnapped the CEO’s son.</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>The walls are painted by them.</t>
+          <t>Someone has kidnapped the CEO’s son.</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>The walls are being painted by them.</t>
+          <t>Someone is going to kidnap the CEO’s son.</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>The walls in painted by them.</t>
+          <t>Someone is kidnapping the CEO’s son.</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>The walls are being painted by them.</t>
+          <t>Someone kidnapped the CEO’s son.</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>The object "the walls" becomes the subject, and "are painting" changes to "are being painted.</t>
+          <t>The subject "someone" is added to make the sentence active, and "was kidnapped" changes to "kidnapped."</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>96</v>
+        <v>8</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>One should not question his integrity.</t>
+          <t>The comic scenes in the play were overdone by the actor</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>His integrity should not be questioned by</t>
+          <t>The actors overdid the comic scenes in the</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>His integrity should not be questioned.</t>
+          <t>The actors overacted the comic scenes in the play</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>How can his integrity be questioned ?</t>
+          <t>The play was full of comic scenes.</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Who can doubt his integrity ?</t>
+          <t>The actors comically performed the play.</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>His integrity should not be questioned.</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr"/>
+          <t>The actors overacted the comic scenes in the play</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>The subject "the actors" becomes active, and "were overdone" changes to "overdid."</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>115</v>
+        <v>106</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Ads on TV increase the sale of any commodity.</t>
+          <t>How many languages are spoken in India?</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>The sale of any commodity is being increased</t>
+          <t>How many languages Indians are speaking</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>The sale of any commodity are increased by</t>
+          <t>How many languages Indians speak?</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>The sale of any commodity are being</t>
+          <t>How many languages do Indians speak?</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>The sale of any commodity is increased by</t>
+          <t>How many languages did Indians speak?</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>The sale of any commodity is increased by</t>
+          <t>How many languages do Indians speak?</t>
         </is>
       </c>
       <c r="H17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>One should not give unsolicited advice.</t>
+          <t>One should avoid honking the horn unnecessarily.</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Unsolicited advice is not to be given.</t>
+          <t>Unnecessary honking of horn ought to be</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Unsolicited advice can’t be given.</t>
+          <t>Unnecessary honking of horn can be avoided.</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Unsolicited advice may not be given.</t>
+          <t>Unnecessary honking of horn should be</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Unsolicited advice should not be given.</t>
+          <t>Unnecessary honking of horn must be</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Unsolicited advice should not be given.</t>
+          <t>Unnecessary honking of horn should be</t>
         </is>
       </c>
       <c r="H18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>112</v>
+        <v>20</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>The purity of justice is maintained by the reports</t>
+          <t>One cannot expect children to understand these problems</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>The law courts maintain purity of justice in</t>
+          <t>Children cannot be expected to understand</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>The reports of the proceedings of the law</t>
+          <t>Children to understand these problems</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Pure justice is maintained in the proceedings</t>
+          <t>Children cannot be expected to understand these problems</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>The maintenance of justice is pure in the</t>
+          <t>To understand these problems cannot be</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>The reports of the proceedings of the law</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr"/>
+          <t>Children cannot be expected to understand these problems</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>The object "children" becomes the subject, and "cannot expect" changes to "cannot be expected."</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>93</v>
+        <v>52</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>He abandoned his medical studies.</t>
+          <t>Two hundred people were arrested by the police.</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>His medical studies had abandoned.</t>
+          <t>The police have arrested two hundred people.</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>His medical studies are abandoned.</t>
+          <t>The police arrested two hundred people.</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>His medical studies have been abandoned.</t>
+          <t>The police had arrested two hundred people.</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>His medical studies were abandoned.</t>
+          <t>The police has arrested two hundred people.</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>His medical studies were abandoned.</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr"/>
+          <t>The police arrested two hundred people.</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>The subject "the police" becomes active, and "were arrested" changes to "arrested."</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121</v>
+        <v>64</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Nobody has answered my question.</t>
+          <t>Who wrote this article?</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>My question has been answered by</t>
+          <t>Whom was this article written?</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>My question has not been answered by</t>
+          <t>By whom this article was written. ?</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>My question was not answered.</t>
+          <t>Who was written this article?</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>My question remains unanswered.</t>
+          <t>By whom was this article written?</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>My question has not been answered by</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr"/>
+          <t>By whom was this article written?</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>The object "this article" becomes the subject, and "wrote" changes to "was written."</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>8</v>
+        <v>77</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>The comic scenes in the play were overdone by the actor</t>
+          <t>They created such a fuss over a trivial matter.</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>The actors overdid the comic scenes in the</t>
+          <t>Such a fuss is being created over a trivial</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>The actors overacted the comic scenes in the play</t>
+          <t>Such a fuss was created over a trivial matter.</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>The play was full of comic scenes.</t>
+          <t>Such a fuss has been created over a trivial</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>The actors comically performed the play.</t>
+          <t>By them such a fuss has been created over a</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>The actors overacted the comic scenes in the play</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>The subject "the actors" becomes active, and "were overdone" changes to "overdid."</t>
-        </is>
-      </c>
+          <t>Such a fuss was created over a trivial matter.</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>40</v>
+        <v>89</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Has anybody answered your question?</t>
+          <t>One should not give unsolicited advice.</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Your question has been answered?</t>
+          <t>Unsolicited advice is not to be given.</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Anybody has answered your question?</t>
+          <t>Unsolicited advice can’t be given.</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Has your question been answered by anybody?</t>
+          <t>Unsolicited advice may not be given.</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Have your answered you question ?</t>
+          <t>Unsolicited advice should not be given.</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Has your question been answered by anybody?</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>The object "your question" becomes the subject, and "has answered" changes to "has been answered."</t>
-        </is>
-      </c>
+          <t>Unsolicited advice should not be given.</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>27</v>
+        <v>121</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>You will be taken care of by me.</t>
+          <t>Nobody has answered my question.</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>I will be taking care of you.</t>
+          <t>My question has been answered by</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>I would take care of you.</t>
+          <t>My question has not been answered by</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>I will take care of you.</t>
+          <t>My question was not answered.</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>I will being take care of you.</t>
+          <t>My question remains unanswered.</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>I will take care of you.</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>The subject "you" becomes the object, and "will be taken care of" changes to "will take care of."</t>
-        </is>
-      </c>
+          <t>My question has not been answered by</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Call the police at once</t>
+          <t>The whole village was ravaged by the man-eater.</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Let the police be called at once.</t>
+          <t>The man-eater ravages the whole village.</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>The police was to be called at once.</t>
+          <t>The whole village is ravaged by the maneater.</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>The police is to be called at once.</t>
+          <t>The man-eater ravaged the whole village.</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Let the police called at once.</t>
+          <t>The whole village is being ravaged by the</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Let the police be called at once.</t>
+          <t>The man-eater ravaged the whole village.</t>
         </is>
       </c>
       <c r="H25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124</v>
+        <v>21</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>People use computers for various purposes.</t>
+          <t>Why did she break the garden wall?</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Computers are being used by people for</t>
+          <t>Why the garden wall was broken by her?</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Computers have been used by people for</t>
+          <t>Why had the garden wall been broken by</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Computers are used by people for various</t>
+          <t>Why was the garden wall broken by her?</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Computers will be used by people for various</t>
+          <t>Why will the garden wall be broken by her?</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Computers are used by people for various</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr"/>
+          <t>Why was the garden wall broken by her?</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>The object "the garden wall" becomes the subject, and "did break" changes to "was broken."</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129</v>
+        <v>103</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Do not insult him.</t>
+          <t>Jane Austen devoted her whole life to her</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Let he not be insulted.</t>
+          <t>Jane Austen’s whole life is devoted to her</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Let him not be insulted.</t>
+          <t>Jane Austen’s whole life had been devoted</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Let not he be insulted.</t>
+          <t>Jane Austen’s whole life was devoted to her</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Let not him be insulted.</t>
+          <t>Jane Austen’s whole life has devoted to her</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Let him not be insulted.</t>
+          <t>Jane Austen’s whole life was devoted to her</t>
         </is>
       </c>
       <c r="H27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>52</v>
+        <v>13</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Two hundred people were arrested by the police.</t>
+          <t>He had committed a mistake.</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>The police have arrested two hundred people.</t>
+          <t>A mistake had committed by him.</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>The police arrested two hundred people.</t>
+          <t>A mistake was committed by him.</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>The police had arrested two hundred people.</t>
+          <t>A mistake had been committed by him.</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>The police has arrested two hundred people.</t>
+          <t>A mistake has been committed by him</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>The police arrested two hundred people.</t>
+          <t>A mistake had been committed by him.</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>The subject "the police" becomes active, and "were arrested" changes to "arrested."</t>
+          <t>The object "a mistake" becomes the subject, and "had committed" changes to "had been committed."</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>51</v>
+        <v>119</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>They are considering your proposal,</t>
+          <t>Post the letter.</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Your proposal is being considered by them.</t>
+          <t>The letter is posted.</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>You proposal was being considered by them.</t>
+          <t>The letter was posted.</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Your proposal was considered by them.</t>
+          <t>Let the letter be posted.</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Your proposal is considered by them.</t>
+          <t>The letter will be posted.</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Your proposal is being considered by them.</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>The object "your proposal" becomes the subject, and "are considering" changes to "is being considered.</t>
-        </is>
-      </c>
+          <t>Let the letter be posted.</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>83</v>
+        <v>108</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>We had to stop all other work to complete our</t>
+          <t>The Manager granted me two days leave.</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>All other work has to be stopped by us to</t>
+          <t>I had been granted two days’ leave by the</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>All other work has stopped by us to complete</t>
+          <t>I have been granted two days’ leave by the</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>All other work had to be stopped by us to</t>
+          <t>I granted two days’ leave by the Manager.</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>All other work was stopped by us to complete</t>
+          <t>I was granted two days’ leave by the</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>All other work had to be stopped by us to</t>
+          <t>I was granted two days’ leave by the</t>
         </is>
       </c>
       <c r="H30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>When did he return my books ?</t>
+          <t>Today I accomplished my task successfully.</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>When were my books returned by him ?</t>
+          <t>Today my task is accomplished successfully</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>When will my books be returned by him ?</t>
+          <t>Today my task accomplished successfully.</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>When has he returned my books ?</t>
+          <t>Today my task was accomplished</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>When are my books returned by him ?</t>
+          <t>Today my task was accomplished
+successfully</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>When were my books returned by him ?</t>
+          <t>Today my task was accomplished
+successfully</t>
         </is>
       </c>
       <c r="H31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>42</v>
+        <v>81</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>One must keep one’s promises.</t>
+          <t>She was advised 15 days’ rest after her surgery.</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>One’s promises are kept</t>
+          <t>The doctor was advised her 15 days’ rest after</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>One’s promises must kept</t>
+          <t>The doctor has advised her 15 days’ rest after</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>One’s promises were kept</t>
+          <t>The doctor advised her 15 days’ rest after</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>One’s promises must be kept</t>
+          <t>The doctor had advised her 15 days’ rest after</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>One’s promises must be kept</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>The object "promises" becomes the subject, and "must keep" changes to "must be kept."</t>
-        </is>
-      </c>
+          <t>The doctor advised her 15 days’ rest after</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>43</v>
+        <v>58</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>The government has not approved the new drug</t>
+          <t>All the letters were posted by them.</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>The government approval for the sale of the</t>
+          <t>They have posted all the letters.</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>The new drug has not been approved by the government</t>
+          <t>They had posted all the letters.</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>For the sale of the new drug we have not</t>
+          <t>They were posting all the letters.</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>The new drug was not approved by the</t>
+          <t>They posted all the letters.</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>The new drug has not been approved by the government</t>
+          <t>They posted all the letters.</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>The object "the new drug" becomes the subject, and "has not approved" changes to "has not been approved."</t>
+          <t>The subject "they" performs the action, and "were posted" changes to "posted."</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>14</v>
+        <v>104</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>The most useful training of my career was given to me by my boss</t>
+          <t>Hamlet was written by Shakespeare.</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>My boss has been giving me the most useful</t>
+          <t>Shakespeare has written Hamlet.</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>My boss gives me the most useful training.</t>
+          <t>Shakespeare had written Hamlet.</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>My boss is giving me the most usefully</t>
+          <t>Shakespeare wrote Hamlet.</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>My boss gave me the most useful training of my career</t>
+          <t>Shakespeare writes Hamlet.</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>My boss gave me the most useful training of my career</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>The subject "the mentor" becomes active, and "was given" changes to "gave."</t>
-        </is>
-      </c>
+          <t>Shakespeare wrote Hamlet.</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>105</v>
+        <v>68</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>They are looking after the child jointly.</t>
+          <t>They are painting the walls.</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>The child is being looked after by them</t>
+          <t>The walls are painting them.</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>The child is looked after by them jointly</t>
+          <t>The walls are painted by them.</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>The child was being looked after by them</t>
+          <t>The walls are being painted by them.</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>The child had been looked after by them</t>
+          <t>The walls in painted by them.</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>The child is being looked after by them</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr"/>
+          <t>The walls are being painted by them.</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>The object "the walls" becomes the subject, and "are painting" changes to "are being painted.</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>103</v>
+        <v>30</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Jane Austen devoted her whole life to her</t>
+          <t>He would have written this essay in time.</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Jane Austen’s whole life is devoted to her</t>
+          <t>The essay was written on time.</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Jane Austen’s whole life had been devoted</t>
+          <t>This essay would have been written by him in time</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Jane Austen’s whole life was devoted to her</t>
+          <t>The essay was written by him in time.</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Jane Austen’s whole life has devoted to her</t>
+          <t>He wrote the essay on time.</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Jane Austen’s whole life was devoted to her</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr"/>
+          <t>This essay would have been written by him in time</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>The object "this essay" becomes the subject, and "would have written" changes to "would have been written."</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>49</v>
+        <v>130</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>It is impossible to do this.</t>
+          <t>Sameer shut the door with a bang.</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Doing this is impossible.</t>
+          <t>The door was shut with a bang by Sameer.</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>This is impossible to be done</t>
+          <t>The door with a bang shut by Sameer.</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>This must not be done</t>
+          <t>The door shut Sameer with a bang.</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>This can’t be done</t>
+          <t>The door had been shut with a bang by</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>This is impossible to be done</t>
+          <t>The door was shut with a bang by Sameer.</t>
         </is>
       </c>
       <c r="H37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>114</v>
+        <v>49</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>An awareness is being created among the people</t>
+          <t>It is impossible to do this.</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>The Government is creating an awareness</t>
+          <t>Doing this is impossible.</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>The Government are creating an awareness</t>
+          <t>This is impossible to be done</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>The Government creates an awareness</t>
+          <t>This must not be done</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>The Government created an awareness</t>
+          <t>This can’t be done</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>The Government is creating an awareness</t>
+          <t>This is impossible to be done</t>
         </is>
       </c>
       <c r="H38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>101</v>
+        <v>73</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>I was given a watch by my father.</t>
+          <t>Rosemary was moved to tears at the sight of the</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>My father gives me a watch.</t>
+          <t>The sight of the miserable beggar moved</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>My father has given me a watch.</t>
+          <t>The sight of the miserable beggar has moved</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>My father had given me a watch.</t>
+          <t>The sight of the miserable beggar moves</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>My father gave me a watch.</t>
+          <t>The sight of the miserable beggar had moved</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>My father gave me a watch.</t>
+          <t>The sight of the miserable beggar moved</t>
         </is>
       </c>
       <c r="H39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Who helps you in your daily chores?</t>
+          <t>Cigarettes cannot be sold here.</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>By who are you helped in your daily chores?</t>
+          <t>Nobody sold cigarettes here.</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>By whom are you helped in your daily</t>
+          <t>Nobody could sell cigarettes here.</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>By who you are helped in your daily chores?</t>
+          <t>Nobody can sell cigarettes here.</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>By whom you were helped in your daily</t>
+          <t>Anybody can’t sell cigarettes here.</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>By whom are you helped in your daily</t>
+          <t>Nobody can sell cigarettes here.</t>
         </is>
       </c>
       <c r="H40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>39</v>
+        <v>102</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>We have warned you.</t>
+          <t>Who helps you in your daily chores?</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>You have been warned by us</t>
+          <t>By who are you helped in your daily chores?</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>We have you warned.</t>
+          <t>By whom are you helped in your daily</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Warned you have been.</t>
+          <t>By who you are helped in your daily chores?</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Have you been warned.</t>
+          <t>By whom you were helped in your daily</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>You have been warned by us</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>The object "you" becomes the subject, and "have warned" changes to "have been warned.</t>
-        </is>
-      </c>
+          <t>By whom are you helped in your daily</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>66</v>
+        <v>53</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>The news surprised me.</t>
+          <t>The storm damaged the roof.</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>I am surprised by the news.</t>
+          <t>The roof is damaged by the storm.</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>I was surprised by the news.</t>
+          <t>The roof was damage by the storm.</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>The news was surprised by me.</t>
+          <t>The roof was damaged by the storm.</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>The news was a big surprise.</t>
+          <t>The roof would be damaged by the storm</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>I was surprised by the news.</t>
+          <t>The roof was damaged by the storm.</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>The object "me" becomes the subject, and "surprised" changes to "was surprised."</t>
+          <t>The object "the roof" becomes the subject, and "damaged" changes to "was damaged."</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>The burglar destroyed several items in the room.</t>
+          <t>We must respect the elders.</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Several items destroyed in the room by the</t>
+          <t>The elders deserve respect from us.</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Several items in the room were destroyed by the burglar</t>
+          <t>The elders must be respected.</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Including the carpet, several items in the</t>
+          <t>The elders must be respected by us.</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>The burglar, being destroyed several items</t>
+          <t>Respect the elders we must.</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Several items in the room were destroyed by the burglar</t>
+          <t>The elders must be respected by us.</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>The object "several items in the room" becomes the subject, and "destroyed" changes to "were destroyed."</t>
+          <t>The object "the elders" becomes the subject, and "must respect" changes to "must be respected."</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>67</v>
+        <v>80</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>I will have completed the task by tomorrow.</t>
+          <t>Look! They have painted the door.</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>The task will be completed by me by</t>
+          <t>Look! The door’s being painted.</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>By tomorrow the task will have been completed</t>
+          <t>Look! The door had been painted.</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>The task would be completed by me by tomorrow</t>
+          <t>Look! The door has been painted.</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>By tomorrow the task would have been  completed</t>
+          <t>Look ! The door was painted.</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>By tomorrow the task will have been completed</t>
-        </is>
-      </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>The object "the task" becomes the subject, and "will have completed" changes to "will have been completed</t>
-        </is>
-      </c>
+          <t>Look! The door has been painted.</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>21</v>
+        <v>74</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Why did she break the garden wall?</t>
+          <t>Could you pass the salt ?</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Why the garden wall was broken by her?</t>
+          <t>Could the salt been passed ?</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Why had the garden wall been broken by</t>
+          <t>Could the salt be passed by anyone ?</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Why was the garden wall broken by her?</t>
+          <t>Could the salt be past ?</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Why will the garden wall be broken by her?</t>
+          <t>Could the salt be passed ?</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Why was the garden wall broken by her?</t>
-        </is>
-      </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>The object "the garden wall" becomes the subject, and "did break" changes to "was broken."</t>
-        </is>
-      </c>
+          <t>Could the salt be passed ?</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>47</v>
+        <v>70</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Prepare yourself for the worst.</t>
+          <t>She learns music.</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>You be prepared for the worst.</t>
+          <t>Music was learnt by her.</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>The worst should be prepared by yourself.</t>
+          <t>Music was being learnt by her.</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Let yourself be prepared for the worst.</t>
+          <t>Music is being learnt by her.</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>For the worst, preparation should be made</t>
+          <t>Music is leant by her.</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Let yourself be prepared for the worst.</t>
-        </is>
-      </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>Imperative sentences use "let" in passive voice</t>
-        </is>
-      </c>
+          <t>Music is leant by her.</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>91</v>
+        <v>114</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>They were pulling down the old building.</t>
+          <t>An awareness is being created among the people</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>The old building has been pulled down.</t>
+          <t>The Government is creating an awareness</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>The old building is being pulled down.</t>
+          <t>The Government are creating an awareness</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>The old building was being pulled down.</t>
+          <t>The Government creates an awareness</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>The old building was pulled down.</t>
+          <t>The Government created an awareness</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>The old building was being pulled down.</t>
+          <t>The Government is creating an awareness</t>
         </is>
       </c>
       <c r="H47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>48</v>
+        <v>35</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Please shut the door and go to sleep.</t>
+          <t>They drew a circle in the morning.</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>The door is to be shut and you are to go to sleep</t>
+          <t>A circle was being drawn by them in the</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Let the door be shut and you be asleep</t>
+          <t>A circle was drawn by them in the morning.</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>You are requested to shut the door and go to sleep</t>
+          <t>In the morning a circle have been drawn by</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>The door is to be shut and you are requested</t>
+          <t>A circle has been drawing since morning.</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>You are requested to shut the door and go to sleep</t>
-        </is>
-      </c>
-      <c r="H48" t="inlineStr"/>
+          <t>A circle was drawn by them in the morning.</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>The object "a circle" becomes the subject, and "drew" changes to "was drawn."</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>The police caught the thief at last.</t>
+          <t>Circumstances forced him to resign his post.</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>At last the thief was caught by the police</t>
+          <t>Circumstances make him to resign his post.</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>The thief at last caught the police.</t>
+          <t>He was forced to resign his post by circumstances</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>The thief was at last caught by the police.</t>
+          <t>He is forced to resign his post.</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>At last the thief by the police was caught.</t>
+          <t>He is forced and resigned his post.</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>At last the thief was caught by the police</t>
+          <t>He was forced to resign his post by circumstances</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>"The police" is the subject, and "the thief" is the object. The verb "caught" changes to "was caught" in the passive form.</t>
+          <t>The object "him" becomes the subject, and "forced" changes to "was forced."</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>35</v>
+        <v>109</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>They drew a circle in the morning.</t>
+          <t>They should shoot the terrorists dead.</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>A circle was being drawn by them in the</t>
+          <t>The terrorists been shot dead by them.</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>A circle was drawn by them in the morning.</t>
+          <t>The terrorists should have been shot dead</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>In the morning a circle have been drawn by</t>
+          <t>The terrorists should be shot dead by them.</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>A circle has been drawing since morning.</t>
+          <t>The terrorists have been shot dead by them.</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>A circle was drawn by them in the morning.</t>
-        </is>
-      </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>The object "a circle" becomes the subject, and "drew" changes to "was drawn."</t>
-        </is>
-      </c>
+          <t>The terrorists should be shot dead by them.</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>78</v>
+        <v>99</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>The lightning caused a serious forest fire and</t>
+          <t>A big variety store was inaugurated by Sachin.</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>A serious forest fire has been caused by</t>
+          <t>Sachin inaugurated a big variety store.</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>A serious forest fire has been caused by lightning</t>
+          <t>Sachin had inaugurated a big variety store.</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>A serious forest fire had been caused by</t>
+          <t>Sachin has inaugurated a big variety store.</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>A serious forest fire was caused by lightning</t>
+          <t>Sachin inaugurate a big variety store.</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>A serious forest fire was caused by lightning</t>
+          <t>Sachin inaugurated a big variety store.</t>
         </is>
       </c>
       <c r="H51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Hamlet was written by Shakespeare.</t>
+          <t>Honey is made by bees.</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Shakespeare has written Hamlet.</t>
+          <t>Bees makes honey.</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Shakespeare had written Hamlet.</t>
+          <t>Bees made honey.</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Shakespeare wrote Hamlet.</t>
+          <t>Bees are making honey.</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Shakespeare writes Hamlet.</t>
+          <t>Bees make honey.</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Shakespeare wrote Hamlet.</t>
+          <t>Bees make honey.</t>
         </is>
       </c>
       <c r="H52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>106</v>
+        <v>116</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>How many languages are spoken in India?</t>
+          <t>The Indian Government is encouraging the</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>How many languages Indians are speaking</t>
+          <t>The Europeans are encouraged by the Indian</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>How many languages Indians speak?</t>
+          <t>The Europeans are encouraging by the Indian</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>How many languages do Indians speak?</t>
+          <t>The Europeans are being encouraged by the</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>How many languages did Indians speak?</t>
+          <t>The Europeans is being encouraged by the</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>How many languages do Indians speak?</t>
+          <t>The Europeans are being encouraged by the</t>
         </is>
       </c>
       <c r="H53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>70</v>
+        <v>26</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>She learns music.</t>
+          <t>We found him a good wife.</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Music was learnt by her.</t>
+          <t>He was found a good wife by us.</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Music was being learnt by her.</t>
+          <t>A good wife was found out by them.</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Music is being learnt by her.</t>
+          <t>A good wife found him.</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Music is leant by her.</t>
+          <t>A good wife was being found by us.</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Music is leant by her.</t>
-        </is>
-      </c>
-      <c r="H54" t="inlineStr"/>
+          <t>He was found a good wife by us.</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>The object "him" becomes the subject, and "found" changes to "was found."</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>56</v>
+        <v>3</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>The criminal has to obey the court.</t>
+          <t>The question paper for the eleventh standard was set by the history teacher</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>The court has to be obeyed by the criminal.</t>
+          <t>The history teacher set the question paper.</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>The court will have to be obeyed by the</t>
+          <t>The history teacher set the eleventh question</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>The court must be obeyed.</t>
+          <t>The history teacher set the question paper</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>The court will be obeyed.</t>
+          <t>The history teacher had the question paper</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>The court has to be obeyed by the criminal.</t>
+          <t>The history teacher set the question paper</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>The object "the court" becomes the subject, and "has to obey" changes to "has to be obeyed."</t>
+          <t>The subject "the history teacher" performs the action, and "was set" changes to "set."</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>We have decided to open a new branch</t>
+          <t>Somebody has stolen his book.</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>To open a new branch was decided by us.</t>
+          <t>His book was stolen.</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>To be opened a new branch has been decided.</t>
+          <t>His book was stolen by somebody.</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>It has been decided to open a new branch.</t>
+          <t>His book has been stolen.</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>It may be decided to open a new branch by</t>
+          <t>His book had been stolen by somebody.</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>It has been decided to open a new branch.</t>
+          <t>His book has been stolen.</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>The object "a new branch" becomes the subject, and "have decided" changes to "has been decided to be open."</t>
+          <t>The object "his book" becomes the subject, and the verb changes to "has been stolen."</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>98</v>
+        <v>7</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Cigarettes cannot be sold here.</t>
+          <t>‘The Titanic’ was hit by an iceberg.</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Nobody sold cigarettes here.</t>
+          <t>An iceberg hit “The Titanic’.</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Nobody could sell cigarettes here.</t>
+          <t>An iceberg was hit by ‘The Titanic.’`</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Nobody can sell cigarettes here.</t>
+          <t>An iceberg was being hit by ‘The Titanic’.</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Anybody can’t sell cigarettes here.</t>
+          <t>An iceberg was hitting ‘The Titanic.’</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Nobody can sell cigarettes here.</t>
-        </is>
-      </c>
-      <c r="H57" t="inlineStr"/>
+          <t>An iceberg hit “The Titanic’.</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>he subject "The Titanic" becomes the object, and "was hit" changes to "hit."</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>He admonished her for the error.</t>
+          <t>The boy laughed at the beggar.</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>She was admonished by him for the error.</t>
+          <t>The beggar was laughed by the boy.</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>She has been admonished by him for the</t>
+          <t>The beggar was being laughed by the boy.</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>She would be admonished by him for the</t>
+          <t>The beggar was being laughed at by the boy.</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>She is admonished by him for the error.</t>
+          <t>The beggar was laughed at by the boy.</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>She was admonished by him for the error.</t>
+          <t>The beggar was laughed at by the boy.</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>The object "her" becomes the subject, and "admonished" changes to "was admonished."</t>
+          <t>The object "the beggar" becomes the subject, and "laughed at" changes to "was laughed at.</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>18</v>
+        <v>125</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>The traitors should be shot dead.</t>
+          <t>The problem has been treated by numerous</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>They should have shot the traitors dead.</t>
+          <t>Numerous experts have been treating the</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>They shall shoot the traitors dead.</t>
+          <t>Numerous experts have treated the problem.</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>They should shoot the traitors dead.</t>
+          <t>Numerous experts had been treating the</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>They shot the traitors dead.</t>
+          <t>Numerous experts treated the problem.</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>They should shoot the traitors dead.</t>
-        </is>
-      </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>The subject "someone" performs the action, and "should be shot" changes to "should shoot."</t>
-        </is>
-      </c>
+          <t>Numerous experts have treated the problem.</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>123</v>
+        <v>97</v>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Shut all the doors and windows in the night.</t>
+          <t>I have been sent here by the editor of Tribune.</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Let all the doors and windows be shut in the</t>
+          <t>The editor of Tribune has send me here.</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>All the doors and windows may be shut in</t>
+          <t>The editor of Tribune sent me here.</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Let all the doors and windows remain shut</t>
+          <t>The editor of Tribune has sent me here.</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>All the doors and windows be shutted in</t>
+          <t>The editor of Tribune send me here.</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Let all the doors and windows be shut in the</t>
+          <t>The editor of Tribune has sent me here.</t>
         </is>
       </c>
       <c r="H60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>65</v>
+        <v>51</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>The house has been painted yellow by Nikil.</t>
+          <t>They are considering your proposal,</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Nikil had painted the house yellow.</t>
+          <t>Your proposal is being considered by them.</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Nikil has painted the house yellow.</t>
+          <t>You proposal was being considered by them.</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Nikil was painting yellow the house.</t>
+          <t>Your proposal was considered by them.</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Nikil has been painting yellow the house.</t>
+          <t>Your proposal is considered by them.</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Nikil has painted the house yellow.</t>
+          <t>Your proposal is being considered by them.</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>The subject "Nikhil" becomes active, and "has been painted" changes to "has painted."</t>
+          <t>The object "your proposal" becomes the subject, and "are considering" changes to "is being considered.</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>13</v>
+        <v>93</v>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>He had committed a mistake.</t>
+          <t>He abandoned his medical studies.</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>A mistake had committed by him.</t>
+          <t>His medical studies had abandoned.</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>A mistake was committed by him.</t>
+          <t>His medical studies are abandoned.</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>A mistake had been committed by him.</t>
+          <t>His medical studies have been abandoned.</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>A mistake has been committed by him</t>
+          <t>His medical studies were abandoned.</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>A mistake had been committed by him.</t>
-        </is>
-      </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>The object "a mistake" becomes the subject, and "had committed" changes to "had been committed."</t>
-        </is>
-      </c>
+          <t>His medical studies were abandoned.</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>They are going to build a new airport near the old</t>
+          <t>Who asked you to draft this letter ?</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>A new airport going to be built near the old</t>
+          <t>By who you are asked to draft this letter.</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>A new airport is being built near the old one.</t>
+          <t>By who have you been asked to draft this</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>A new airport will be built near the old one.</t>
+          <t>By whom were you asked to draft this letter</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>A new airport is going to be built near the</t>
+          <t>By whom you were asked to draft this letter.</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>A new airport is going to be built near the</t>
+          <t>By whom were you asked to draft this letter</t>
         </is>
       </c>
       <c r="H63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>84</v>
+        <v>117</v>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Gandhiji started the Quit India Movement in 1942.</t>
+          <t>He handed her a chair.</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>The Quit India Movement was started by</t>
+          <t>She was handed a chair by him.</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>The Quit India Movement was been started</t>
+          <t>He handed a chair to her.</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>The Quit India Movement had been started</t>
+          <t>He will hand a chair to her.</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>The Quit India Movement started by</t>
+          <t>A chair will be handed to her by him</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>The Quit India Movement was started by</t>
+          <t>She was handed a chair by him.</t>
         </is>
       </c>
       <c r="H64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>The box was dropped by the boy.</t>
+          <t>My books have been stolen.</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>The boy dropped the box.</t>
+          <t>Someone has stolen my books.</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>The boy drops the box.</t>
+          <t>Someone stole my books.</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>The boy has dropped the box.</t>
+          <t>Someone have stolen my books.</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>The boy is dropping the box.</t>
+          <t>They stole my books.</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>The boy dropped the box.</t>
+          <t>Someone has stolen my books.</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>The subject "the boy" becomes active, and "was dropped" changes to "dropped."</t>
+          <t>The subject "someone" is added, and "have been stolen" changes to "has stolen."</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Where did you buy this pen ?</t>
+          <t>One should not question his integrity.</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Where shall you buy this pen ?</t>
+          <t>His integrity should not be questioned by</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Where is this pen bought by you ?</t>
+          <t>His integrity should not be questioned.</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Where was this pen bought ?</t>
+          <t>How can his integrity be questioned ?</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Where will you buy this pen ?</t>
+          <t>Who can doubt his integrity ?</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Where was this pen bought ?</t>
+          <t>His integrity should not be questioned.</t>
         </is>
       </c>
       <c r="H66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>19</v>
+        <v>69</v>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Rahul is teaching the children in the slum areas.</t>
+          <t>The box was dropped by the boy.</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>The children in the slum areas are taught by</t>
+          <t>The boy dropped the box.</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>The children are taught by Rahul in the slum</t>
+          <t>The boy drops the box.</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>In the slum areas the children are learning</t>
+          <t>The boy has dropped the box.</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>The children in the slum areas are being taught by Rahul</t>
+          <t>The boy is dropping the box.</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>The children in the slum areas are being taught by Rahul</t>
+          <t>The boy dropped the box.</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>The object "the children in the slum areas" becomes the subject, and "is teaching" changes to "are being taught."</t>
+          <t>The subject "the boy" becomes active, and "was dropped" changes to "dropped."</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>126</v>
+        <v>94</v>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>She always cooks delicious food.</t>
+          <t>One should keep one’s promises.</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Delicious food is always cooked by her.</t>
+          <t>Promises should be kept.</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Delicious food is always being cooked by</t>
+          <t>One’s promises should be kept.</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Delicious food has been cooked by her.</t>
+          <t>Keep the promises made by you.</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Delicious food was being cooked by her.</t>
+          <t>Promises be kept.</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Delicious food is always cooked by her.</t>
+          <t>One’s promises should be kept.</t>
         </is>
       </c>
       <c r="H68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>46</v>
+        <v>126</v>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>The manager could not accept the union leader’s proposal</t>
+          <t>She always cooks delicious food.</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>The union leader’s proposal could not be accepted by the manager</t>
+          <t>Delicious food is always cooked by her.</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>The union leader’s proposals were not</t>
+          <t>Delicious food is always being cooked by</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>The union leader’s proposals will not be</t>
+          <t>Delicious food has been cooked by her.</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>The union leader’s proposals would not be</t>
+          <t>Delicious food was being cooked by her.</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>The union leader’s proposal could not be accepted by the manager</t>
-        </is>
-      </c>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>The object "the union leader’s proposal" becomes the subject, and "could not accept" changes to "could not be accepted."</t>
-        </is>
-      </c>
+          <t>Delicious food is always cooked by her.</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>31</v>
+        <v>86</v>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Our task had been completed before sunset.</t>
+          <t>Gagan Narang and Vijay won bronze medals in</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>We completed our task before sunset.</t>
+          <t>Bronze medals won by Gagan Narang and</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>We have completed our task before sunset.</t>
+          <t>Bronze medals had been won by Gagan</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>We complete our task before sunset.</t>
+          <t>Bronze medals were won by Gagan Narang</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>We had completed our task before sunset.</t>
+          <t>Bronze medals have been won by Gagan</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>We had completed our task before sunset.</t>
-        </is>
-      </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>The subject "our task" becomes the object, and "had been completed" changes to "had completed</t>
-        </is>
-      </c>
+          <t>Bronze medals were won by Gagan Narang</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>62</v>
+        <v>19</v>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>We waste much time on social websites.</t>
+          <t>Rahul is teaching the children in the slum areas.</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Much time was wasted on social websites.</t>
+          <t>The children in the slum areas are taught by</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Much time will be wasted on social websites.</t>
+          <t>The children are taught by Rahul in the slum</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Much time is wasted by us on social websites</t>
+          <t>In the slum areas the children are learning</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Much time is being wasted y us on social websites</t>
+          <t>The children in the slum areas are being taught by Rahul</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Much time is wasted by us on social websites</t>
+          <t>The children in the slum areas are being taught by Rahul</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>The object "much time" becomes the subject, and "waste" changes to "is wasted."</t>
+          <t>The object "the children in the slum areas" becomes the subject, and "is teaching" changes to "are being taught."</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>They will demolish the entire block.</t>
+          <t>The government has not approved the new drug</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>The entire block is being demolished</t>
+          <t>The government approval for the sale of the</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>The block may be demolished entirely.</t>
+          <t>The new drug has not been approved by the government</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>The entire block will have to be demolished</t>
+          <t>For the sale of the new drug we have not</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>The entire block will be demolished by them.</t>
+          <t>The new drug was not approved by the</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>The entire block will be demolished by them.</t>
+          <t>The new drug has not been approved by the government</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>The object "the entire block" becomes the subject, and "will demolish" changes to "will be demolished.</t>
+          <t>The object "the new drug" becomes the subject, and "has not approved" changes to "has not been approved."</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>26</v>
+        <v>87</v>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>We found him a good wife.</t>
+          <t>The modern means of communication have made</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>He was found a good wife by us.</t>
+          <t>Life had been made so much easier by the</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>A good wife was found out by them.</t>
+          <t>Life is being so much easier by the modern</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>A good wife found him.</t>
+          <t>Life has been made so much easier by the</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>A good wife was being found by us.</t>
+          <t>Life was made so much easier by the modern</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>He was found a good wife by us.</t>
-        </is>
-      </c>
-      <c r="H73" t="inlineStr">
-        <is>
-          <t>The object "him" becomes the subject, and "found" changes to "was found."</t>
-        </is>
-      </c>
+          <t>Life has been made so much easier by the</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Circumstances forced him to resign his post.</t>
+          <t>The burglar destroyed several items in the room.</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Circumstances make him to resign his post.</t>
+          <t>Several items destroyed in the room by the</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>He was forced to resign his post by circumstances</t>
+          <t>Several items in the room were destroyed by the burglar</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>He is forced to resign his post.</t>
+          <t>Including the carpet, several items in the</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>He is forced and resigned his post.</t>
+          <t>The burglar, being destroyed several items</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>He was forced to resign his post by circumstances</t>
+          <t>Several items in the room were destroyed by the burglar</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>The object "him" becomes the subject, and "forced" changes to "was forced."</t>
+          <t>The object "several items in the room" becomes the subject, and "destroyed" changes to "were destroyed."</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>The boys saved many elders from drowning.</t>
+          <t>The boys were playing cricket.</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Many elders are saved from drowning by the</t>
+          <t>Cricket had been played by the boys.</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Many elders are being saved from drowning</t>
+          <t>Cricket has been played by the boys.</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Many elders were saved from drowning by the boys</t>
+          <t>Cricket was played by the boys.</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Many elders have been saved from drowning</t>
+          <t>Cricket was being played by the boys.</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Many elders were saved from drowning by the boys</t>
+          <t>Cricket was being played by the boys.</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>The object "many elders" becomes the subject, and "saved" changes to "were saved</t>
+          <t>The object "cricket" becomes the subject, and "were playing" changes to "was being played.</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>99</v>
+        <v>45</v>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>A big variety store was inaugurated by Sachin.</t>
+          <t>He teaches us grammar.</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Sachin inaugurated a big variety store.</t>
+          <t>Grammar is taught to us by him</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Sachin had inaugurated a big variety store.</t>
+          <t>We are taught grammar by him.</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Sachin has inaugurated a big variety store.</t>
+          <t>Grammar will be taught of us by him.</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Sachin inaugurate a big variety store.</t>
+          <t>We were teached grammar by him.</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Sachin inaugurated a big variety store.</t>
-        </is>
-      </c>
-      <c r="H76" t="inlineStr"/>
+          <t>Grammar is taught to us by him</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>The object "grammar" becomes the subject, and "teaches" changes to "is taught."</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>The doctor advised her to take rest.</t>
+          <t>Can we send this big parcel by air?</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>She has been advised rest by the doctor.</t>
+          <t>Can this big parcel be sent by air?</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>She was advised to be taken ret by the doctor.</t>
+          <t>Can this big parcel sent by air?</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>She was advised to take rest by the doctor.</t>
+          <t>Could this big parcel be sent by air?</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>She has been advised to take rest by the</t>
+          <t>Could this big parcel sent by us by air?</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>She was advised to take rest by the doctor.</t>
+          <t>Can this big parcel be sent by air?</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>The object "her" becomes the subject, and "advised" changes to "was advised."</t>
+          <t>The object "this big parcel" becomes the subject, and "send" changes to "be sent."</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>38</v>
+        <v>75</v>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>We must respect the elders.</t>
+          <t>Don’t subject the animals to cruelty.</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>The elders deserve respect from us.</t>
+          <t>The animals are not to be subjected to</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>The elders must be respected.</t>
+          <t>The animals shall not be subjected to cruelty.</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>The elders must be respected by us.</t>
+          <t>The animals will not be subjected to cruelty.</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Respect the elders we must.</t>
+          <t>The animals should not be subjected to</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>The elders must be respected by us.</t>
-        </is>
-      </c>
-      <c r="H78" t="inlineStr">
-        <is>
-          <t>The object "the elders" becomes the subject, and "must respect" changes to "must be respected."</t>
-        </is>
-      </c>
+          <t>The animals should not be subjected to</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>‘The Titanic’ was hit by an iceberg.</t>
+          <t>Open the door.</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>An iceberg hit “The Titanic’.</t>
+          <t>Let the door should open.</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>An iceberg was hit by ‘The Titanic.’`</t>
+          <t>Let the door is opened.</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>An iceberg was being hit by ‘The Titanic’.</t>
+          <t>Let open the door.</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>An iceberg was hitting ‘The Titanic.’</t>
+          <t>Let the door be opened.</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>An iceberg hit “The Titanic’.</t>
+          <t>Let the door be opened.</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>he subject "The Titanic" becomes the object, and "was hit" changes to "hit."</t>
+          <t>In imperative sentences, "let" is used to form the passive voice.</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>87</v>
+        <v>56</v>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>The modern means of communication have made</t>
+          <t>The criminal has to obey the court.</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Life had been made so much easier by the</t>
+          <t>The court has to be obeyed by the criminal.</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Life is being so much easier by the modern</t>
+          <t>The court will have to be obeyed by the</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Life has been made so much easier by the</t>
+          <t>The court must be obeyed.</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Life was made so much easier by the modern</t>
+          <t>The court will be obeyed.</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Life has been made so much easier by the</t>
-        </is>
-      </c>
-      <c r="H80" t="inlineStr"/>
+          <t>The court has to be obeyed by the criminal.</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>The object "the court" becomes the subject, and "has to obey" changes to "has to be obeyed."</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>117</v>
+        <v>91</v>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>He handed her a chair.</t>
+          <t>They were pulling down the old building.</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>She was handed a chair by him.</t>
+          <t>The old building has been pulled down.</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>He handed a chair to her.</t>
+          <t>The old building is being pulled down.</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>He will hand a chair to her.</t>
+          <t>The old building was being pulled down.</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>A chair will be handed to her by him</t>
+          <t>The old building was pulled down.</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>She was handed a chair by him.</t>
+          <t>The old building was being pulled down.</t>
         </is>
       </c>
       <c r="H81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>128</v>
+        <v>112</v>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>The company paid her a meagre salary.</t>
+          <t>The purity of justice is maintained by the reports</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>She was paid a meagre salary by the</t>
+          <t>The law courts maintain purity of justice in</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>A meagre salary has been paid to her by the</t>
+          <t>The reports of the proceedings of the law</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>She was being paid a meagre salary by the</t>
+          <t>Pure justice is maintained in the proceedings</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>A meagre salary was to be paid to her by the</t>
+          <t>The maintenance of justice is pure in the</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>She was paid a meagre salary by the</t>
+          <t>The reports of the proceedings of the law</t>
         </is>
       </c>
       <c r="H82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>90</v>
+        <v>55</v>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>The scheme permits investors to buy the shares</t>
+          <t>Your little boy broke my kitchen window this</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Under the scheme the investors may be</t>
+          <t>My kitchen window was broken by your little boy this morning.</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Under the scheme the investors have been</t>
+          <t>My kitchen window had been broken by your</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Under the scheme the investors are permitted</t>
+          <t>My kitchen window is broken by you little</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Under the scheme the investors were</t>
+          <t>My kitchen window was being broken by</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Under the scheme the investors are permitted</t>
-        </is>
-      </c>
-      <c r="H83" t="inlineStr"/>
+          <t>My kitchen window was broken by your little boy this morning.</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>The object "my kitchen window" becomes the subject, and "broke" changes to "was broken."</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Newton wrote this letter yesterday.</t>
+          <t>Ads on TV increase the sale of any commodity.</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Yesterday was written letter by Newton.</t>
+          <t>The sale of any commodity is being increased</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>This letter is written by Newton yesterday.</t>
+          <t>The sale of any commodity are increased by</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>This letter was written by Newton yesterday.</t>
+          <t>The sale of any commodity are being</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>This letter was wrote by Newton yesterday.</t>
+          <t>The sale of any commodity is increased by</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>This letter was written by Newton yesterday.</t>
+          <t>The sale of any commodity is increased by</t>
         </is>
       </c>
       <c r="H84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>95</v>
+        <v>9</v>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>The thief was caught.</t>
+          <t>My watch has been stolen.</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>The policeman may have caught the thief.</t>
+          <t>Someone has stolen my watch.</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>The policeman caught the thief.</t>
+          <t>They have stolen my watch.</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>The policeman has caught the thief.</t>
+          <t>The watch has been stolen by him.</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>The policeman had caught the thief.</t>
+          <t>Somebody have stolen my watch.</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>The policeman caught the thief.</t>
-        </is>
-      </c>
-      <c r="H85" t="inlineStr"/>
+          <t>Someone has stolen my watch.</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>The subject "someone" becomes explicit, and "has been stolen" changes to "has stolen."</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>116</v>
+        <v>36</v>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>The Indian Government is encouraging the</t>
+          <t>They will demolish the entire block.</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>The Europeans are encouraged by the Indian</t>
+          <t>The entire block is being demolished</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>The Europeans are encouraging by the Indian</t>
+          <t>The block may be demolished entirely.</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>The Europeans are being encouraged by the</t>
+          <t>The entire block will have to be demolished</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>The Europeans is being encouraged by the</t>
+          <t>The entire block will be demolished by them.</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>The Europeans are being encouraged by the</t>
-        </is>
-      </c>
-      <c r="H86" t="inlineStr"/>
+          <t>The entire block will be demolished by them.</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>The object "the entire block" becomes the subject, and "will demolish" changes to "will be demolished.</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>50</v>
+        <v>120</v>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>We must take care of all living species on Earth.</t>
+          <t>Who painted it?</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>All living species on Earth are taken care of</t>
+          <t>It was painted?</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>All living species on Earth must be taken care of by us</t>
+          <t>Was it painted?</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>All living species on Earth had been taken</t>
+          <t>Had it been painted by?</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>All living species on Earth will be taken care</t>
+          <t>By whom was it painted?</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>All living species on Earth must be taken care of by us</t>
-        </is>
-      </c>
-      <c r="H87" t="inlineStr">
-        <is>
-          <t>The object "all living species on Earth" becomes the subject, and "must take care of" changes to "must be taken care of</t>
-        </is>
-      </c>
+          <t>By whom was it painted?</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>74</v>
+        <v>33</v>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Could you pass the salt ?</t>
+          <t>The government has launched a massive tribal</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Could the salt been passed ?</t>
+          <t>A massive tribal welfare programme is</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Could the salt be passed by anyone ?</t>
+          <t>A massive tribal welfare program has been launched by the government.</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Could the salt be past ?</t>
+          <t>Jharkhand government has launched a</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Could the salt be passed ?</t>
+          <t>The government in Jharkhand has launched</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Could the salt be passed ?</t>
-        </is>
-      </c>
-      <c r="H88" t="inlineStr"/>
+          <t>A massive tribal welfare program has been launched by the government.</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>The object "a massive tribal welfare program" becomes the subject, and "has launched" changes to "has been launched</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Paint the windows.</t>
+          <t>Promises should be kept.</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Windows should be painted.</t>
+          <t>You must keep the premises.</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Let the windows be painted.</t>
+          <t>We must keep the promises</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Let be the windows painted.</t>
+          <t>Keep the promises</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Windows are let to be painted.</t>
+          <t>One should keep the promises</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Let the windows be painted.</t>
+          <t>One should keep the promises</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>In imperative sentences, "let" is used for passive voice.</t>
+          <t>The subject "promises" becomes the object, and "should be kept" changes to "should keep."</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>97</v>
+        <v>31</v>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>I have been sent here by the editor of Tribune.</t>
+          <t>Our task had been completed before sunset.</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>The editor of Tribune has send me here.</t>
+          <t>We completed our task before sunset.</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>The editor of Tribune sent me here.</t>
+          <t>We have completed our task before sunset.</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>The editor of Tribune has sent me here.</t>
+          <t>We complete our task before sunset.</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>The editor of Tribune send me here.</t>
+          <t>We had completed our task before sunset.</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>The editor of Tribune has sent me here.</t>
-        </is>
-      </c>
-      <c r="H90" t="inlineStr"/>
+          <t>We had completed our task before sunset.</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>The subject "our task" becomes the object, and "had been completed" changes to "had completed</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>12</v>
+        <v>82</v>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>It is being read by us.</t>
+          <t>When did he return my books ?</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>We are reading it.</t>
+          <t>When were my books returned by him ?</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>It will be read by us.</t>
+          <t>When will my books be returned by him ?</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>We can read it.</t>
+          <t>When has he returned my books ?</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>We have to read it.</t>
+          <t>When are my books returned by him ?</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>We are reading it.</t>
-        </is>
-      </c>
-      <c r="H91" t="inlineStr">
-        <is>
-          <t>The subject "we" performs the action, and "is being read" changes to "are reading."</t>
-        </is>
-      </c>
+          <t>When were my books returned by him ?</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Somebody has stolen his book.</t>
+          <t>The students were laughing at the old man.</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>His book was stolen.</t>
+          <t>The old man was being laughed at by the</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>His book was stolen by somebody.</t>
+          <t>The old man was laughed at by the students.</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>His book has been stolen.</t>
+          <t>The old man was being laughed by the</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>His book had been stolen by somebody.</t>
+          <t>The old man is laughing at the students.</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>His book has been stolen.</t>
-        </is>
-      </c>
-      <c r="H92" t="inlineStr">
-        <is>
-          <t>The object "his book" becomes the subject, and the verb changes to "has been stolen."</t>
-        </is>
-      </c>
+          <t>The old man was being laughed at by the</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>79</v>
+        <v>105</v>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Today I accomplished my task successfully.</t>
+          <t>They are looking after the child jointly.</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Today my task is accomplished successfully</t>
+          <t>The child is being looked after by them</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Today my task accomplished successfully.</t>
+          <t>The child is looked after by them jointly</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Today my task was accomplished</t>
+          <t>The child was being looked after by them</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Today my task was accomplished
-successfully</t>
+          <t>The child had been looked after by them</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Today my task was accomplished
-successfully</t>
+          <t>The child is being looked after by them</t>
         </is>
       </c>
       <c r="H93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>75</v>
+        <v>12</v>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Don’t subject the animals to cruelty.</t>
+          <t>It is being read by us.</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>The animals are not to be subjected to</t>
+          <t>We are reading it.</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>The animals shall not be subjected to cruelty.</t>
+          <t>It will be read by us.</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>The animals will not be subjected to cruelty.</t>
+          <t>We can read it.</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>The animals should not be subjected to</t>
+          <t>We have to read it.</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>The animals should not be subjected to</t>
-        </is>
-      </c>
-      <c r="H94" t="inlineStr"/>
+          <t>We are reading it.</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>The subject "we" performs the action, and "is being read" changes to "are reading."</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>54</v>
+        <v>90</v>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>People speak English all over the world.</t>
+          <t>The scheme permits investors to buy the shares</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>English was spoken all over the world.</t>
+          <t>Under the scheme the investors may be</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>English have been spoken all over the world.</t>
+          <t>Under the scheme the investors have been</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>English has been spoken all over the world.</t>
+          <t>Under the scheme the investors are permitted</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>English is spoken all over the world by people</t>
+          <t>Under the scheme the investors were</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>English is spoken all over the world by people</t>
-        </is>
-      </c>
-      <c r="H95" t="inlineStr">
-        <is>
-          <t>The object "English" becomes the subject, and "speak" changes to "is spoken."</t>
-        </is>
-      </c>
+          <t>Under the scheme the investors are permitted</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>63</v>
+        <v>129</v>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>A great deal of harm is caused to the environment</t>
+          <t>Do not insult him.</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>We have caused a great deal of harm to the environment</t>
+          <t>Let he not be insulted.</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>The environment causes a great deal of harm</t>
+          <t>Let him not be insulted.</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>We cause a great deal of harm to the environment</t>
+          <t>Let not he be insulted.</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>The environment is being caused a great deal harm</t>
+          <t>Let not him be insulted.</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>We cause a great deal of harm to the environment</t>
-        </is>
-      </c>
-      <c r="H96" t="inlineStr">
-        <is>
-          <t>The subject "human activities" becomes active, and "is caused" changes to "cause."</t>
-        </is>
-      </c>
+          <t>Let him not be insulted.</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>111</v>
+        <v>10</v>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>The whole village was ravaged by the man-eater.</t>
+          <t>The doctor advised her to take rest.</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>The man-eater ravages the whole village.</t>
+          <t>She has been advised rest by the doctor.</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>The whole village is ravaged by the maneater.</t>
+          <t>She was advised to be taken ret by the doctor.</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>The man-eater ravaged the whole village.</t>
+          <t>She was advised to take rest by the doctor.</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>The whole village is being ravaged by the</t>
+          <t>She has been advised to take rest by the</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>The man-eater ravaged the whole village.</t>
-        </is>
-      </c>
-      <c r="H97" t="inlineStr"/>
+          <t>She was advised to take rest by the doctor.</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>The object "her" becomes the subject, and "advised" changes to "was advised."</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>120</v>
+        <v>66</v>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Who painted it?</t>
+          <t>The news surprised me.</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>It was painted?</t>
+          <t>I am surprised by the news.</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Was it painted?</t>
+          <t>I was surprised by the news.</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Had it been painted by?</t>
+          <t>The news was surprised by me.</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>By whom was it painted?</t>
+          <t>The news was a big surprise.</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>By whom was it painted?</t>
-        </is>
-      </c>
-      <c r="H98" t="inlineStr"/>
+          <t>I was surprised by the news.</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>The object "me" becomes the subject, and "surprised" changes to "was surprised."</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>53</v>
+        <v>118</v>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>The storm damaged the roof.</t>
+          <t>Call the police at once</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>The roof is damaged by the storm.</t>
+          <t>Let the police be called at once.</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>The roof was damage by the storm.</t>
+          <t>The police was to be called at once.</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>The roof was damaged by the storm.</t>
+          <t>The police is to be called at once.</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>The roof would be damaged by the storm</t>
+          <t>Let the police called at once.</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>The roof was damaged by the storm.</t>
-        </is>
-      </c>
-      <c r="H99" t="inlineStr">
-        <is>
-          <t>The object "the roof" becomes the subject, and "damaged" changes to "was damaged."</t>
-        </is>
-      </c>
+          <t>Let the police be called at once.</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>109</v>
+        <v>1</v>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>They should shoot the terrorists dead.</t>
+          <t>They do not accept credit cards everywhere.</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>The terrorists been shot dead by them.</t>
+          <t>Credit cards are not being accepted</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>The terrorists should have been shot dead</t>
+          <t>Credit cards were not accepted everywhere.</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>The terrorists should be shot dead by them.</t>
+          <t>Credit cards do not accept them everywhere.</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>The terrorists have been shot dead by them.</t>
+          <t>Credit cards are not accepted everywhere.</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>The terrorists should be shot dead by them.</t>
-        </is>
-      </c>
-      <c r="H100" t="inlineStr"/>
+          <t>Credit cards are not accepted everywhere.</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>"They" is the subject, and "credit cards" is the object. In passive voice, the object becomes the subject, and the verb changes to "are not accepted."</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>76</v>
+        <v>54</v>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Who asked you to draft this letter ?</t>
+          <t>People speak English all over the world.</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>By who you are asked to draft this letter.</t>
+          <t>English was spoken all over the world.</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>By who have you been asked to draft this</t>
+          <t>English have been spoken all over the world.</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>By whom were you asked to draft this letter</t>
+          <t>English has been spoken all over the world.</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>By whom you were asked to draft this letter.</t>
+          <t>English is spoken all over the world by people</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>By whom were you asked to draft this letter</t>
-        </is>
-      </c>
-      <c r="H101" t="inlineStr"/>
+          <t>English is spoken all over the world by people</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>The object "English" becomes the subject, and "speak" changes to "is spoken."</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>34</v>
+        <v>100</v>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>The boys were playing cricket.</t>
+          <t>When did he finish this work?</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Cricket had been played by the boys.</t>
+          <t>When this work was finished by him?</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Cricket has been played by the boys.</t>
+          <t>When was this work finished by him?</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Cricket was played by the boys.</t>
+          <t>When will this work be finished by him?</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Cricket was being played by the boys.</t>
+          <t>When he finished this work?</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Cricket was being played by the boys.</t>
-        </is>
-      </c>
-      <c r="H102" t="inlineStr">
-        <is>
-          <t>The object "cricket" becomes the subject, and "were playing" changes to "was being played.</t>
-        </is>
-      </c>
+          <t>When was this work finished by him?</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>86</v>
+        <v>67</v>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Gagan Narang and Vijay won bronze medals in</t>
+          <t>I will have completed the task by tomorrow.</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Bronze medals won by Gagan Narang and</t>
+          <t>The task will be completed by me by</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Bronze medals had been won by Gagan</t>
+          <t>By tomorrow the task will have been completed</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Bronze medals were won by Gagan Narang</t>
+          <t>The task would be completed by me by tomorrow</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Bronze medals have been won by Gagan</t>
+          <t>By tomorrow the task would have been  completed</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Bronze medals were won by Gagan Narang</t>
-        </is>
-      </c>
-      <c r="H103" t="inlineStr"/>
+          <t>By tomorrow the task will have been completed</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>The object "the task" becomes the subject, and "will have completed" changes to "will have been completed</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>108</v>
+        <v>11</v>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>The Manager granted me two days leave.</t>
+          <t>People call him a fool.</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>I had been granted two days’ leave by the</t>
+          <t>He has been called a fool</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>I have been granted two days’ leave by the</t>
+          <t>He is called a fool by the people.</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>I granted two days’ leave by the Manager.</t>
+          <t>The people have been calling him a fool.</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>I was granted two days’ leave by the</t>
+          <t>We all people have called him a fool</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>I was granted two days’ leave by the</t>
-        </is>
-      </c>
-      <c r="H104" t="inlineStr"/>
+          <t>He is called a fool by the people.</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>The object "him" becomes the subject, and "call" changes to "is called."</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>127</v>
+        <v>72</v>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Mother gave him a little puppy.</t>
+          <t>My watch can’t be repaired by anyone.</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>He was given a little puppy by mother.</t>
+          <t>No one will repair my watch.</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>A little puppy was being given to him by</t>
+          <t>No one can repair my watch.</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>He had been given a little puppy by mother.</t>
+          <t>No one can’t repair my watch.</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>A little puppy is given to him by his mother.</t>
+          <t>No one will be able to repair my watch.</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>He was given a little puppy by mother.</t>
+          <t>No one can repair my watch.</t>
         </is>
       </c>
       <c r="H105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>5</v>
+        <v>71</v>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>We will telecast the programme next Sunday at 4</t>
+          <t>They are going to build a new airport near the old</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>The programme will be telecast by us next sunday at 4pm</t>
+          <t>A new airport going to be built near the old</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>The programme would be telecast by us next</t>
+          <t>A new airport is being built near the old one.</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>The programme will be telecasted by us next</t>
+          <t>A new airport will be built near the old one.</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>The programme would be telecasted by us</t>
+          <t>A new airport is going to be built near the</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>The programme will be telecast by us next sunday at 4pm</t>
-        </is>
-      </c>
-      <c r="H106" t="inlineStr">
-        <is>
-          <t>The object "the programme" becomes the subject, and the verb changes to "will be telecast."</t>
-        </is>
-      </c>
+          <t>A new airport is going to be built near the</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>9</v>
+        <v>83</v>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>My watch has been stolen.</t>
+          <t>We had to stop all other work to complete our</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Someone has stolen my watch.</t>
+          <t>All other work has to be stopped by us to</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>They have stolen my watch.</t>
+          <t>All other work has stopped by us to complete</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>The watch has been stolen by him.</t>
+          <t>All other work had to be stopped by us to</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Somebody have stolen my watch.</t>
+          <t>All other work was stopped by us to complete</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Someone has stolen my watch.</t>
-        </is>
-      </c>
-      <c r="H107" t="inlineStr">
-        <is>
-          <t>The subject "someone" becomes explicit, and "has been stolen" changes to "has stolen."</t>
-        </is>
-      </c>
+          <t>All other work had to be stopped by us to</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>The government has launched a massive tribal</t>
+          <t>The boys saved many elders from drowning.</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>A massive tribal welfare programme is</t>
+          <t>Many elders are saved from drowning by the</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>A massive tribal welfare program has been launched by the government.</t>
+          <t>Many elders are being saved from drowning</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Jharkhand government has launched a</t>
+          <t>Many elders were saved from drowning by the boys</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>The government in Jharkhand has launched</t>
+          <t>Many elders have been saved from drowning</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>A massive tribal welfare program has been launched by the government.</t>
+          <t>Many elders were saved from drowning by the boys</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>The object "a massive tribal welfare program" becomes the subject, and "has launched" changes to "has been launched</t>
+          <t>The object "many elders" becomes the subject, and "saved" changes to "were saved</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>The shopkeeper lowered the prices.</t>
+          <t>The manager could not accept the union leader’s proposal</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>The prices lowered the shopkeeper</t>
+          <t>The union leader’s proposal could not be accepted by the manager</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>The prices were lowered by the shopkeeper</t>
+          <t>The union leader’s proposals were not</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Down went the prices</t>
+          <t>The union leader’s proposals will not be</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>The shopkeeper got down the prices</t>
+          <t>The union leader’s proposals would not be</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>The prices were lowered by the shopkeeper</t>
+          <t>The union leader’s proposal could not be accepted by the manager</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>The object "the prices" becomes the subject, and "lowered" changes to "were lowered."</t>
+          <t>The object "the union leader’s proposal" becomes the subject, and "could not accept" changes to "could not be accepted."</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>59</v>
+        <v>124</v>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>The CEO’s son was kidnapped.</t>
+          <t>People use computers for various purposes.</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Someone kidnapped the CEO’s son.</t>
+          <t>Computers are being used by people for</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Someone has kidnapped the CEO’s son.</t>
+          <t>Computers have been used by people for</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Someone is going to kidnap the CEO’s son.</t>
+          <t>Computers are used by people for various</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Someone is kidnapping the CEO’s son.</t>
+          <t>Computers will be used by people for various</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Someone kidnapped the CEO’s son.</t>
-        </is>
-      </c>
-      <c r="H110" t="inlineStr">
-        <is>
-          <t>The subject "someone" is added to make the sentence active, and "was kidnapped" changes to "kidnapped."</t>
-        </is>
-      </c>
+          <t>Computers are used by people for various</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>110</v>
+        <v>39</v>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Honey is made by bees.</t>
+          <t>We have warned you.</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Bees makes honey.</t>
+          <t>You have been warned by us</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Bees made honey.</t>
+          <t>We have you warned.</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Bees are making honey.</t>
+          <t>Warned you have been.</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Bees make honey.</t>
+          <t>Have you been warned.</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Bees make honey.</t>
-        </is>
-      </c>
-      <c r="H111" t="inlineStr"/>
+          <t>You have been warned by us</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>The object "you" becomes the subject, and "have warned" changes to "have been warned.</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>22</v>
+        <v>122</v>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>The students were laughing at the old man.</t>
+          <t>The judge delivered the sentence at the courtroom</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>The old man was being laughed at by the</t>
+          <t>The sentence been delivered yesterday by the</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>The old man was laughed at by the students.</t>
+          <t>The sentence was delivered by the judge at</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>The old man was being laughed by the</t>
+          <t>The sentence was being delivered at the</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>The old man is laughing at the students.</t>
+          <t>Yesterday, the sentence had been delivered</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>The old man was being laughed at by the</t>
+          <t>The sentence was delivered by the judge at</t>
         </is>
       </c>
       <c r="H112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>61</v>
+        <v>95</v>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>My parents are advising me about my further studies</t>
+          <t>The thief was caught.</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>I am being advised about my further studies by my parents.</t>
+          <t>The policeman may have caught the thief.</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>I am advised by my parents about my further studies</t>
+          <t>The policeman caught the thief.</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>I was advised about my further studies by my parent</t>
+          <t>The policeman has caught the thief.</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>I had been advised about my further studies</t>
+          <t>The policeman had caught the thief.</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>I am being advised about my further studies by my parents.</t>
-        </is>
-      </c>
-      <c r="H113" t="inlineStr">
-        <is>
-          <t>The object "me" becomes the subject, and "are advising" changes to "am being advised."</t>
-        </is>
-      </c>
+          <t>The policeman caught the thief.</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>73</v>
+        <v>62</v>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Rosemary was moved to tears at the sight of the</t>
+          <t>We waste much time on social websites.</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>The sight of the miserable beggar moved</t>
+          <t>Much time was wasted on social websites.</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>The sight of the miserable beggar has moved</t>
+          <t>Much time will be wasted on social websites.</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>The sight of the miserable beggar moves</t>
+          <t>Much time is wasted by us on social websites</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>The sight of the miserable beggar had moved</t>
+          <t>Much time is being wasted y us on social websites</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>The sight of the miserable beggar moved</t>
-        </is>
-      </c>
-      <c r="H114" t="inlineStr"/>
+          <t>Much time is wasted by us on social websites</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>The object "much time" becomes the subject, and "waste" changes to "is wasted."</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>3</v>
+        <v>88</v>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>The question paper for the eleventh standard was set by the history teacher</t>
+          <t>Thick clouds have overcast the sky.</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>The history teacher set the question paper.</t>
+          <t>The sky has been overcast by thick clouds.</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>The history teacher set the eleventh question</t>
+          <t>The sky overcast by thick clouds.</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>The history teacher set the question paper</t>
+          <t>The sky is overcast by thick clouds.</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>The history teacher had the question paper</t>
+          <t>The sky is being overcast by thick clouds.</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>The history teacher set the question paper</t>
-        </is>
-      </c>
-      <c r="H115" t="inlineStr">
-        <is>
-          <t>The subject "the history teacher" performs the action, and "was set" changes to "set."</t>
-        </is>
-      </c>
+          <t>The sky has been overcast by thick clouds.</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>All the letters were posted by them.</t>
+          <t>A great deal of harm is caused to the environment</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>They have posted all the letters.</t>
+          <t>We have caused a great deal of harm to the environment</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>They had posted all the letters.</t>
+          <t>The environment causes a great deal of harm</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>They were posting all the letters.</t>
+          <t>We cause a great deal of harm to the environment</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>They posted all the letters.</t>
+          <t>The environment is being caused a great deal harm</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>They posted all the letters.</t>
+          <t>We cause a great deal of harm to the environment</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>The subject "they" performs the action, and "were posted" changes to "posted."</t>
+          <t>The subject "human activities" becomes active, and "is caused" changes to "cause."</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>6</v>
+        <v>48</v>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Open the door.</t>
+          <t>Please shut the door and go to sleep.</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Let the door should open.</t>
+          <t>The door is to be shut and you are to go to sleep</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>Let the door is opened.</t>
+          <t>Let the door be shut and you be asleep</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Let open the door.</t>
+          <t>You are requested to shut the door and go to sleep</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Let the door be opened.</t>
+          <t>The door is to be shut and you are requested</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Let the door be opened.</t>
-        </is>
-      </c>
-      <c r="H117" t="inlineStr">
-        <is>
-          <t>In imperative sentences, "let" is used to form the passive voice.</t>
-        </is>
-      </c>
+          <t>You are requested to shut the door and go to sleep</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>64</v>
+        <v>44</v>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Who wrote this article?</t>
+          <t>They have published all the details of the report</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Whom was this article written?</t>
+          <t>All the details of the report have been published by them</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>By whom this article was written. ?</t>
+          <t>The publication of the details of invention</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Who was written this article?</t>
+          <t>All the details have been invented by the</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>By whom was this article written?</t>
+          <t>All the inventions have been detailed by</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>By whom was this article written?</t>
+          <t>All the details of the report have been published by them</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>The object "this article" becomes the subject, and "wrote" changes to "was written."</t>
+          <t>The object "all the details of the report" becomes the subject, and "have published" changes to "have been published."</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>88</v>
+        <v>123</v>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Thick clouds have overcast the sky.</t>
+          <t>Shut all the doors and windows in the night.</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>The sky has been overcast by thick clouds.</t>
+          <t>Let all the doors and windows be shut in the</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>The sky overcast by thick clouds.</t>
+          <t>All the doors and windows may be shut in</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>The sky is overcast by thick clouds.</t>
+          <t>Let all the doors and windows remain shut</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>The sky is being overcast by thick clouds.</t>
+          <t>All the doors and windows be shutted in</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>The sky has been overcast by thick clouds.</t>
+          <t>Let all the doors and windows be shut in the</t>
         </is>
       </c>
       <c r="H119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Can we send this big parcel by air?</t>
+          <t>We will telecast the programme next Sunday at 4</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Can this big parcel be sent by air?</t>
+          <t>The programme will be telecast by us next sunday at 4pm</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Can this big parcel sent by air?</t>
+          <t>The programme would be telecast by us next</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Could this big parcel be sent by air?</t>
+          <t>The programme will be telecasted by us next</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Could this big parcel sent by us by air?</t>
+          <t>The programme would be telecasted by us</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Can this big parcel be sent by air?</t>
+          <t>The programme will be telecast by us next sunday at 4pm</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>The object "this big parcel" becomes the subject, and "send" changes to "be sent."</t>
+          <t>The object "the programme" becomes the subject, and the verb changes to "will be telecast."</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>11</v>
+        <v>50</v>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>People call him a fool.</t>
+          <t>We must take care of all living species on Earth.</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>He has been called a fool</t>
+          <t>All living species on Earth are taken care of</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>He is called a fool by the people.</t>
+          <t>All living species on Earth must be taken care of by us</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>The people have been calling him a fool.</t>
+          <t>All living species on Earth had been taken</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>We all people have called him a fool</t>
+          <t>All living species on Earth will be taken care</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>He is called a fool by the people.</t>
+          <t>All living species on Earth must be taken care of by us</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>The object "him" becomes the subject, and "call" changes to "is called."</t>
+          <t>The object "all living species on Earth" becomes the subject, and "must take care of" changes to "must be taken care of</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>77</v>
+        <v>57</v>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>They created such a fuss over a trivial matter.</t>
+          <t>The Metro Rail is being constructed by the corporation</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Such a fuss is being created over a trivial</t>
+          <t>The Corporation has been constructing the metro rail</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>Such a fuss was created over a trivial matter.</t>
+          <t>The Corporation is constructing the Metro rail</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Such a fuss has been created over a trivial</t>
+          <t>The Corporation has constructed the Metro rail</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>By them such a fuss has been created over a</t>
+          <t>The Corporation was constructing the Metro rail</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Such a fuss was created over a trivial matter.</t>
-        </is>
-      </c>
-      <c r="H122" t="inlineStr"/>
+          <t>The Corporation is constructing the Metro rail</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>The subject "the corporation" becomes active, and "is being constructed" changes to "is constructing."</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>125</v>
+        <v>65</v>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>The problem has been treated by numerous</t>
+          <t>The house has been painted yellow by Nikil.</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Numerous experts have been treating the</t>
+          <t>Nikil had painted the house yellow.</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>Numerous experts have treated the problem.</t>
+          <t>Nikil has painted the house yellow.</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Numerous experts had been treating the</t>
+          <t>Nikil was painting yellow the house.</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Numerous experts treated the problem.</t>
+          <t>Nikil has been painting yellow the house.</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Numerous experts have treated the problem.</t>
-        </is>
-      </c>
-      <c r="H123" t="inlineStr"/>
+          <t>Nikil has painted the house yellow.</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>The subject "Nikhil" becomes active, and "has been painted" changes to "has painted."</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>72</v>
+        <v>16</v>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>My watch can’t be repaired by anyone.</t>
+          <t>The loan will be sanctioned by the bank.</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>No one will repair my watch.</t>
+          <t>The bank sanctioned the loan.</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>No one can repair my watch.</t>
+          <t>The bank is going to sanction the loan.</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>No one can’t repair my watch.</t>
+          <t>The bank would sanction the loan.</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>No one will be able to repair my watch.</t>
+          <t>The bank will sanction the loan.</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>No one can repair my watch.</t>
-        </is>
-      </c>
-      <c r="H124" t="inlineStr"/>
+          <t>The bank will sanction the loan.</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>The subject "the bank" performs the action, and "will be sanctioned" changes to "will sanction."</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Post the letter.</t>
+          <t>Newton wrote this letter yesterday.</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>The letter is posted.</t>
+          <t>Yesterday was written letter by Newton.</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>The letter was posted.</t>
+          <t>This letter is written by Newton yesterday.</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Let the letter be posted.</t>
+          <t>This letter was written by Newton yesterday.</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>The letter will be posted.</t>
+          <t>This letter was wrote by Newton yesterday.</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Let the letter be posted.</t>
+          <t>This letter was written by Newton yesterday.</t>
         </is>
       </c>
       <c r="H125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>122</v>
+        <v>61</v>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>The judge delivered the sentence at the courtroom</t>
+          <t>My parents are advising me about my further studies</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>The sentence been delivered yesterday by the</t>
+          <t>I am being advised about my further studies by my parents.</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>The sentence was delivered by the judge at</t>
+          <t>I am advised by my parents about my further studies</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>The sentence was being delivered at the</t>
+          <t>I was advised about my further studies by my parent</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Yesterday, the sentence had been delivered</t>
+          <t>I had been advised about my further studies</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>The sentence was delivered by the judge at</t>
-        </is>
-      </c>
-      <c r="H126" t="inlineStr"/>
+          <t>I am being advised about my further studies by my parents.</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>The object "me" becomes the subject, and "are advising" changes to "am being advised."</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>They have published all the details of the report</t>
+          <t>The shopkeeper lowered the prices.</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>All the details of the report have been published by them</t>
+          <t>The prices lowered the shopkeeper</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>The publication of the details of invention</t>
+          <t>The prices were lowered by the shopkeeper</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>All the details have been invented by the</t>
+          <t>Down went the prices</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>All the inventions have been detailed by</t>
+          <t>The shopkeeper got down the prices</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>All the details of the report have been published by them</t>
+          <t>The prices were lowered by the shopkeeper</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>The object "all the details of the report" becomes the subject, and "have published" changes to "have been published."</t>
+          <t>The object "the prices" becomes the subject, and "lowered" changes to "were lowered."</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Promises should be kept.</t>
+          <t>The most useful training of my career was given to me by my boss</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>You must keep the premises.</t>
+          <t>My boss has been giving me the most useful</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>We must keep the promises</t>
+          <t>My boss gives me the most useful training.</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Keep the promises</t>
+          <t>My boss is giving me the most usefully</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>One should keep the promises</t>
+          <t>My boss gave me the most useful training of my career</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>One should keep the promises</t>
+          <t>My boss gave me the most useful training of my career</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>The subject "promises" becomes the object, and "should be kept" changes to "should keep."</t>
+          <t>The subject "the mentor" becomes active, and "was given" changes to "gave."</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>85</v>
+        <v>101</v>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>One should avoid honking the horn unnecessarily.</t>
+          <t>I was given a watch by my father.</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Unnecessary honking of horn ought to be</t>
+          <t>My father gives me a watch.</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>Unnecessary honking of horn can be avoided.</t>
+          <t>My father has given me a watch.</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Unnecessary honking of horn should be</t>
+          <t>My father had given me a watch.</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Unnecessary honking of horn must be</t>
+          <t>My father gave me a watch.</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Unnecessary honking of horn should be</t>
+          <t>My father gave me a watch.</t>
         </is>
       </c>
       <c r="H129" t="inlineStr"/>
@@ -5382,39 +5378,43 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>80</v>
+        <v>18</v>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Look! They have painted the door.</t>
+          <t>The traitors should be shot dead.</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Look! The door’s being painted.</t>
+          <t>They should have shot the traitors dead.</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>Look! The door had been painted.</t>
+          <t>They shall shoot the traitors dead.</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Look! The door has been painted.</t>
+          <t>They should shoot the traitors dead.</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Look ! The door was painted.</t>
+          <t>They shot the traitors dead.</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Look! The door has been painted.</t>
-        </is>
-      </c>
-      <c r="H131" t="inlineStr"/>
+          <t>They should shoot the traitors dead.</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>The subject "someone" performs the action, and "should be shot" changes to "should shoot."</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Data/NDA_active_passive_voice1.xlsx
+++ b/Data/NDA_active_passive_voice1.xlsx
@@ -472,4949 +472,4949 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>23</v>
+        <v>70</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>He admonished her for the error.</t>
+          <t>She learns music.</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>She was admonished by him for the error.</t>
+          <t>Music was learnt by her.</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>She has been admonished by him for the</t>
+          <t>Music was being learnt by her.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>She would be admonished by him for the</t>
+          <t>Music is being learnt by her.</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>She is admonished by him for the error.</t>
+          <t>Music is leant by her.</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>She was admonished by him for the error.</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>The object "her" becomes the subject, and "admonished" changes to "was admonished."</t>
-        </is>
-      </c>
+          <t>Music is leant by her.</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>The police caught the thief at last.</t>
+          <t>They do not accept credit cards everywhere.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>At last the thief was caught by the police</t>
+          <t>Credit cards are not being accepted</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>The thief at last caught the police.</t>
+          <t>Credit cards were not accepted everywhere.</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>The thief was at last caught by the police.</t>
+          <t>Credit cards do not accept them everywhere.</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>At last the thief by the police was caught.</t>
+          <t>Credit cards are not accepted everywhere.</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>At last the thief was caught by the police</t>
+          <t>Credit cards are not accepted everywhere.</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>"The police" is the subject, and "the thief" is the object. The verb "caught" changes to "was caught" in the passive form.</t>
+          <t>"They" is the subject, and "credit cards" is the object. In passive voice, the object becomes the subject, and the verb changes to "are not accepted."</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Gandhiji started the Quit India Movement in 1942.</t>
+          <t>One should keep one’s promises.</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>The Quit India Movement was started by</t>
+          <t>Promises should be kept.</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>The Quit India Movement was been started</t>
+          <t>One’s promises should be kept.</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>The Quit India Movement had been started</t>
+          <t>Keep the promises made by you.</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>The Quit India Movement started by</t>
+          <t>Promises be kept.</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>The Quit India Movement was started by</t>
+          <t>One’s promises should be kept.</t>
         </is>
       </c>
       <c r="H4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>42</v>
+        <v>5</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>One must keep one’s promises.</t>
+          <t>We will telecast the programme next Sunday at 4</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>One’s promises are kept</t>
+          <t>The programme will be telecast by us next sunday at 4pm</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>One’s promises must kept</t>
+          <t>The programme would be telecast by us next</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>One’s promises were kept</t>
+          <t>The programme will be telecasted by us next</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>One’s promises must be kept</t>
+          <t>The programme would be telecasted by us</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>One’s promises must be kept</t>
+          <t>The programme will be telecast by us next sunday at 4pm</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>The object "promises" becomes the subject, and "must keep" changes to "must be kept."</t>
+          <t>The object "the programme" becomes the subject, and the verb changes to "will be telecast."</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>47</v>
+        <v>2</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Prepare yourself for the worst.</t>
+          <t>The police caught the thief at last.</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>You be prepared for the worst.</t>
+          <t>At last the thief was caught by the police</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>The worst should be prepared by yourself.</t>
+          <t>The thief at last caught the police.</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Let yourself be prepared for the worst.</t>
+          <t>The thief was at last caught by the police.</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>For the worst, preparation should be made</t>
+          <t>At last the thief by the police was caught.</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Let yourself be prepared for the worst.</t>
+          <t>At last the thief was caught by the police</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Imperative sentences use "let" in passive voice</t>
+          <t>"The police" is the subject, and "the thief" is the object. The verb "caught" changes to "was caught" in the passive form.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128</v>
+        <v>38</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>The company paid her a meagre salary.</t>
+          <t>We must respect the elders.</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>She was paid a meagre salary by the</t>
+          <t>The elders deserve respect from us.</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>A meagre salary has been paid to her by the</t>
+          <t>The elders must be respected.</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>She was being paid a meagre salary by the</t>
+          <t>The elders must be respected by us.</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>A meagre salary was to be paid to her by the</t>
+          <t>Respect the elders we must.</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>She was paid a meagre salary by the</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr"/>
+          <t>The elders must be respected by us.</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>The object "the elders" becomes the subject, and "must respect" changes to "must be respected."</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>27</v>
+        <v>90</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>You will be taken care of by me.</t>
+          <t>The scheme permits investors to buy the shares</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>I will be taking care of you.</t>
+          <t>Under the scheme the investors may be</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>I would take care of you.</t>
+          <t>Under the scheme the investors have been</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>I will take care of you.</t>
+          <t>Under the scheme the investors are permitted</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>I will being take care of you.</t>
+          <t>Under the scheme the investors were</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>I will take care of you.</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>The subject "you" becomes the object, and "will be taken care of" changes to "will take care of."</t>
-        </is>
-      </c>
+          <t>Under the scheme the investors are permitted</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>We have decided to open a new branch</t>
+          <t>You will be taken care of by me.</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>To open a new branch was decided by us.</t>
+          <t>I will be taking care of you.</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>To be opened a new branch has been decided.</t>
+          <t>I would take care of you.</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>It has been decided to open a new branch.</t>
+          <t>I will take care of you.</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>It may be decided to open a new branch by</t>
+          <t>I will being take care of you.</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>It has been decided to open a new branch.</t>
+          <t>I will take care of you.</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>The object "a new branch" becomes the subject, and "have decided" changes to "has been decided to be open."</t>
+          <t>The subject "you" becomes the object, and "will be taken care of" changes to "will take care of."</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>40</v>
+        <v>125</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Has anybody answered your question?</t>
+          <t>The problem has been treated by numerous</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Your question has been answered?</t>
+          <t>Numerous experts have been treating the</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Anybody has answered your question?</t>
+          <t>Numerous experts have treated the problem.</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Has your question been answered by anybody?</t>
+          <t>Numerous experts had been treating the</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Have your answered you question ?</t>
+          <t>Numerous experts treated the problem.</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Has your question been answered by anybody?</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>The object "your question" becomes the subject, and "has answered" changes to "has been answered."</t>
-        </is>
-      </c>
+          <t>Numerous experts have treated the problem.</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>17</v>
+        <v>76</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Paint the windows.</t>
+          <t>Who asked you to draft this letter ?</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Windows should be painted.</t>
+          <t>By who you are asked to draft this letter.</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Let the windows be painted.</t>
+          <t>By who have you been asked to draft this</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Let be the windows painted.</t>
+          <t>By whom were you asked to draft this letter</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Windows are let to be painted.</t>
+          <t>By whom you were asked to draft this letter.</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Let the windows be painted.</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>In imperative sentences, "let" is used for passive voice.</t>
-        </is>
-      </c>
+          <t>By whom were you asked to draft this letter</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>The lightning caused a serious forest fire and</t>
+          <t>Don’t subject the animals to cruelty.</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>A serious forest fire has been caused by</t>
+          <t>The animals are not to be subjected to</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>A serious forest fire has been caused by lightning</t>
+          <t>The animals shall not be subjected to cruelty.</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>A serious forest fire had been caused by</t>
+          <t>The animals will not be subjected to cruelty.</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>A serious forest fire was caused by lightning</t>
+          <t>The animals should not be subjected to</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>A serious forest fire was caused by lightning</t>
+          <t>The animals should not be subjected to</t>
         </is>
       </c>
       <c r="H12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127</v>
+        <v>41</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Mother gave him a little puppy.</t>
+          <t>The shopkeeper lowered the prices.</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>He was given a little puppy by mother.</t>
+          <t>The prices lowered the shopkeeper</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>A little puppy was being given to him by</t>
+          <t>The prices were lowered by the shopkeeper</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>He had been given a little puppy by mother.</t>
+          <t>Down went the prices</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>A little puppy is given to him by his mother.</t>
+          <t>The shopkeeper got down the prices</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>He was given a little puppy by mother.</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr"/>
+          <t>The prices were lowered by the shopkeeper</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>The object "the prices" becomes the subject, and "lowered" changes to "were lowered."</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Where did you buy this pen ?</t>
+          <t>One should not give unsolicited advice.</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Where shall you buy this pen ?</t>
+          <t>Unsolicited advice is not to be given.</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Where is this pen bought by you ?</t>
+          <t>Unsolicited advice can’t be given.</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Where was this pen bought ?</t>
+          <t>Unsolicited advice may not be given.</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Where will you buy this pen ?</t>
+          <t>Unsolicited advice should not be given.</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Where was this pen bought ?</t>
+          <t>Unsolicited advice should not be given.</t>
         </is>
       </c>
       <c r="H14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>59</v>
+        <v>79</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>The CEO’s son was kidnapped.</t>
+          <t>Today I accomplished my task successfully.</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Someone kidnapped the CEO’s son.</t>
+          <t>Today my task is accomplished successfully</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Someone has kidnapped the CEO’s son.</t>
+          <t>Today my task accomplished successfully.</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Someone is going to kidnap the CEO’s son.</t>
+          <t>Today my task was accomplished</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Someone is kidnapping the CEO’s son.</t>
+          <t>Today my task was accomplished
+successfully</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Someone kidnapped the CEO’s son.</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>The subject "someone" is added to make the sentence active, and "was kidnapped" changes to "kidnapped."</t>
-        </is>
-      </c>
+          <t>Today my task was accomplished
+successfully</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>8</v>
+        <v>40</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>The comic scenes in the play were overdone by the actor</t>
+          <t>Has anybody answered your question?</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>The actors overdid the comic scenes in the</t>
+          <t>Your question has been answered?</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>The actors overacted the comic scenes in the play</t>
+          <t>Anybody has answered your question?</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>The play was full of comic scenes.</t>
+          <t>Has your question been answered by anybody?</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>The actors comically performed the play.</t>
+          <t>Have your answered you question ?</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>The actors overacted the comic scenes in the play</t>
+          <t>Has your question been answered by anybody?</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>The subject "the actors" becomes active, and "were overdone" changes to "overdid."</t>
+          <t>The object "your question" becomes the subject, and "has answered" changes to "has been answered."</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>How many languages are spoken in India?</t>
+          <t>Honey is made by bees.</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>How many languages Indians are speaking</t>
+          <t>Bees makes honey.</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>How many languages Indians speak?</t>
+          <t>Bees made honey.</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>How many languages do Indians speak?</t>
+          <t>Bees are making honey.</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>How many languages did Indians speak?</t>
+          <t>Bees make honey.</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>How many languages do Indians speak?</t>
+          <t>Bees make honey.</t>
         </is>
       </c>
       <c r="H17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>85</v>
+        <v>28</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>One should avoid honking the horn unnecessarily.</t>
+          <t>Promises should be kept.</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Unnecessary honking of horn ought to be</t>
+          <t>You must keep the premises.</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Unnecessary honking of horn can be avoided.</t>
+          <t>We must keep the promises</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Unnecessary honking of horn should be</t>
+          <t>Keep the promises</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Unnecessary honking of horn must be</t>
+          <t>One should keep the promises</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Unnecessary honking of horn should be</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr"/>
+          <t>One should keep the promises</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>The subject "promises" becomes the object, and "should be kept" changes to "should keep."</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>20</v>
+        <v>61</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>One cannot expect children to understand these problems</t>
+          <t>My parents are advising me about my further studies</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Children cannot be expected to understand</t>
+          <t>I am being advised about my further studies by my parents.</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Children to understand these problems</t>
+          <t>I am advised by my parents about my further studies</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Children cannot be expected to understand these problems</t>
+          <t>I was advised about my further studies by my parent</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>To understand these problems cannot be</t>
+          <t>I had been advised about my further studies</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Children cannot be expected to understand these problems</t>
+          <t>I am being advised about my further studies by my parents.</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>The object "children" becomes the subject, and "cannot expect" changes to "cannot be expected."</t>
+          <t>The object "me" becomes the subject, and "are advising" changes to "am being advised."</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>52</v>
+        <v>34</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Two hundred people were arrested by the police.</t>
+          <t>The boys were playing cricket.</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>The police have arrested two hundred people.</t>
+          <t>Cricket had been played by the boys.</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>The police arrested two hundred people.</t>
+          <t>Cricket has been played by the boys.</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>The police had arrested two hundred people.</t>
+          <t>Cricket was played by the boys.</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>The police has arrested two hundred people.</t>
+          <t>Cricket was being played by the boys.</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>The police arrested two hundred people.</t>
+          <t>Cricket was being played by the boys.</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>The subject "the police" becomes active, and "were arrested" changes to "arrested."</t>
+          <t>The object "cricket" becomes the subject, and "were playing" changes to "was being played.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Who wrote this article?</t>
+          <t>My books have been stolen.</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Whom was this article written?</t>
+          <t>Someone has stolen my books.</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>By whom this article was written. ?</t>
+          <t>Someone stole my books.</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Who was written this article?</t>
+          <t>Someone have stolen my books.</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>By whom was this article written?</t>
+          <t>They stole my books.</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>By whom was this article written?</t>
+          <t>Someone has stolen my books.</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>The object "this article" becomes the subject, and "wrote" changes to "was written."</t>
+          <t>The subject "someone" is added, and "have been stolen" changes to "has stolen."</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>77</v>
+        <v>119</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>They created such a fuss over a trivial matter.</t>
+          <t>Post the letter.</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Such a fuss is being created over a trivial</t>
+          <t>The letter is posted.</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Such a fuss was created over a trivial matter.</t>
+          <t>The letter was posted.</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Such a fuss has been created over a trivial</t>
+          <t>Let the letter be posted.</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>By them such a fuss has been created over a</t>
+          <t>The letter will be posted.</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Such a fuss was created over a trivial matter.</t>
+          <t>Let the letter be posted.</t>
         </is>
       </c>
       <c r="H22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>89</v>
+        <v>123</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>One should not give unsolicited advice.</t>
+          <t>Shut all the doors and windows in the night.</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Unsolicited advice is not to be given.</t>
+          <t>Let all the doors and windows be shut in the</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Unsolicited advice can’t be given.</t>
+          <t>All the doors and windows may be shut in</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Unsolicited advice may not be given.</t>
+          <t>Let all the doors and windows remain shut</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Unsolicited advice should not be given.</t>
+          <t>All the doors and windows be shutted in</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Unsolicited advice should not be given.</t>
+          <t>Let all the doors and windows be shut in the</t>
         </is>
       </c>
       <c r="H23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Nobody has answered my question.</t>
+          <t>He handed her a chair.</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>My question has been answered by</t>
+          <t>She was handed a chair by him.</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>My question has not been answered by</t>
+          <t>He handed a chair to her.</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>My question was not answered.</t>
+          <t>He will hand a chair to her.</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>My question remains unanswered.</t>
+          <t>A chair will be handed to her by him</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>My question has not been answered by</t>
+          <t>She was handed a chair by him.</t>
         </is>
       </c>
       <c r="H24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>111</v>
+        <v>23</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>The whole village was ravaged by the man-eater.</t>
+          <t>He admonished her for the error.</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>The man-eater ravages the whole village.</t>
+          <t>She was admonished by him for the error.</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>The whole village is ravaged by the maneater.</t>
+          <t>She has been admonished by him for the</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>The man-eater ravaged the whole village.</t>
+          <t>She would be admonished by him for the</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>The whole village is being ravaged by the</t>
+          <t>She is admonished by him for the error.</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>The man-eater ravaged the whole village.</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr"/>
+          <t>She was admonished by him for the error.</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>The object "her" becomes the subject, and "admonished" changes to "was admonished."</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>21</v>
+        <v>111</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Why did she break the garden wall?</t>
+          <t>The whole village was ravaged by the man-eater.</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Why the garden wall was broken by her?</t>
+          <t>The man-eater ravages the whole village.</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Why had the garden wall been broken by</t>
+          <t>The whole village is ravaged by the maneater.</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Why was the garden wall broken by her?</t>
+          <t>The man-eater ravaged the whole village.</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Why will the garden wall be broken by her?</t>
+          <t>The whole village is being ravaged by the</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Why was the garden wall broken by her?</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>The object "the garden wall" becomes the subject, and "did break" changes to "was broken."</t>
-        </is>
-      </c>
+          <t>The man-eater ravaged the whole village.</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>103</v>
+        <v>59</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Jane Austen devoted her whole life to her</t>
+          <t>The CEO’s son was kidnapped.</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Jane Austen’s whole life is devoted to her</t>
+          <t>Someone kidnapped the CEO’s son.</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Jane Austen’s whole life had been devoted</t>
+          <t>Someone has kidnapped the CEO’s son.</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Jane Austen’s whole life was devoted to her</t>
+          <t>Someone is going to kidnap the CEO’s son.</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Jane Austen’s whole life has devoted to her</t>
+          <t>Someone is kidnapping the CEO’s son.</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Jane Austen’s whole life was devoted to her</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr"/>
+          <t>Someone kidnapped the CEO’s son.</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>The subject "someone" is added to make the sentence active, and "was kidnapped" changes to "kidnapped."</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>13</v>
+        <v>66</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>He had committed a mistake.</t>
+          <t>The news surprised me.</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>A mistake had committed by him.</t>
+          <t>I am surprised by the news.</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>A mistake was committed by him.</t>
+          <t>I was surprised by the news.</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>A mistake had been committed by him.</t>
+          <t>The news was surprised by me.</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>A mistake has been committed by him</t>
+          <t>The news was a big surprise.</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>A mistake had been committed by him.</t>
+          <t>I was surprised by the news.</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>The object "a mistake" becomes the subject, and "had committed" changes to "had been committed."</t>
+          <t>The object "me" becomes the subject, and "surprised" changes to "was surprised."</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119</v>
+        <v>97</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Post the letter.</t>
+          <t>I have been sent here by the editor of Tribune.</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>The letter is posted.</t>
+          <t>The editor of Tribune has send me here.</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>The letter was posted.</t>
+          <t>The editor of Tribune sent me here.</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Let the letter be posted.</t>
+          <t>The editor of Tribune has sent me here.</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>The letter will be posted.</t>
+          <t>The editor of Tribune send me here.</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Let the letter be posted.</t>
+          <t>The editor of Tribune has sent me here.</t>
         </is>
       </c>
       <c r="H29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>The Manager granted me two days leave.</t>
+          <t>They should shoot the terrorists dead.</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>I had been granted two days’ leave by the</t>
+          <t>The terrorists been shot dead by them.</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>I have been granted two days’ leave by the</t>
+          <t>The terrorists should have been shot dead</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>I granted two days’ leave by the Manager.</t>
+          <t>The terrorists should be shot dead by them.</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>I was granted two days’ leave by the</t>
+          <t>The terrorists have been shot dead by them.</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>I was granted two days’ leave by the</t>
+          <t>The terrorists should be shot dead by them.</t>
         </is>
       </c>
       <c r="H30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>79</v>
+        <v>129</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Today I accomplished my task successfully.</t>
+          <t>Do not insult him.</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Today my task is accomplished successfully</t>
+          <t>Let he not be insulted.</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Today my task accomplished successfully.</t>
+          <t>Let him not be insulted.</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Today my task was accomplished</t>
+          <t>Let not he be insulted.</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Today my task was accomplished
-successfully</t>
+          <t>Let not him be insulted.</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Today my task was accomplished
-successfully</t>
+          <t>Let him not be insulted.</t>
         </is>
       </c>
       <c r="H31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>81</v>
+        <v>113</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>She was advised 15 days’ rest after her surgery.</t>
+          <t>Newton wrote this letter yesterday.</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>The doctor was advised her 15 days’ rest after</t>
+          <t>Yesterday was written letter by Newton.</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>The doctor has advised her 15 days’ rest after</t>
+          <t>This letter is written by Newton yesterday.</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>The doctor advised her 15 days’ rest after</t>
+          <t>This letter was written by Newton yesterday.</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>The doctor had advised her 15 days’ rest after</t>
+          <t>This letter was wrote by Newton yesterday.</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>The doctor advised her 15 days’ rest after</t>
+          <t>This letter was written by Newton yesterday.</t>
         </is>
       </c>
       <c r="H32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>58</v>
+        <v>24</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>All the letters were posted by them.</t>
+          <t>Can we send this big parcel by air?</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>They have posted all the letters.</t>
+          <t>Can this big parcel be sent by air?</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>They had posted all the letters.</t>
+          <t>Can this big parcel sent by air?</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>They were posting all the letters.</t>
+          <t>Could this big parcel be sent by air?</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>They posted all the letters.</t>
+          <t>Could this big parcel sent by us by air?</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>They posted all the letters.</t>
+          <t>Can this big parcel be sent by air?</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>The subject "they" performs the action, and "were posted" changes to "posted."</t>
+          <t>The object "this big parcel" becomes the subject, and "send" changes to "be sent."</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>104</v>
+        <v>15</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Hamlet was written by Shakespeare.</t>
+          <t>We have decided to open a new branch</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Shakespeare has written Hamlet.</t>
+          <t>To open a new branch was decided by us.</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Shakespeare had written Hamlet.</t>
+          <t>To be opened a new branch has been decided.</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Shakespeare wrote Hamlet.</t>
+          <t>It has been decided to open a new branch.</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Shakespeare writes Hamlet.</t>
+          <t>It may be decided to open a new branch by</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Shakespeare wrote Hamlet.</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr"/>
+          <t>It has been decided to open a new branch.</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>The object "a new branch" becomes the subject, and "have decided" changes to "has been decided to be open."</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>68</v>
+        <v>33</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>They are painting the walls.</t>
+          <t>The government has launched a massive tribal</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>The walls are painting them.</t>
+          <t>A massive tribal welfare programme is</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>The walls are painted by them.</t>
+          <t>A massive tribal welfare program has been launched by the government.</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>The walls are being painted by them.</t>
+          <t>Jharkhand government has launched a</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>The walls in painted by them.</t>
+          <t>The government in Jharkhand has launched</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>The walls are being painted by them.</t>
+          <t>A massive tribal welfare program has been launched by the government.</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>The object "the walls" becomes the subject, and "are painting" changes to "are being painted.</t>
+          <t>The object "a massive tribal welfare program" becomes the subject, and "has launched" changes to "has been launched</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>30</v>
+        <v>103</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>He would have written this essay in time.</t>
+          <t>Jane Austen devoted her whole life to her</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>The essay was written on time.</t>
+          <t>Jane Austen’s whole life is devoted to her</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>This essay would have been written by him in time</t>
+          <t>Jane Austen’s whole life had been devoted</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>The essay was written by him in time.</t>
+          <t>Jane Austen’s whole life was devoted to her</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>He wrote the essay on time.</t>
+          <t>Jane Austen’s whole life has devoted to her</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>This essay would have been written by him in time</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>The object "this essay" becomes the subject, and "would have written" changes to "would have been written."</t>
-        </is>
-      </c>
+          <t>Jane Austen’s whole life was devoted to her</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>130</v>
+        <v>100</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Sameer shut the door with a bang.</t>
+          <t>When did he finish this work?</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>The door was shut with a bang by Sameer.</t>
+          <t>When this work was finished by him?</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>The door with a bang shut by Sameer.</t>
+          <t>When was this work finished by him?</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>The door shut Sameer with a bang.</t>
+          <t>When will this work be finished by him?</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>The door had been shut with a bang by</t>
+          <t>When he finished this work?</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>The door was shut with a bang by Sameer.</t>
+          <t>When was this work finished by him?</t>
         </is>
       </c>
       <c r="H37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>49</v>
+        <v>99</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>It is impossible to do this.</t>
+          <t>A big variety store was inaugurated by Sachin.</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Doing this is impossible.</t>
+          <t>Sachin inaugurated a big variety store.</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>This is impossible to be done</t>
+          <t>Sachin had inaugurated a big variety store.</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>This must not be done</t>
+          <t>Sachin has inaugurated a big variety store.</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>This can’t be done</t>
+          <t>Sachin inaugurate a big variety store.</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>This is impossible to be done</t>
+          <t>Sachin inaugurated a big variety store.</t>
         </is>
       </c>
       <c r="H38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>73</v>
+        <v>54</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Rosemary was moved to tears at the sight of the</t>
+          <t>People speak English all over the world.</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>The sight of the miserable beggar moved</t>
+          <t>English was spoken all over the world.</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>The sight of the miserable beggar has moved</t>
+          <t>English have been spoken all over the world.</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>The sight of the miserable beggar moves</t>
+          <t>English has been spoken all over the world.</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>The sight of the miserable beggar had moved</t>
+          <t>English is spoken all over the world by people</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>The sight of the miserable beggar moved</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr"/>
+          <t>English is spoken all over the world by people</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>The object "English" becomes the subject, and "speak" changes to "is spoken."</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Cigarettes cannot be sold here.</t>
+          <t>I was given a watch by my father.</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Nobody sold cigarettes here.</t>
+          <t>My father gives me a watch.</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Nobody could sell cigarettes here.</t>
+          <t>My father has given me a watch.</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Nobody can sell cigarettes here.</t>
+          <t>My father had given me a watch.</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Anybody can’t sell cigarettes here.</t>
+          <t>My father gave me a watch.</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Nobody can sell cigarettes here.</t>
+          <t>My father gave me a watch.</t>
         </is>
       </c>
       <c r="H40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>102</v>
+        <v>26</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Who helps you in your daily chores?</t>
+          <t>We found him a good wife.</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>By who are you helped in your daily chores?</t>
+          <t>He was found a good wife by us.</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>By whom are you helped in your daily</t>
+          <t>A good wife was found out by them.</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>By who you are helped in your daily chores?</t>
+          <t>A good wife found him.</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>By whom you were helped in your daily</t>
+          <t>A good wife was being found by us.</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>By whom are you helped in your daily</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr"/>
+          <t>He was found a good wife by us.</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>The object "him" becomes the subject, and "found" changes to "was found."</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>53</v>
+        <v>20</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>The storm damaged the roof.</t>
+          <t>One cannot expect children to understand these problems</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>The roof is damaged by the storm.</t>
+          <t>Children cannot be expected to understand</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>The roof was damage by the storm.</t>
+          <t>Children to understand these problems</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>The roof was damaged by the storm.</t>
+          <t>Children cannot be expected to understand these problems</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>The roof would be damaged by the storm</t>
+          <t>To understand these problems cannot be</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>The roof was damaged by the storm.</t>
+          <t>Children cannot be expected to understand these problems</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>The object "the roof" becomes the subject, and "damaged" changes to "was damaged."</t>
+          <t>The object "children" becomes the subject, and "cannot expect" changes to "cannot be expected."</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>38</v>
+        <v>104</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>We must respect the elders.</t>
+          <t>Hamlet was written by Shakespeare.</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>The elders deserve respect from us.</t>
+          <t>Shakespeare has written Hamlet.</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>The elders must be respected.</t>
+          <t>Shakespeare had written Hamlet.</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>The elders must be respected by us.</t>
+          <t>Shakespeare wrote Hamlet.</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Respect the elders we must.</t>
+          <t>Shakespeare writes Hamlet.</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>The elders must be respected by us.</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>The object "the elders" becomes the subject, and "must respect" changes to "must be respected."</t>
-        </is>
-      </c>
+          <t>Shakespeare wrote Hamlet.</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>80</v>
+        <v>53</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Look! They have painted the door.</t>
+          <t>The storm damaged the roof.</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Look! The door’s being painted.</t>
+          <t>The roof is damaged by the storm.</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Look! The door had been painted.</t>
+          <t>The roof was damage by the storm.</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Look! The door has been painted.</t>
+          <t>The roof was damaged by the storm.</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Look ! The door was painted.</t>
+          <t>The roof would be damaged by the storm</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Look! The door has been painted.</t>
-        </is>
-      </c>
-      <c r="H44" t="inlineStr"/>
+          <t>The roof was damaged by the storm.</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>The object "the roof" becomes the subject, and "damaged" changes to "was damaged."</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Could you pass the salt ?</t>
+          <t>The lightning caused a serious forest fire and</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Could the salt been passed ?</t>
+          <t>A serious forest fire has been caused by</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Could the salt be passed by anyone ?</t>
+          <t>A serious forest fire has been caused by lightning</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Could the salt be past ?</t>
+          <t>A serious forest fire had been caused by</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Could the salt be passed ?</t>
+          <t>A serious forest fire was caused by lightning</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Could the salt be passed ?</t>
+          <t>A serious forest fire was caused by lightning</t>
         </is>
       </c>
       <c r="H45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>70</v>
+        <v>87</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>She learns music.</t>
+          <t>The modern means of communication have made</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Music was learnt by her.</t>
+          <t>Life had been made so much easier by the</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Music was being learnt by her.</t>
+          <t>Life is being so much easier by the modern</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Music is being learnt by her.</t>
+          <t>Life has been made so much easier by the</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Music is leant by her.</t>
+          <t>Life was made so much easier by the modern</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Music is leant by her.</t>
+          <t>Life has been made so much easier by the</t>
         </is>
       </c>
       <c r="H46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>114</v>
+        <v>127</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>An awareness is being created among the people</t>
+          <t>Mother gave him a little puppy.</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>The Government is creating an awareness</t>
+          <t>He was given a little puppy by mother.</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>The Government are creating an awareness</t>
+          <t>A little puppy was being given to him by</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>The Government creates an awareness</t>
+          <t>He had been given a little puppy by mother.</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>The Government created an awareness</t>
+          <t>A little puppy is given to him by his mother.</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>The Government is creating an awareness</t>
+          <t>He was given a little puppy by mother.</t>
         </is>
       </c>
       <c r="H47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>35</v>
+        <v>73</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>They drew a circle in the morning.</t>
+          <t>Rosemary was moved to tears at the sight of the</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>A circle was being drawn by them in the</t>
+          <t>The sight of the miserable beggar moved</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>A circle was drawn by them in the morning.</t>
+          <t>The sight of the miserable beggar has moved</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>In the morning a circle have been drawn by</t>
+          <t>The sight of the miserable beggar moves</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>A circle has been drawing since morning.</t>
+          <t>The sight of the miserable beggar had moved</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>A circle was drawn by them in the morning.</t>
-        </is>
-      </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>The object "a circle" becomes the subject, and "drew" changes to "was drawn."</t>
-        </is>
-      </c>
+          <t>The sight of the miserable beggar moved</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>29</v>
+        <v>85</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Circumstances forced him to resign his post.</t>
+          <t>One should avoid honking the horn unnecessarily.</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Circumstances make him to resign his post.</t>
+          <t>Unnecessary honking of horn ought to be</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>He was forced to resign his post by circumstances</t>
+          <t>Unnecessary honking of horn can be avoided.</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>He is forced to resign his post.</t>
+          <t>Unnecessary honking of horn should be</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>He is forced and resigned his post.</t>
+          <t>Unnecessary honking of horn must be</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>He was forced to resign his post by circumstances</t>
-        </is>
-      </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>The object "him" becomes the subject, and "forced" changes to "was forced."</t>
-        </is>
-      </c>
+          <t>Unnecessary honking of horn should be</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>109</v>
+        <v>3</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>They should shoot the terrorists dead.</t>
+          <t>The question paper for the eleventh standard was set by the history teacher</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>The terrorists been shot dead by them.</t>
+          <t>The history teacher set the question paper.</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>The terrorists should have been shot dead</t>
+          <t>The history teacher set the eleventh question</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>The terrorists should be shot dead by them.</t>
+          <t>The history teacher set the question paper</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>The terrorists have been shot dead by them.</t>
+          <t>The history teacher had the question paper</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>The terrorists should be shot dead by them.</t>
-        </is>
-      </c>
-      <c r="H50" t="inlineStr"/>
+          <t>The history teacher set the question paper</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>The subject "the history teacher" performs the action, and "was set" changes to "set."</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>99</v>
+        <v>124</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>A big variety store was inaugurated by Sachin.</t>
+          <t>People use computers for various purposes.</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Sachin inaugurated a big variety store.</t>
+          <t>Computers are being used by people for</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Sachin had inaugurated a big variety store.</t>
+          <t>Computers have been used by people for</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Sachin has inaugurated a big variety store.</t>
+          <t>Computers are used by people for various</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Sachin inaugurate a big variety store.</t>
+          <t>Computers will be used by people for various</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Sachin inaugurated a big variety store.</t>
+          <t>Computers are used by people for various</t>
         </is>
       </c>
       <c r="H51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>110</v>
+        <v>50</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Honey is made by bees.</t>
+          <t>We must take care of all living species on Earth.</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Bees makes honey.</t>
+          <t>All living species on Earth are taken care of</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Bees made honey.</t>
+          <t>All living species on Earth must be taken care of by us</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Bees are making honey.</t>
+          <t>All living species on Earth had been taken</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Bees make honey.</t>
+          <t>All living species on Earth will be taken care</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Bees make honey.</t>
-        </is>
-      </c>
-      <c r="H52" t="inlineStr"/>
+          <t>All living species on Earth must be taken care of by us</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>The object "all living species on Earth" becomes the subject, and "must take care of" changes to "must be taken care of</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>116</v>
+        <v>71</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>The Indian Government is encouraging the</t>
+          <t>They are going to build a new airport near the old</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>The Europeans are encouraged by the Indian</t>
+          <t>A new airport going to be built near the old</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>The Europeans are encouraging by the Indian</t>
+          <t>A new airport is being built near the old one.</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>The Europeans are being encouraged by the</t>
+          <t>A new airport will be built near the old one.</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>The Europeans is being encouraged by the</t>
+          <t>A new airport is going to be built near the</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>The Europeans are being encouraged by the</t>
+          <t>A new airport is going to be built near the</t>
         </is>
       </c>
       <c r="H53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>26</v>
+        <v>64</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>We found him a good wife.</t>
+          <t>Who wrote this article?</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>He was found a good wife by us.</t>
+          <t>Whom was this article written?</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>A good wife was found out by them.</t>
+          <t>By whom this article was written. ?</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>A good wife found him.</t>
+          <t>Who was written this article?</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>A good wife was being found by us.</t>
+          <t>By whom was this article written?</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>He was found a good wife by us.</t>
+          <t>By whom was this article written?</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>The object "him" becomes the subject, and "found" changes to "was found."</t>
+          <t>The object "this article" becomes the subject, and "wrote" changes to "was written."</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>The question paper for the eleventh standard was set by the history teacher</t>
+          <t>‘The Titanic’ was hit by an iceberg.</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>The history teacher set the question paper.</t>
+          <t>An iceberg hit “The Titanic’.</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>The history teacher set the eleventh question</t>
+          <t>An iceberg was hit by ‘The Titanic.’`</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>The history teacher set the question paper</t>
+          <t>An iceberg was being hit by ‘The Titanic’.</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>The history teacher had the question paper</t>
+          <t>An iceberg was hitting ‘The Titanic.’</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>The history teacher set the question paper</t>
+          <t>An iceberg hit “The Titanic’.</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>The subject "the history teacher" performs the action, and "was set" changes to "set."</t>
+          <t>he subject "The Titanic" becomes the object, and "was hit" changes to "hit."</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>4</v>
+        <v>47</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Somebody has stolen his book.</t>
+          <t>Prepare yourself for the worst.</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>His book was stolen.</t>
+          <t>You be prepared for the worst.</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>His book was stolen by somebody.</t>
+          <t>The worst should be prepared by yourself.</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>His book has been stolen.</t>
+          <t>Let yourself be prepared for the worst.</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>His book had been stolen by somebody.</t>
+          <t>For the worst, preparation should be made</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>His book has been stolen.</t>
+          <t>Let yourself be prepared for the worst.</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>The object "his book" becomes the subject, and the verb changes to "has been stolen."</t>
+          <t>Imperative sentences use "let" in passive voice</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>‘The Titanic’ was hit by an iceberg.</t>
+          <t>It is being read by us.</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>An iceberg hit “The Titanic’.</t>
+          <t>We are reading it.</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>An iceberg was hit by ‘The Titanic.’`</t>
+          <t>It will be read by us.</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>An iceberg was being hit by ‘The Titanic’.</t>
+          <t>We can read it.</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>An iceberg was hitting ‘The Titanic.’</t>
+          <t>We have to read it.</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>An iceberg hit “The Titanic’.</t>
+          <t>We are reading it.</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>he subject "The Titanic" becomes the object, and "was hit" changes to "hit."</t>
+          <t>The subject "we" performs the action, and "is being read" changes to "are reading."</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>32</v>
+        <v>9</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>The boy laughed at the beggar.</t>
+          <t>My watch has been stolen.</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>The beggar was laughed by the boy.</t>
+          <t>Someone has stolen my watch.</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>The beggar was being laughed by the boy.</t>
+          <t>They have stolen my watch.</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>The beggar was being laughed at by the boy.</t>
+          <t>The watch has been stolen by him.</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>The beggar was laughed at by the boy.</t>
+          <t>Somebody have stolen my watch.</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>The beggar was laughed at by the boy.</t>
+          <t>Someone has stolen my watch.</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>The object "the beggar" becomes the subject, and "laughed at" changes to "was laughed at.</t>
+          <t>The subject "someone" becomes explicit, and "has been stolen" changes to "has stolen."</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>125</v>
+        <v>118</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>The problem has been treated by numerous</t>
+          <t>Call the police at once</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Numerous experts have been treating the</t>
+          <t>Let the police be called at once.</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Numerous experts have treated the problem.</t>
+          <t>The police was to be called at once.</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Numerous experts had been treating the</t>
+          <t>The police is to be called at once.</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Numerous experts treated the problem.</t>
+          <t>Let the police called at once.</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Numerous experts have treated the problem.</t>
+          <t>Let the police be called at once.</t>
         </is>
       </c>
       <c r="H59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>97</v>
+        <v>22</v>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>I have been sent here by the editor of Tribune.</t>
+          <t>The students were laughing at the old man.</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>The editor of Tribune has send me here.</t>
+          <t>The old man was being laughed at by the</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>The editor of Tribune sent me here.</t>
+          <t>The old man was laughed at by the students.</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>The editor of Tribune has sent me here.</t>
+          <t>The old man was being laughed by the</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>The editor of Tribune send me here.</t>
+          <t>The old man is laughing at the students.</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>The editor of Tribune has sent me here.</t>
+          <t>The old man was being laughed at by the</t>
         </is>
       </c>
       <c r="H60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>51</v>
+        <v>122</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>They are considering your proposal,</t>
+          <t>The judge delivered the sentence at the courtroom</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Your proposal is being considered by them.</t>
+          <t>The sentence been delivered yesterday by the</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>You proposal was being considered by them.</t>
+          <t>The sentence was delivered by the judge at</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Your proposal was considered by them.</t>
+          <t>The sentence was being delivered at the</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Your proposal is considered by them.</t>
+          <t>Yesterday, the sentence had been delivered</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Your proposal is being considered by them.</t>
-        </is>
-      </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>The object "your proposal" becomes the subject, and "are considering" changes to "is being considered.</t>
-        </is>
-      </c>
+          <t>The sentence was delivered by the judge at</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>93</v>
+        <v>30</v>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>He abandoned his medical studies.</t>
+          <t>He would have written this essay in time.</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>His medical studies had abandoned.</t>
+          <t>The essay was written on time.</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>His medical studies are abandoned.</t>
+          <t>This essay would have been written by him in time</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>His medical studies have been abandoned.</t>
+          <t>The essay was written by him in time.</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>His medical studies were abandoned.</t>
+          <t>He wrote the essay on time.</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>His medical studies were abandoned.</t>
-        </is>
-      </c>
-      <c r="H62" t="inlineStr"/>
+          <t>This essay would have been written by him in time</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>The object "this essay" becomes the subject, and "would have written" changes to "would have been written."</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>76</v>
+        <v>107</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Who asked you to draft this letter ?</t>
+          <t>Everyone admires our principal.</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>By who you are asked to draft this letter.</t>
+          <t>Our principal has been admired by everyone.</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>By who have you been asked to draft this</t>
+          <t>Our principal was admired by everyone.</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>By whom were you asked to draft this letter</t>
+          <t>Our principal is being admired by everyone.</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>By whom you were asked to draft this letter.</t>
+          <t>Our principal is admired by everyone.</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>By whom were you asked to draft this letter</t>
+          <t>Our principal is admired by everyone.</t>
         </is>
       </c>
       <c r="H63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>117</v>
+        <v>36</v>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>He handed her a chair.</t>
+          <t>They will demolish the entire block.</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>She was handed a chair by him.</t>
+          <t>The entire block is being demolished</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>He handed a chair to her.</t>
+          <t>The block may be demolished entirely.</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>He will hand a chair to her.</t>
+          <t>The entire block will have to be demolished</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>A chair will be handed to her by him</t>
+          <t>The entire block will be demolished by them.</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>She was handed a chair by him.</t>
-        </is>
-      </c>
-      <c r="H64" t="inlineStr"/>
+          <t>The entire block will be demolished by them.</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>The object "the entire block" becomes the subject, and "will demolish" changes to "will be demolished.</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>60</v>
+        <v>86</v>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>My books have been stolen.</t>
+          <t>Gagan Narang and Vijay won bronze medals in</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Someone has stolen my books.</t>
+          <t>Bronze medals won by Gagan Narang and</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Someone stole my books.</t>
+          <t>Bronze medals had been won by Gagan</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Someone have stolen my books.</t>
+          <t>Bronze medals were won by Gagan Narang</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>They stole my books.</t>
+          <t>Bronze medals have been won by Gagan</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Someone has stolen my books.</t>
-        </is>
-      </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>The subject "someone" is added, and "have been stolen" changes to "has stolen."</t>
-        </is>
-      </c>
+          <t>Bronze medals were won by Gagan Narang</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>One should not question his integrity.</t>
+          <t>They were pulling down the old building.</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>His integrity should not be questioned by</t>
+          <t>The old building has been pulled down.</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>His integrity should not be questioned.</t>
+          <t>The old building is being pulled down.</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>How can his integrity be questioned ?</t>
+          <t>The old building was being pulled down.</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Who can doubt his integrity ?</t>
+          <t>The old building was pulled down.</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>His integrity should not be questioned.</t>
+          <t>The old building was being pulled down.</t>
         </is>
       </c>
       <c r="H66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>69</v>
+        <v>83</v>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>The box was dropped by the boy.</t>
+          <t>We had to stop all other work to complete our</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>The boy dropped the box.</t>
+          <t>All other work has to be stopped by us to</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>The boy drops the box.</t>
+          <t>All other work has stopped by us to complete</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>The boy has dropped the box.</t>
+          <t>All other work had to be stopped by us to</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>The boy is dropping the box.</t>
+          <t>All other work was stopped by us to complete</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>The boy dropped the box.</t>
-        </is>
-      </c>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>The subject "the boy" becomes active, and "was dropped" changes to "dropped."</t>
-        </is>
-      </c>
+          <t>All other work had to be stopped by us to</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>94</v>
+        <v>4</v>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>One should keep one’s promises.</t>
+          <t>Somebody has stolen his book.</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Promises should be kept.</t>
+          <t>His book was stolen.</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>One’s promises should be kept.</t>
+          <t>His book was stolen by somebody.</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Keep the promises made by you.</t>
+          <t>His book has been stolen.</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Promises be kept.</t>
+          <t>His book had been stolen by somebody.</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>One’s promises should be kept.</t>
-        </is>
-      </c>
-      <c r="H68" t="inlineStr"/>
+          <t>His book has been stolen.</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>The object "his book" becomes the subject, and the verb changes to "has been stolen."</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>126</v>
+        <v>81</v>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>She always cooks delicious food.</t>
+          <t>She was advised 15 days’ rest after her surgery.</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Delicious food is always cooked by her.</t>
+          <t>The doctor was advised her 15 days’ rest after</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Delicious food is always being cooked by</t>
+          <t>The doctor has advised her 15 days’ rest after</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Delicious food has been cooked by her.</t>
+          <t>The doctor advised her 15 days’ rest after</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Delicious food was being cooked by her.</t>
+          <t>The doctor had advised her 15 days’ rest after</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Delicious food is always cooked by her.</t>
+          <t>The doctor advised her 15 days’ rest after</t>
         </is>
       </c>
       <c r="H69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>86</v>
+        <v>6</v>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Gagan Narang and Vijay won bronze medals in</t>
+          <t>Open the door.</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Bronze medals won by Gagan Narang and</t>
+          <t>Let the door should open.</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Bronze medals had been won by Gagan</t>
+          <t>Let the door is opened.</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Bronze medals were won by Gagan Narang</t>
+          <t>Let open the door.</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Bronze medals have been won by Gagan</t>
+          <t>Let the door be opened.</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Bronze medals were won by Gagan Narang</t>
-        </is>
-      </c>
-      <c r="H70" t="inlineStr"/>
+          <t>Let the door be opened.</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>In imperative sentences, "let" is used to form the passive voice.</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>19</v>
+        <v>112</v>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Rahul is teaching the children in the slum areas.</t>
+          <t>The purity of justice is maintained by the reports</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>The children in the slum areas are taught by</t>
+          <t>The law courts maintain purity of justice in</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>The children are taught by Rahul in the slum</t>
+          <t>The reports of the proceedings of the law</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>In the slum areas the children are learning</t>
+          <t>Pure justice is maintained in the proceedings</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>The children in the slum areas are being taught by Rahul</t>
+          <t>The maintenance of justice is pure in the</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>The children in the slum areas are being taught by Rahul</t>
-        </is>
-      </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>The object "the children in the slum areas" becomes the subject, and "is teaching" changes to "are being taught."</t>
-        </is>
-      </c>
+          <t>The reports of the proceedings of the law</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>43</v>
+        <v>19</v>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>The government has not approved the new drug</t>
+          <t>Rahul is teaching the children in the slum areas.</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>The government approval for the sale of the</t>
+          <t>The children in the slum areas are taught by</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>The new drug has not been approved by the government</t>
+          <t>The children are taught by Rahul in the slum</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>For the sale of the new drug we have not</t>
+          <t>In the slum areas the children are learning</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>The new drug was not approved by the</t>
+          <t>The children in the slum areas are being taught by Rahul</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>The new drug has not been approved by the government</t>
+          <t>The children in the slum areas are being taught by Rahul</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>The object "the new drug" becomes the subject, and "has not approved" changes to "has not been approved."</t>
+          <t>The object "the children in the slum areas" becomes the subject, and "is teaching" changes to "are being taught."</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>87</v>
+        <v>108</v>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>The modern means of communication have made</t>
+          <t>The Manager granted me two days leave.</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Life had been made so much easier by the</t>
+          <t>I had been granted two days’ leave by the</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Life is being so much easier by the modern</t>
+          <t>I have been granted two days’ leave by the</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Life has been made so much easier by the</t>
+          <t>I granted two days’ leave by the Manager.</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Life was made so much easier by the modern</t>
+          <t>I was granted two days’ leave by the</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Life has been made so much easier by the</t>
+          <t>I was granted two days’ leave by the</t>
         </is>
       </c>
       <c r="H73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>37</v>
+        <v>72</v>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>The burglar destroyed several items in the room.</t>
+          <t>My watch can’t be repaired by anyone.</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Several items destroyed in the room by the</t>
+          <t>No one will repair my watch.</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Several items in the room were destroyed by the burglar</t>
+          <t>No one can repair my watch.</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Including the carpet, several items in the</t>
+          <t>No one can’t repair my watch.</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>The burglar, being destroyed several items</t>
+          <t>No one will be able to repair my watch.</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Several items in the room were destroyed by the burglar</t>
-        </is>
-      </c>
-      <c r="H74" t="inlineStr">
-        <is>
-          <t>The object "several items in the room" becomes the subject, and "destroyed" changes to "were destroyed."</t>
-        </is>
-      </c>
+          <t>No one can repair my watch.</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>34</v>
+        <v>55</v>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>The boys were playing cricket.</t>
+          <t>Your little boy broke my kitchen window this</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Cricket had been played by the boys.</t>
+          <t>My kitchen window was broken by your little boy this morning.</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Cricket has been played by the boys.</t>
+          <t>My kitchen window had been broken by your</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Cricket was played by the boys.</t>
+          <t>My kitchen window is broken by you little</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Cricket was being played by the boys.</t>
+          <t>My kitchen window was being broken by</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Cricket was being played by the boys.</t>
+          <t>My kitchen window was broken by your little boy this morning.</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>The object "cricket" becomes the subject, and "were playing" changes to "was being played.</t>
+          <t>The object "my kitchen window" becomes the subject, and "broke" changes to "was broken."</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>45</v>
+        <v>84</v>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>He teaches us grammar.</t>
+          <t>Gandhiji started the Quit India Movement in 1942.</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Grammar is taught to us by him</t>
+          <t>The Quit India Movement was started by</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>We are taught grammar by him.</t>
+          <t>The Quit India Movement was been started</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Grammar will be taught of us by him.</t>
+          <t>The Quit India Movement had been started</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>We were teached grammar by him.</t>
+          <t>The Quit India Movement started by</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Grammar is taught to us by him</t>
-        </is>
-      </c>
-      <c r="H76" t="inlineStr">
-        <is>
-          <t>The object "grammar" becomes the subject, and "teaches" changes to "is taught."</t>
-        </is>
-      </c>
+          <t>The Quit India Movement was started by</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>24</v>
+        <v>44</v>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Can we send this big parcel by air?</t>
+          <t>They have published all the details of the report</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Can this big parcel be sent by air?</t>
+          <t>All the details of the report have been published by them</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Can this big parcel sent by air?</t>
+          <t>The publication of the details of invention</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Could this big parcel be sent by air?</t>
+          <t>All the details have been invented by the</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Could this big parcel sent by us by air?</t>
+          <t>All the inventions have been detailed by</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Can this big parcel be sent by air?</t>
+          <t>All the details of the report have been published by them</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>The object "this big parcel" becomes the subject, and "send" changes to "be sent."</t>
+          <t>The object "all the details of the report" becomes the subject, and "have published" changes to "have been published."</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>75</v>
+        <v>52</v>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Don’t subject the animals to cruelty.</t>
+          <t>Two hundred people were arrested by the police.</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>The animals are not to be subjected to</t>
+          <t>The police have arrested two hundred people.</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>The animals shall not be subjected to cruelty.</t>
+          <t>The police arrested two hundred people.</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>The animals will not be subjected to cruelty.</t>
+          <t>The police had arrested two hundred people.</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>The animals should not be subjected to</t>
+          <t>The police has arrested two hundred people.</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>The animals should not be subjected to</t>
-        </is>
-      </c>
-      <c r="H78" t="inlineStr"/>
+          <t>The police arrested two hundred people.</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>The subject "the police" becomes active, and "were arrested" changes to "arrested."</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>6</v>
+        <v>130</v>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Open the door.</t>
+          <t>Sameer shut the door with a bang.</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Let the door should open.</t>
+          <t>The door was shut with a bang by Sameer.</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Let the door is opened.</t>
+          <t>The door with a bang shut by Sameer.</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Let open the door.</t>
+          <t>The door shut Sameer with a bang.</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Let the door be opened.</t>
+          <t>The door had been shut with a bang by</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Let the door be opened.</t>
-        </is>
-      </c>
-      <c r="H79" t="inlineStr">
-        <is>
-          <t>In imperative sentences, "let" is used to form the passive voice.</t>
-        </is>
-      </c>
+          <t>The door was shut with a bang by Sameer.</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>The criminal has to obey the court.</t>
+          <t>The Metro Rail is being constructed by the corporation</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>The court has to be obeyed by the criminal.</t>
+          <t>The Corporation has been constructing the metro rail</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>The court will have to be obeyed by the</t>
+          <t>The Corporation is constructing the Metro rail</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>The court must be obeyed.</t>
+          <t>The Corporation has constructed the Metro rail</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>The court will be obeyed.</t>
+          <t>The Corporation was constructing the Metro rail</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>The court has to be obeyed by the criminal.</t>
+          <t>The Corporation is constructing the Metro rail</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>The object "the court" becomes the subject, and "has to obey" changes to "has to be obeyed."</t>
+          <t>The subject "the corporation" becomes active, and "is being constructed" changes to "is constructing."</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>91</v>
+        <v>29</v>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>They were pulling down the old building.</t>
+          <t>Circumstances forced him to resign his post.</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>The old building has been pulled down.</t>
+          <t>Circumstances make him to resign his post.</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>The old building is being pulled down.</t>
+          <t>He was forced to resign his post by circumstances</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>The old building was being pulled down.</t>
+          <t>He is forced to resign his post.</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>The old building was pulled down.</t>
+          <t>He is forced and resigned his post.</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>The old building was being pulled down.</t>
-        </is>
-      </c>
-      <c r="H81" t="inlineStr"/>
+          <t>He was forced to resign his post by circumstances</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>The object "him" becomes the subject, and "forced" changes to "was forced."</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>112</v>
+        <v>49</v>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>The purity of justice is maintained by the reports</t>
+          <t>It is impossible to do this.</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>The law courts maintain purity of justice in</t>
+          <t>Doing this is impossible.</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>The reports of the proceedings of the law</t>
+          <t>This is impossible to be done</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Pure justice is maintained in the proceedings</t>
+          <t>This must not be done</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>The maintenance of justice is pure in the</t>
+          <t>This can’t be done</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>The reports of the proceedings of the law</t>
+          <t>This is impossible to be done</t>
         </is>
       </c>
       <c r="H82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>55</v>
+        <v>18</v>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Your little boy broke my kitchen window this</t>
+          <t>The traitors should be shot dead.</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>My kitchen window was broken by your little boy this morning.</t>
+          <t>They should have shot the traitors dead.</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>My kitchen window had been broken by your</t>
+          <t>They shall shoot the traitors dead.</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>My kitchen window is broken by you little</t>
+          <t>They should shoot the traitors dead.</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>My kitchen window was being broken by</t>
+          <t>They shot the traitors dead.</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>My kitchen window was broken by your little boy this morning.</t>
+          <t>They should shoot the traitors dead.</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>The object "my kitchen window" becomes the subject, and "broke" changes to "was broken."</t>
+          <t>The subject "someone" performs the action, and "should be shot" changes to "should shoot."</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>115</v>
+        <v>42</v>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Ads on TV increase the sale of any commodity.</t>
+          <t>One must keep one’s promises.</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>The sale of any commodity is being increased</t>
+          <t>One’s promises are kept</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>The sale of any commodity are increased by</t>
+          <t>One’s promises must kept</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>The sale of any commodity are being</t>
+          <t>One’s promises were kept</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>The sale of any commodity is increased by</t>
+          <t>One’s promises must be kept</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>The sale of any commodity is increased by</t>
-        </is>
-      </c>
-      <c r="H84" t="inlineStr"/>
+          <t>One’s promises must be kept</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>The object "promises" becomes the subject, and "must keep" changes to "must be kept."</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>9</v>
+        <v>46</v>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>My watch has been stolen.</t>
+          <t>The manager could not accept the union leader’s proposal</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Someone has stolen my watch.</t>
+          <t>The union leader’s proposal could not be accepted by the manager</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>They have stolen my watch.</t>
+          <t>The union leader’s proposals were not</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>The watch has been stolen by him.</t>
+          <t>The union leader’s proposals will not be</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Somebody have stolen my watch.</t>
+          <t>The union leader’s proposals would not be</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Someone has stolen my watch.</t>
+          <t>The union leader’s proposal could not be accepted by the manager</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>The subject "someone" becomes explicit, and "has been stolen" changes to "has stolen."</t>
+          <t>The object "the union leader’s proposal" becomes the subject, and "could not accept" changes to "could not be accepted."</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>They will demolish the entire block.</t>
+          <t>The boys saved many elders from drowning.</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>The entire block is being demolished</t>
+          <t>Many elders are saved from drowning by the</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>The block may be demolished entirely.</t>
+          <t>Many elders are being saved from drowning</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>The entire block will have to be demolished</t>
+          <t>Many elders were saved from drowning by the boys</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>The entire block will be demolished by them.</t>
+          <t>Many elders have been saved from drowning</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>The entire block will be demolished by them.</t>
+          <t>Many elders were saved from drowning by the boys</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>The object "the entire block" becomes the subject, and "will demolish" changes to "will be demolished.</t>
+          <t>The object "many elders" becomes the subject, and "saved" changes to "were saved</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>120</v>
+        <v>82</v>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Who painted it?</t>
+          <t>When did he return my books ?</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>It was painted?</t>
+          <t>When were my books returned by him ?</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Was it painted?</t>
+          <t>When will my books be returned by him ?</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Had it been painted by?</t>
+          <t>When has he returned my books ?</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>By whom was it painted?</t>
+          <t>When are my books returned by him ?</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>By whom was it painted?</t>
+          <t>When were my books returned by him ?</t>
         </is>
       </c>
       <c r="H87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>33</v>
+        <v>65</v>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>The government has launched a massive tribal</t>
+          <t>The house has been painted yellow by Nikil.</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>A massive tribal welfare programme is</t>
+          <t>Nikil had painted the house yellow.</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>A massive tribal welfare program has been launched by the government.</t>
+          <t>Nikil has painted the house yellow.</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Jharkhand government has launched a</t>
+          <t>Nikil was painting yellow the house.</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>The government in Jharkhand has launched</t>
+          <t>Nikil has been painting yellow the house.</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>A massive tribal welfare program has been launched by the government.</t>
+          <t>Nikil has painted the house yellow.</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>The object "a massive tribal welfare program" becomes the subject, and "has launched" changes to "has been launched</t>
+          <t>The subject "Nikhil" becomes active, and "has been painted" changes to "has painted."</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>28</v>
+        <v>121</v>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Promises should be kept.</t>
+          <t>Nobody has answered my question.</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>You must keep the premises.</t>
+          <t>My question has been answered by</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>We must keep the promises</t>
+          <t>My question has not been answered by</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Keep the promises</t>
+          <t>My question was not answered.</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>One should keep the promises</t>
+          <t>My question remains unanswered.</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>One should keep the promises</t>
-        </is>
-      </c>
-      <c r="H89" t="inlineStr">
-        <is>
-          <t>The subject "promises" becomes the object, and "should be kept" changes to "should keep."</t>
-        </is>
-      </c>
+          <t>My question has not been answered by</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>31</v>
+        <v>63</v>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Our task had been completed before sunset.</t>
+          <t>A great deal of harm is caused to the environment</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>We completed our task before sunset.</t>
+          <t>We have caused a great deal of harm to the environment</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>We have completed our task before sunset.</t>
+          <t>The environment causes a great deal of harm</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>We complete our task before sunset.</t>
+          <t>We cause a great deal of harm to the environment</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>We had completed our task before sunset.</t>
+          <t>The environment is being caused a great deal harm</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>We had completed our task before sunset.</t>
+          <t>We cause a great deal of harm to the environment</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>The subject "our task" becomes the object, and "had been completed" changes to "had completed</t>
+          <t>The subject "human activities" becomes active, and "is caused" changes to "cause."</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>82</v>
+        <v>14</v>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>When did he return my books ?</t>
+          <t>The most useful training of my career was given to me by my boss</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>When were my books returned by him ?</t>
+          <t>My boss has been giving me the most useful</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>When will my books be returned by him ?</t>
+          <t>My boss gives me the most useful training.</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>When has he returned my books ?</t>
+          <t>My boss is giving me the most usefully</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>When are my books returned by him ?</t>
+          <t>My boss gave me the most useful training of my career</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>When were my books returned by him ?</t>
-        </is>
-      </c>
-      <c r="H91" t="inlineStr"/>
+          <t>My boss gave me the most useful training of my career</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>The subject "the mentor" becomes active, and "was given" changes to "gave."</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>22</v>
+        <v>88</v>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>The students were laughing at the old man.</t>
+          <t>Thick clouds have overcast the sky.</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>The old man was being laughed at by the</t>
+          <t>The sky has been overcast by thick clouds.</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>The old man was laughed at by the students.</t>
+          <t>The sky overcast by thick clouds.</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>The old man was being laughed by the</t>
+          <t>The sky is overcast by thick clouds.</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>The old man is laughing at the students.</t>
+          <t>The sky is being overcast by thick clouds.</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>The old man was being laughed at by the</t>
+          <t>The sky has been overcast by thick clouds.</t>
         </is>
       </c>
       <c r="H92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>105</v>
+        <v>114</v>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>They are looking after the child jointly.</t>
+          <t>An awareness is being created among the people</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>The child is being looked after by them</t>
+          <t>The Government is creating an awareness</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>The child is looked after by them jointly</t>
+          <t>The Government are creating an awareness</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>The child was being looked after by them</t>
+          <t>The Government creates an awareness</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>The child had been looked after by them</t>
+          <t>The Government created an awareness</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>The child is being looked after by them</t>
+          <t>The Government is creating an awareness</t>
         </is>
       </c>
       <c r="H93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>12</v>
+        <v>69</v>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>It is being read by us.</t>
+          <t>The box was dropped by the boy.</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>We are reading it.</t>
+          <t>The boy dropped the box.</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>It will be read by us.</t>
+          <t>The boy drops the box.</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>We can read it.</t>
+          <t>The boy has dropped the box.</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>We have to read it.</t>
+          <t>The boy is dropping the box.</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>We are reading it.</t>
+          <t>The boy dropped the box.</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>The subject "we" performs the action, and "is being read" changes to "are reading."</t>
+          <t>The subject "the boy" becomes active, and "was dropped" changes to "dropped."</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>90</v>
+        <v>43</v>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>The scheme permits investors to buy the shares</t>
+          <t>The government has not approved the new drug</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Under the scheme the investors may be</t>
+          <t>The government approval for the sale of the</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Under the scheme the investors have been</t>
+          <t>The new drug has not been approved by the government</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Under the scheme the investors are permitted</t>
+          <t>For the sale of the new drug we have not</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Under the scheme the investors were</t>
+          <t>The new drug was not approved by the</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Under the scheme the investors are permitted</t>
-        </is>
-      </c>
-      <c r="H95" t="inlineStr"/>
+          <t>The new drug has not been approved by the government</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>The object "the new drug" becomes the subject, and "has not approved" changes to "has not been approved."</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129</v>
+        <v>116</v>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Do not insult him.</t>
+          <t>The Indian Government is encouraging the</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Let he not be insulted.</t>
+          <t>The Europeans are encouraged by the Indian</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Let him not be insulted.</t>
+          <t>The Europeans are encouraging by the Indian</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Let not he be insulted.</t>
+          <t>The Europeans are being encouraged by the</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Let not him be insulted.</t>
+          <t>The Europeans is being encouraged by the</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Let him not be insulted.</t>
+          <t>The Europeans are being encouraged by the</t>
         </is>
       </c>
       <c r="H96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>The doctor advised her to take rest.</t>
+          <t>The boy laughed at the beggar.</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>She has been advised rest by the doctor.</t>
+          <t>The beggar was laughed by the boy.</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>She was advised to be taken ret by the doctor.</t>
+          <t>The beggar was being laughed by the boy.</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>She was advised to take rest by the doctor.</t>
+          <t>The beggar was being laughed at by the boy.</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>She has been advised to take rest by the</t>
+          <t>The beggar was laughed at by the boy.</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>She was advised to take rest by the doctor.</t>
+          <t>The beggar was laughed at by the boy.</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>The object "her" becomes the subject, and "advised" changes to "was advised."</t>
+          <t>The object "the beggar" becomes the subject, and "laughed at" changes to "was laughed at.</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>66</v>
+        <v>95</v>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>The news surprised me.</t>
+          <t>The thief was caught.</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>I am surprised by the news.</t>
+          <t>The policeman may have caught the thief.</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>I was surprised by the news.</t>
+          <t>The policeman caught the thief.</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>The news was surprised by me.</t>
+          <t>The policeman has caught the thief.</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>The news was a big surprise.</t>
+          <t>The policeman had caught the thief.</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>I was surprised by the news.</t>
-        </is>
-      </c>
-      <c r="H98" t="inlineStr">
-        <is>
-          <t>The object "me" becomes the subject, and "surprised" changes to "was surprised."</t>
-        </is>
-      </c>
+          <t>The policeman caught the thief.</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>118</v>
+        <v>37</v>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Call the police at once</t>
+          <t>The burglar destroyed several items in the room.</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Let the police be called at once.</t>
+          <t>Several items destroyed in the room by the</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>The police was to be called at once.</t>
+          <t>Several items in the room were destroyed by the burglar</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>The police is to be called at once.</t>
+          <t>Including the carpet, several items in the</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Let the police called at once.</t>
+          <t>The burglar, being destroyed several items</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Let the police be called at once.</t>
-        </is>
-      </c>
-      <c r="H99" t="inlineStr"/>
+          <t>Several items in the room were destroyed by the burglar</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>The object "several items in the room" becomes the subject, and "destroyed" changes to "were destroyed."</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>1</v>
+        <v>35</v>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>They do not accept credit cards everywhere.</t>
+          <t>They drew a circle in the morning.</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Credit cards are not being accepted</t>
+          <t>A circle was being drawn by them in the</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Credit cards were not accepted everywhere.</t>
+          <t>A circle was drawn by them in the morning.</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Credit cards do not accept them everywhere.</t>
+          <t>In the morning a circle have been drawn by</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Credit cards are not accepted everywhere.</t>
+          <t>A circle has been drawing since morning.</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Credit cards are not accepted everywhere.</t>
+          <t>A circle was drawn by them in the morning.</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>"They" is the subject, and "credit cards" is the object. In passive voice, the object becomes the subject, and the verb changes to "are not accepted."</t>
+          <t>The object "a circle" becomes the subject, and "drew" changes to "was drawn."</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>54</v>
+        <v>8</v>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>People speak English all over the world.</t>
+          <t>The comic scenes in the play were overdone by the actor</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>English was spoken all over the world.</t>
+          <t>The actors overdid the comic scenes in the</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>English have been spoken all over the world.</t>
+          <t>The actors overacted the comic scenes in the play</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>English has been spoken all over the world.</t>
+          <t>The play was full of comic scenes.</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>English is spoken all over the world by people</t>
+          <t>The actors comically performed the play.</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>English is spoken all over the world by people</t>
+          <t>The actors overacted the comic scenes in the play</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>The object "English" becomes the subject, and "speak" changes to "is spoken."</t>
+          <t>The subject "the actors" becomes active, and "were overdone" changes to "overdid."</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>100</v>
+        <v>48</v>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>When did he finish this work?</t>
+          <t>Please shut the door and go to sleep.</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>When this work was finished by him?</t>
+          <t>The door is to be shut and you are to go to sleep</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>When was this work finished by him?</t>
+          <t>Let the door be shut and you be asleep</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>When will this work be finished by him?</t>
+          <t>You are requested to shut the door and go to sleep</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>When he finished this work?</t>
+          <t>The door is to be shut and you are requested</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>When was this work finished by him?</t>
+          <t>You are requested to shut the door and go to sleep</t>
         </is>
       </c>
       <c r="H102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>67</v>
+        <v>31</v>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>I will have completed the task by tomorrow.</t>
+          <t>Our task had been completed before sunset.</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>The task will be completed by me by</t>
+          <t>We completed our task before sunset.</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>By tomorrow the task will have been completed</t>
+          <t>We have completed our task before sunset.</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>The task would be completed by me by tomorrow</t>
+          <t>We complete our task before sunset.</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>By tomorrow the task would have been  completed</t>
+          <t>We had completed our task before sunset.</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>By tomorrow the task will have been completed</t>
+          <t>We had completed our task before sunset.</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>The object "the task" becomes the subject, and "will have completed" changes to "will have been completed</t>
+          <t>The subject "our task" becomes the object, and "had been completed" changes to "had completed</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>11</v>
+        <v>45</v>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>People call him a fool.</t>
+          <t>He teaches us grammar.</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>He has been called a fool</t>
+          <t>Grammar is taught to us by him</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>He is called a fool by the people.</t>
+          <t>We are taught grammar by him.</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>The people have been calling him a fool.</t>
+          <t>Grammar will be taught of us by him.</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>We all people have called him a fool</t>
+          <t>We were teached grammar by him.</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>He is called a fool by the people.</t>
+          <t>Grammar is taught to us by him</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>The object "him" becomes the subject, and "call" changes to "is called."</t>
+          <t>The object "grammar" becomes the subject, and "teaches" changes to "is taught."</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>72</v>
+        <v>105</v>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>My watch can’t be repaired by anyone.</t>
+          <t>They are looking after the child jointly.</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>No one will repair my watch.</t>
+          <t>The child is being looked after by them</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>No one can repair my watch.</t>
+          <t>The child is looked after by them jointly</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>No one can’t repair my watch.</t>
+          <t>The child was being looked after by them</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>No one will be able to repair my watch.</t>
+          <t>The child had been looked after by them</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>No one can repair my watch.</t>
+          <t>The child is being looked after by them</t>
         </is>
       </c>
       <c r="H105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>71</v>
+        <v>93</v>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>They are going to build a new airport near the old</t>
+          <t>He abandoned his medical studies.</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>A new airport going to be built near the old</t>
+          <t>His medical studies had abandoned.</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>A new airport is being built near the old one.</t>
+          <t>His medical studies are abandoned.</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>A new airport will be built near the old one.</t>
+          <t>His medical studies have been abandoned.</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>A new airport is going to be built near the</t>
+          <t>His medical studies were abandoned.</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>A new airport is going to be built near the</t>
+          <t>His medical studies were abandoned.</t>
         </is>
       </c>
       <c r="H106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>83</v>
+        <v>16</v>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>We had to stop all other work to complete our</t>
+          <t>The loan will be sanctioned by the bank.</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>All other work has to be stopped by us to</t>
+          <t>The bank sanctioned the loan.</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>All other work has stopped by us to complete</t>
+          <t>The bank is going to sanction the loan.</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>All other work had to be stopped by us to</t>
+          <t>The bank would sanction the loan.</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>All other work was stopped by us to complete</t>
+          <t>The bank will sanction the loan.</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>All other work had to be stopped by us to</t>
-        </is>
-      </c>
-      <c r="H107" t="inlineStr"/>
+          <t>The bank will sanction the loan.</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>The subject "the bank" performs the action, and "will be sanctioned" changes to "will sanction."</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>25</v>
+        <v>56</v>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>The boys saved many elders from drowning.</t>
+          <t>The criminal has to obey the court.</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Many elders are saved from drowning by the</t>
+          <t>The court has to be obeyed by the criminal.</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Many elders are being saved from drowning</t>
+          <t>The court will have to be obeyed by the</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Many elders were saved from drowning by the boys</t>
+          <t>The court must be obeyed.</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Many elders have been saved from drowning</t>
+          <t>The court will be obeyed.</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Many elders were saved from drowning by the boys</t>
+          <t>The court has to be obeyed by the criminal.</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>The object "many elders" becomes the subject, and "saved" changes to "were saved</t>
+          <t>The object "the court" becomes the subject, and "has to obey" changes to "has to be obeyed."</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>46</v>
+        <v>128</v>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>The manager could not accept the union leader’s proposal</t>
+          <t>The company paid her a meagre salary.</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>The union leader’s proposal could not be accepted by the manager</t>
+          <t>She was paid a meagre salary by the</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>The union leader’s proposals were not</t>
+          <t>A meagre salary has been paid to her by the</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>The union leader’s proposals will not be</t>
+          <t>She was being paid a meagre salary by the</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>The union leader’s proposals would not be</t>
+          <t>A meagre salary was to be paid to her by the</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>The union leader’s proposal could not be accepted by the manager</t>
-        </is>
-      </c>
-      <c r="H109" t="inlineStr">
-        <is>
-          <t>The object "the union leader’s proposal" becomes the subject, and "could not accept" changes to "could not be accepted."</t>
-        </is>
-      </c>
+          <t>She was paid a meagre salary by the</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>124</v>
+        <v>39</v>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>People use computers for various purposes.</t>
+          <t>We have warned you.</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Computers are being used by people for</t>
+          <t>You have been warned by us</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Computers have been used by people for</t>
+          <t>We have you warned.</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Computers are used by people for various</t>
+          <t>Warned you have been.</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Computers will be used by people for various</t>
+          <t>Have you been warned.</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Computers are used by people for various</t>
-        </is>
-      </c>
-      <c r="H110" t="inlineStr"/>
+          <t>You have been warned by us</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>The object "you" becomes the subject, and "have warned" changes to "have been warned.</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>39</v>
+        <v>21</v>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>We have warned you.</t>
+          <t>Why did she break the garden wall?</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>You have been warned by us</t>
+          <t>Why the garden wall was broken by her?</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>We have you warned.</t>
+          <t>Why had the garden wall been broken by</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Warned you have been.</t>
+          <t>Why was the garden wall broken by her?</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Have you been warned.</t>
+          <t>Why will the garden wall be broken by her?</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>You have been warned by us</t>
+          <t>Why was the garden wall broken by her?</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>The object "you" becomes the subject, and "have warned" changes to "have been warned.</t>
+          <t>The object "the garden wall" becomes the subject, and "did break" changes to "was broken."</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>122</v>
+        <v>92</v>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>The judge delivered the sentence at the courtroom</t>
+          <t>Where did you buy this pen ?</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>The sentence been delivered yesterday by the</t>
+          <t>Where shall you buy this pen ?</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>The sentence was delivered by the judge at</t>
+          <t>Where is this pen bought by you ?</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>The sentence was being delivered at the</t>
+          <t>Where was this pen bought ?</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Yesterday, the sentence had been delivered</t>
+          <t>Where will you buy this pen ?</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>The sentence was delivered by the judge at</t>
+          <t>Where was this pen bought ?</t>
         </is>
       </c>
       <c r="H112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>The thief was caught.</t>
+          <t>Cigarettes cannot be sold here.</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>The policeman may have caught the thief.</t>
+          <t>Nobody sold cigarettes here.</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>The policeman caught the thief.</t>
+          <t>Nobody could sell cigarettes here.</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>The policeman has caught the thief.</t>
+          <t>Nobody can sell cigarettes here.</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>The policeman had caught the thief.</t>
+          <t>Anybody can’t sell cigarettes here.</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>The policeman caught the thief.</t>
+          <t>Nobody can sell cigarettes here.</t>
         </is>
       </c>
       <c r="H113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>62</v>
+        <v>10</v>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>We waste much time on social websites.</t>
+          <t>The doctor advised her to take rest.</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Much time was wasted on social websites.</t>
+          <t>She has been advised rest by the doctor.</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Much time will be wasted on social websites.</t>
+          <t>She was advised to be taken ret by the doctor.</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Much time is wasted by us on social websites</t>
+          <t>She was advised to take rest by the doctor.</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Much time is being wasted y us on social websites</t>
+          <t>She has been advised to take rest by the</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Much time is wasted by us on social websites</t>
+          <t>She was advised to take rest by the doctor.</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>The object "much time" becomes the subject, and "waste" changes to "is wasted."</t>
+          <t>The object "her" becomes the subject, and "advised" changes to "was advised."</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>88</v>
+        <v>126</v>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Thick clouds have overcast the sky.</t>
+          <t>She always cooks delicious food.</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>The sky has been overcast by thick clouds.</t>
+          <t>Delicious food is always cooked by her.</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>The sky overcast by thick clouds.</t>
+          <t>Delicious food is always being cooked by</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>The sky is overcast by thick clouds.</t>
+          <t>Delicious food has been cooked by her.</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>The sky is being overcast by thick clouds.</t>
+          <t>Delicious food was being cooked by her.</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>The sky has been overcast by thick clouds.</t>
+          <t>Delicious food is always cooked by her.</t>
         </is>
       </c>
       <c r="H115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>63</v>
+        <v>102</v>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>A great deal of harm is caused to the environment</t>
+          <t>Who helps you in your daily chores?</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>We have caused a great deal of harm to the environment</t>
+          <t>By who are you helped in your daily chores?</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>The environment causes a great deal of harm</t>
+          <t>By whom are you helped in your daily</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>We cause a great deal of harm to the environment</t>
+          <t>By who you are helped in your daily chores?</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>The environment is being caused a great deal harm</t>
+          <t>By whom you were helped in your daily</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>We cause a great deal of harm to the environment</t>
-        </is>
-      </c>
-      <c r="H116" t="inlineStr">
-        <is>
-          <t>The subject "human activities" becomes active, and "is caused" changes to "cause."</t>
-        </is>
-      </c>
+          <t>By whom are you helped in your daily</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>48</v>
+        <v>11</v>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Please shut the door and go to sleep.</t>
+          <t>People call him a fool.</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>The door is to be shut and you are to go to sleep</t>
+          <t>He has been called a fool</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>Let the door be shut and you be asleep</t>
+          <t>He is called a fool by the people.</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>You are requested to shut the door and go to sleep</t>
+          <t>The people have been calling him a fool.</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>The door is to be shut and you are requested</t>
+          <t>We all people have called him a fool</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>You are requested to shut the door and go to sleep</t>
-        </is>
-      </c>
-      <c r="H117" t="inlineStr"/>
+          <t>He is called a fool by the people.</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>The object "him" becomes the subject, and "call" changes to "is called."</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>44</v>
+        <v>62</v>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>They have published all the details of the report</t>
+          <t>We waste much time on social websites.</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>All the details of the report have been published by them</t>
+          <t>Much time was wasted on social websites.</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>The publication of the details of invention</t>
+          <t>Much time will be wasted on social websites.</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>All the details have been invented by the</t>
+          <t>Much time is wasted by us on social websites</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>All the inventions have been detailed by</t>
+          <t>Much time is being wasted y us on social websites</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>All the details of the report have been published by them</t>
+          <t>Much time is wasted by us on social websites</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>The object "all the details of the report" becomes the subject, and "have published" changes to "have been published."</t>
+          <t>The object "much time" becomes the subject, and "waste" changes to "is wasted."</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>123</v>
+        <v>106</v>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Shut all the doors and windows in the night.</t>
+          <t>How many languages are spoken in India?</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Let all the doors and windows be shut in the</t>
+          <t>How many languages Indians are speaking</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>All the doors and windows may be shut in</t>
+          <t>How many languages Indians speak?</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Let all the doors and windows remain shut</t>
+          <t>How many languages do Indians speak?</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>All the doors and windows be shutted in</t>
+          <t>How many languages did Indians speak?</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Let all the doors and windows be shut in the</t>
+          <t>How many languages do Indians speak?</t>
         </is>
       </c>
       <c r="H119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>5</v>
+        <v>74</v>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>We will telecast the programme next Sunday at 4</t>
+          <t>Could you pass the salt ?</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>The programme will be telecast by us next sunday at 4pm</t>
+          <t>Could the salt been passed ?</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>The programme would be telecast by us next</t>
+          <t>Could the salt be passed by anyone ?</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>The programme will be telecasted by us next</t>
+          <t>Could the salt be past ?</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>The programme would be telecasted by us</t>
+          <t>Could the salt be passed ?</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>The programme will be telecast by us next sunday at 4pm</t>
-        </is>
-      </c>
-      <c r="H120" t="inlineStr">
-        <is>
-          <t>The object "the programme" becomes the subject, and the verb changes to "will be telecast."</t>
-        </is>
-      </c>
+          <t>Could the salt be passed ?</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>We must take care of all living species on Earth.</t>
+          <t>All the letters were posted by them.</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>All living species on Earth are taken care of</t>
+          <t>They have posted all the letters.</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>All living species on Earth must be taken care of by us</t>
+          <t>They had posted all the letters.</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>All living species on Earth had been taken</t>
+          <t>They were posting all the letters.</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>All living species on Earth will be taken care</t>
+          <t>They posted all the letters.</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>All living species on Earth must be taken care of by us</t>
+          <t>They posted all the letters.</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>The object "all living species on Earth" becomes the subject, and "must take care of" changes to "must be taken care of</t>
+          <t>The subject "they" performs the action, and "were posted" changes to "posted."</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>57</v>
+        <v>68</v>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>The Metro Rail is being constructed by the corporation</t>
+          <t>They are painting the walls.</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>The Corporation has been constructing the metro rail</t>
+          <t>The walls are painting them.</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>The Corporation is constructing the Metro rail</t>
+          <t>The walls are painted by them.</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>The Corporation has constructed the Metro rail</t>
+          <t>The walls are being painted by them.</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>The Corporation was constructing the Metro rail</t>
+          <t>The walls in painted by them.</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>The Corporation is constructing the Metro rail</t>
+          <t>The walls are being painted by them.</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>The subject "the corporation" becomes active, and "is being constructed" changes to "is constructing."</t>
+          <t>The object "the walls" becomes the subject, and "are painting" changes to "are being painted.</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>65</v>
+        <v>17</v>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>The house has been painted yellow by Nikil.</t>
+          <t>Paint the windows.</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Nikil had painted the house yellow.</t>
+          <t>Windows should be painted.</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>Nikil has painted the house yellow.</t>
+          <t>Let the windows be painted.</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Nikil was painting yellow the house.</t>
+          <t>Let be the windows painted.</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Nikil has been painting yellow the house.</t>
+          <t>Windows are let to be painted.</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Nikil has painted the house yellow.</t>
+          <t>Let the windows be painted.</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>The subject "Nikhil" becomes active, and "has been painted" changes to "has painted."</t>
+          <t>In imperative sentences, "let" is used for passive voice.</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>The loan will be sanctioned by the bank.</t>
+          <t>He had committed a mistake.</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>The bank sanctioned the loan.</t>
+          <t>A mistake had committed by him.</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>The bank is going to sanction the loan.</t>
+          <t>A mistake was committed by him.</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>The bank would sanction the loan.</t>
+          <t>A mistake had been committed by him.</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>The bank will sanction the loan.</t>
+          <t>A mistake has been committed by him</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>The bank will sanction the loan.</t>
+          <t>A mistake had been committed by him.</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>The subject "the bank" performs the action, and "will be sanctioned" changes to "will sanction."</t>
+          <t>The object "a mistake" becomes the subject, and "had committed" changes to "had been committed."</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Newton wrote this letter yesterday.</t>
+          <t>Who painted it?</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Yesterday was written letter by Newton.</t>
+          <t>It was painted?</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>This letter is written by Newton yesterday.</t>
+          <t>Was it painted?</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>This letter was written by Newton yesterday.</t>
+          <t>Had it been painted by?</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>This letter was wrote by Newton yesterday.</t>
+          <t>By whom was it painted?</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>This letter was written by Newton yesterday.</t>
+          <t>By whom was it painted?</t>
         </is>
       </c>
       <c r="H125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>61</v>
+        <v>115</v>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>My parents are advising me about my further studies</t>
+          <t>Ads on TV increase the sale of any commodity.</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>I am being advised about my further studies by my parents.</t>
+          <t>The sale of any commodity is being increased</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>I am advised by my parents about my further studies</t>
+          <t>The sale of any commodity are increased by</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>I was advised about my further studies by my parent</t>
+          <t>The sale of any commodity are being</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>I had been advised about my further studies</t>
+          <t>The sale of any commodity is increased by</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>I am being advised about my further studies by my parents.</t>
-        </is>
-      </c>
-      <c r="H126" t="inlineStr">
-        <is>
-          <t>The object "me" becomes the subject, and "are advising" changes to "am being advised."</t>
-        </is>
-      </c>
+          <t>The sale of any commodity is increased by</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>41</v>
+        <v>67</v>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>The shopkeeper lowered the prices.</t>
+          <t>I will have completed the task by tomorrow.</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>The prices lowered the shopkeeper</t>
+          <t>The task will be completed by me by</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>The prices were lowered by the shopkeeper</t>
+          <t>By tomorrow the task will have been completed</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Down went the prices</t>
+          <t>The task would be completed by me by tomorrow</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>The shopkeeper got down the prices</t>
+          <t>By tomorrow the task would have been  completed</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>The prices were lowered by the shopkeeper</t>
+          <t>By tomorrow the task will have been completed</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>The object "the prices" becomes the subject, and "lowered" changes to "were lowered."</t>
+          <t>The object "the task" becomes the subject, and "will have completed" changes to "will have been completed</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>14</v>
+        <v>51</v>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>The most useful training of my career was given to me by my boss</t>
+          <t>They are considering your proposal,</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>My boss has been giving me the most useful</t>
+          <t>Your proposal is being considered by them.</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>My boss gives me the most useful training.</t>
+          <t>You proposal was being considered by them.</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>My boss is giving me the most usefully</t>
+          <t>Your proposal was considered by them.</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>My boss gave me the most useful training of my career</t>
+          <t>Your proposal is considered by them.</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>My boss gave me the most useful training of my career</t>
+          <t>Your proposal is being considered by them.</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>The subject "the mentor" becomes active, and "was given" changes to "gave."</t>
+          <t>The object "your proposal" becomes the subject, and "are considering" changes to "is being considered.</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>I was given a watch by my father.</t>
+          <t>One should not question his integrity.</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>My father gives me a watch.</t>
+          <t>His integrity should not be questioned by</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>My father has given me a watch.</t>
+          <t>His integrity should not be questioned.</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>My father had given me a watch.</t>
+          <t>How can his integrity be questioned ?</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>My father gave me a watch.</t>
+          <t>Who can doubt his integrity ?</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>My father gave me a watch.</t>
+          <t>His integrity should not be questioned.</t>
         </is>
       </c>
       <c r="H129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>107</v>
+        <v>77</v>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Everyone admires our principal.</t>
+          <t>They created such a fuss over a trivial matter.</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Our principal has been admired by everyone.</t>
+          <t>Such a fuss is being created over a trivial</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>Our principal was admired by everyone.</t>
+          <t>Such a fuss was created over a trivial matter.</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Our principal is being admired by everyone.</t>
+          <t>Such a fuss has been created over a trivial</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Our principal is admired by everyone.</t>
+          <t>By them such a fuss has been created over a</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Our principal is admired by everyone.</t>
+          <t>Such a fuss was created over a trivial matter.</t>
         </is>
       </c>
       <c r="H130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>18</v>
+        <v>80</v>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>The traitors should be shot dead.</t>
+          <t>Look! They have painted the door.</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>They should have shot the traitors dead.</t>
+          <t>Look! The door’s being painted.</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>They shall shoot the traitors dead.</t>
+          <t>Look! The door had been painted.</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>They should shoot the traitors dead.</t>
+          <t>Look! The door has been painted.</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>They shot the traitors dead.</t>
+          <t>Look ! The door was painted.</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>They should shoot the traitors dead.</t>
-        </is>
-      </c>
-      <c r="H131" t="inlineStr">
-        <is>
-          <t>The subject "someone" performs the action, and "should be shot" changes to "should shoot."</t>
-        </is>
-      </c>
+          <t>Look! The door has been painted.</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
